--- a/AAII_Financials/Quarterly/CABGY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CABGY_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="494" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="508" uniqueCount="92">
   <si>
     <t>CABGY</t>
   </si>
@@ -656,238 +656,250 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>2953200</v>
+        <v>5225300</v>
       </c>
       <c r="E8" s="3">
-        <v>5498900</v>
+        <v>2962300</v>
       </c>
       <c r="F8" s="3">
-        <v>2387300</v>
+        <v>5515900</v>
       </c>
       <c r="G8" s="3">
-        <v>5066700</v>
+        <v>2394600</v>
       </c>
       <c r="H8" s="3">
-        <v>2945000</v>
+        <v>5082400</v>
       </c>
       <c r="I8" s="3">
-        <v>5158200</v>
+        <v>2954100</v>
       </c>
       <c r="J8" s="3">
+        <v>5174200</v>
+      </c>
+      <c r="K8" s="3">
         <v>2173500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>4572300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2586000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>4077200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1620100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>3984500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2407800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>4229100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1899000</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E9" s="3">
-        <v>3042200</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G9" s="3">
-        <v>2787000</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I9" s="3">
-        <v>2771600</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K9" s="3">
+      <c r="D9" s="3">
+        <v>2897100</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F9" s="3">
+        <v>3051600</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H9" s="3">
+        <v>2795600</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J9" s="3">
+        <v>2780100</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L9" s="3">
         <v>2415700</v>
       </c>
-      <c r="L9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M9" s="3">
+      <c r="M9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N9" s="3">
         <v>2122300</v>
       </c>
-      <c r="N9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O9" s="3">
+      <c r="O9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P9" s="3">
         <v>2061000</v>
       </c>
-      <c r="P9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q9" s="3">
+      <c r="Q9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R9" s="3">
         <v>2172800</v>
       </c>
-      <c r="R9" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E10" s="3">
-        <v>2456700</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G10" s="3">
-        <v>2279700</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I10" s="3">
-        <v>2386700</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K10" s="3">
+      <c r="D10" s="3">
+        <v>2328200</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F10" s="3">
+        <v>2464300</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H10" s="3">
+        <v>2286800</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J10" s="3">
+        <v>2394100</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L10" s="3">
         <v>2156600</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M10" s="3">
+      <c r="M10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N10" s="3">
         <v>1954800</v>
       </c>
-      <c r="N10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O10" s="3">
+      <c r="O10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P10" s="3">
         <v>1923500</v>
       </c>
-      <c r="P10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q10" s="3">
+      <c r="Q10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R10" s="3">
         <v>2056300</v>
       </c>
-      <c r="R10" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -906,8 +918,9 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -956,8 +969,11 @@
       <c r="R12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1006,58 +1022,64 @@
       <c r="R13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E14" s="3">
-        <v>24600</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G14" s="3">
-        <v>-10000</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I14" s="3">
-        <v>124100</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K14" s="3">
+      <c r="D14" s="3">
+        <v>38200</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F14" s="3">
+        <v>24700</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H14" s="3">
+        <v>-10100</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J14" s="3">
+        <v>124500</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L14" s="3">
         <v>-34900</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M14" s="3">
+      <c r="M14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N14" s="3">
         <v>28200</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O14" s="3">
+      <c r="O14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P14" s="3">
         <v>38500</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q14" s="3">
+      <c r="Q14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R14" s="3">
         <v>1800</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1106,8 +1128,11 @@
       <c r="R15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1123,108 +1148,115 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E17" s="3">
-        <v>4610800</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G17" s="3">
-        <v>4325000</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I17" s="3">
-        <v>4344900</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K17" s="3">
+      <c r="D17" s="3">
+        <v>4558100</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F17" s="3">
+        <v>4625100</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H17" s="3">
+        <v>4338400</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J17" s="3">
+        <v>4358400</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L17" s="3">
         <v>3608300</v>
       </c>
-      <c r="L17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M17" s="3">
+      <c r="M17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N17" s="3">
         <v>3427400</v>
       </c>
-      <c r="N17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O17" s="3">
+      <c r="O17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P17" s="3">
         <v>3341200</v>
       </c>
-      <c r="P17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q17" s="3">
+      <c r="Q17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R17" s="3">
         <v>3553900</v>
       </c>
-      <c r="R17" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E18" s="3">
-        <v>888100</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G18" s="3">
-        <v>741700</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I18" s="3">
-        <v>813300</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K18" s="3">
+      <c r="D18" s="3">
+        <v>667200</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F18" s="3">
+        <v>890900</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H18" s="3">
+        <v>744000</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J18" s="3">
+        <v>815800</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L18" s="3">
         <v>964100</v>
       </c>
-      <c r="L18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M18" s="3">
+      <c r="M18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N18" s="3">
         <v>649700</v>
       </c>
-      <c r="N18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O18" s="3">
+      <c r="O18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P18" s="3">
         <v>643300</v>
       </c>
-      <c r="P18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q18" s="3">
+      <c r="Q18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R18" s="3">
         <v>675200</v>
       </c>
-      <c r="R18" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1243,58 +1275,62 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E20" s="3">
+      <c r="D20" s="3">
+        <v>-8900</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F20" s="3">
         <v>-1000</v>
       </c>
-      <c r="F20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G20" s="3">
+      <c r="G20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H20" s="3">
         <v>11800</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I20" s="3">
-        <v>-38700</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K20" s="3">
+      <c r="I20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J20" s="3">
+        <v>-38800</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L20" s="3">
         <v>-33300</v>
       </c>
-      <c r="L20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M20" s="3">
+      <c r="M20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N20" s="3">
         <v>-1600</v>
       </c>
-      <c r="N20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O20" s="3">
+      <c r="O20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P20" s="3">
         <v>13400</v>
       </c>
-      <c r="P20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q20" s="3">
+      <c r="Q20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R20" s="3">
         <v>5300</v>
       </c>
-      <c r="R20" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1313,188 +1349,200 @@
       <c r="H21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I21" s="3">
-        <v>1084300</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K21" s="3">
+      <c r="I21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J21" s="3">
+        <v>1087600</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L21" s="3">
         <v>1547400</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M21" s="3">
+      <c r="M21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N21" s="3">
         <v>926400</v>
       </c>
-      <c r="N21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O21" s="3">
+      <c r="O21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P21" s="3">
         <v>1244900</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q21" s="3">
+      <c r="Q21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R21" s="3">
         <v>1000600</v>
       </c>
-      <c r="R21" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E22" s="3">
-        <v>47300</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G22" s="3">
-        <v>41600</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I22" s="3">
-        <v>37000</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K22" s="3">
+      <c r="D22" s="3">
+        <v>65800</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F22" s="3">
+        <v>47400</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H22" s="3">
+        <v>41700</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J22" s="3">
         <v>37100</v>
       </c>
-      <c r="L22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M22" s="3">
+      <c r="K22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L22" s="3">
+        <v>37100</v>
+      </c>
+      <c r="M22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N22" s="3">
         <v>36000</v>
       </c>
-      <c r="N22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O22" s="3">
+      <c r="O22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P22" s="3">
         <v>34900</v>
       </c>
-      <c r="P22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q22" s="3">
+      <c r="Q22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R22" s="3">
         <v>34500</v>
       </c>
-      <c r="R22" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E23" s="3">
-        <v>839800</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G23" s="3">
-        <v>711900</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I23" s="3">
-        <v>737600</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K23" s="3">
+      <c r="D23" s="3">
+        <v>592500</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F23" s="3">
+        <v>842400</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H23" s="3">
+        <v>714100</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J23" s="3">
+        <v>739900</v>
+      </c>
+      <c r="K23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L23" s="3">
         <v>893700</v>
       </c>
-      <c r="L23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M23" s="3">
+      <c r="M23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N23" s="3">
         <v>612200</v>
       </c>
-      <c r="N23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O23" s="3">
+      <c r="O23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P23" s="3">
         <v>621900</v>
       </c>
-      <c r="P23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q23" s="3">
+      <c r="Q23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R23" s="3">
         <v>646000</v>
       </c>
-      <c r="R23" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E24" s="3">
-        <v>176400</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G24" s="3">
-        <v>96500</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I24" s="3">
-        <v>162300</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K24" s="3">
+      <c r="D24" s="3">
+        <v>94400</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F24" s="3">
+        <v>176900</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H24" s="3">
+        <v>96800</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J24" s="3">
+        <v>162800</v>
+      </c>
+      <c r="K24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L24" s="3">
         <v>152500</v>
       </c>
-      <c r="L24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M24" s="3">
+      <c r="M24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N24" s="3">
         <v>157300</v>
       </c>
-      <c r="N24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O24" s="3">
+      <c r="O24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P24" s="3">
         <v>145900</v>
       </c>
-      <c r="P24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q24" s="3">
+      <c r="Q24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R24" s="3">
         <v>168000</v>
       </c>
-      <c r="R24" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1543,108 +1591,117 @@
       <c r="R25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E26" s="3">
-        <v>663400</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G26" s="3">
-        <v>615400</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I26" s="3">
-        <v>575400</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K26" s="3">
+      <c r="D26" s="3">
+        <v>498000</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F26" s="3">
+        <v>665500</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H26" s="3">
+        <v>617300</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J26" s="3">
+        <v>577200</v>
+      </c>
+      <c r="K26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L26" s="3">
         <v>741200</v>
       </c>
-      <c r="L26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M26" s="3">
+      <c r="M26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N26" s="3">
         <v>454900</v>
       </c>
-      <c r="N26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O26" s="3">
+      <c r="O26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P26" s="3">
         <v>476000</v>
       </c>
-      <c r="P26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q26" s="3">
+      <c r="Q26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R26" s="3">
         <v>478100</v>
       </c>
-      <c r="R26" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E27" s="3">
-        <v>567400</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G27" s="3">
-        <v>534100</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I27" s="3">
-        <v>486300</v>
-      </c>
-      <c r="J27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K27" s="3">
+      <c r="D27" s="3">
+        <v>446800</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F27" s="3">
+        <v>569100</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H27" s="3">
+        <v>535700</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J27" s="3">
+        <v>487800</v>
+      </c>
+      <c r="K27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L27" s="3">
         <v>642700</v>
       </c>
-      <c r="L27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M27" s="3">
+      <c r="M27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N27" s="3">
         <v>385800</v>
       </c>
-      <c r="N27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O27" s="3">
+      <c r="O27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P27" s="3">
         <v>425800</v>
       </c>
-      <c r="P27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q27" s="3">
+      <c r="Q27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R27" s="3">
         <v>418800</v>
       </c>
-      <c r="R27" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1693,49 +1750,52 @@
       <c r="R28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E29" s="3">
-        <v>-58800</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G29" s="3">
-        <v>79000</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I29" s="3">
-        <v>-1254100</v>
-      </c>
-      <c r="J29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K29" s="3">
+      <c r="D29" s="3">
+        <v>-6910800</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F29" s="3">
+        <v>-59000</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H29" s="3">
+        <v>79300</v>
+      </c>
+      <c r="I29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J29" s="3">
+        <v>-1258000</v>
+      </c>
+      <c r="K29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L29" s="3">
         <v>-87000</v>
       </c>
-      <c r="L29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M29" s="3">
+      <c r="M29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N29" s="3">
         <v>44700</v>
       </c>
-      <c r="N29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P29" s="3">
-        <v>0</v>
+      <c r="P29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q29" s="3">
         <v>0</v>
@@ -1743,8 +1803,11 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1793,8 +1856,11 @@
       <c r="R30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1843,108 +1909,117 @@
       <c r="R31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E32" s="3">
+      <c r="D32" s="3">
+        <v>8900</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F32" s="3">
         <v>1000</v>
       </c>
-      <c r="F32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G32" s="3">
+      <c r="G32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H32" s="3">
         <v>-11800</v>
       </c>
-      <c r="H32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I32" s="3">
-        <v>38700</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K32" s="3">
+      <c r="I32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J32" s="3">
+        <v>38800</v>
+      </c>
+      <c r="K32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L32" s="3">
         <v>33300</v>
       </c>
-      <c r="L32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M32" s="3">
+      <c r="M32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N32" s="3">
         <v>1600</v>
       </c>
-      <c r="N32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O32" s="3">
+      <c r="O32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P32" s="3">
         <v>-13400</v>
       </c>
-      <c r="P32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q32" s="3">
+      <c r="Q32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R32" s="3">
         <v>-5300</v>
       </c>
-      <c r="R32" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E33" s="3">
-        <v>508600</v>
-      </c>
-      <c r="F33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G33" s="3">
-        <v>613100</v>
-      </c>
-      <c r="H33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I33" s="3">
-        <v>-767800</v>
-      </c>
-      <c r="J33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K33" s="3">
+      <c r="D33" s="3">
+        <v>-6464000</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F33" s="3">
+        <v>510200</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H33" s="3">
+        <v>615000</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J33" s="3">
+        <v>-770100</v>
+      </c>
+      <c r="K33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L33" s="3">
         <v>555700</v>
       </c>
-      <c r="L33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M33" s="3">
+      <c r="M33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N33" s="3">
         <v>430400</v>
       </c>
-      <c r="N33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O33" s="3">
+      <c r="O33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P33" s="3">
         <v>425800</v>
       </c>
-      <c r="P33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q33" s="3">
+      <c r="Q33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R33" s="3">
         <v>418800</v>
       </c>
-      <c r="R33" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1993,113 +2068,122 @@
       <c r="R34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E35" s="3">
-        <v>508600</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G35" s="3">
-        <v>613100</v>
-      </c>
-      <c r="H35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I35" s="3">
-        <v>-767800</v>
-      </c>
-      <c r="J35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K35" s="3">
+      <c r="D35" s="3">
+        <v>-6464000</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F35" s="3">
+        <v>510200</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H35" s="3">
+        <v>615000</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J35" s="3">
+        <v>-770100</v>
+      </c>
+      <c r="K35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L35" s="3">
         <v>555700</v>
       </c>
-      <c r="L35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M35" s="3">
+      <c r="M35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N35" s="3">
         <v>430400</v>
       </c>
-      <c r="N35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O35" s="3">
+      <c r="O35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P35" s="3">
         <v>425800</v>
       </c>
-      <c r="P35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q35" s="3">
+      <c r="Q35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R35" s="3">
         <v>418800</v>
       </c>
-      <c r="R35" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2118,8 +2202,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2138,28 +2223,29 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>1635200</v>
+        <v>1953400</v>
       </c>
       <c r="E41" s="3">
-        <v>1187900</v>
+        <v>1640300</v>
       </c>
       <c r="F41" s="3">
-        <v>1933500</v>
+        <v>1191600</v>
       </c>
       <c r="G41" s="3">
-        <v>1214200</v>
+        <v>1939500</v>
       </c>
       <c r="H41" s="3">
-        <v>1218900</v>
-      </c>
-      <c r="I41" s="3" t="s">
-        <v>5</v>
+        <v>1218000</v>
+      </c>
+      <c r="I41" s="3">
+        <v>1222600</v>
       </c>
       <c r="J41" s="3" t="s">
         <v>5</v>
@@ -2188,31 +2274,34 @@
       <c r="R41" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
-      </c>
-      <c r="E42" s="3">
-        <v>0</v>
-      </c>
-      <c r="F42" s="3">
-        <v>0</v>
-      </c>
-      <c r="G42" s="3">
-        <v>0</v>
-      </c>
-      <c r="H42" s="3">
-        <v>0</v>
-      </c>
-      <c r="I42" s="3">
-        <v>0</v>
-      </c>
-      <c r="J42" s="3">
-        <v>0</v>
+        <v>326400</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J42" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K42" s="3">
         <v>0</v>
@@ -2238,28 +2327,31 @@
       <c r="R42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>1785100</v>
+        <v>1158100</v>
       </c>
       <c r="E43" s="3">
-        <v>1133000</v>
+        <v>1790600</v>
       </c>
       <c r="F43" s="3">
-        <v>1601400</v>
+        <v>1136500</v>
       </c>
       <c r="G43" s="3">
-        <v>1198500</v>
+        <v>1606400</v>
       </c>
       <c r="H43" s="3">
-        <v>1574400</v>
-      </c>
-      <c r="I43" s="3" t="s">
-        <v>5</v>
+        <v>1202200</v>
+      </c>
+      <c r="I43" s="3">
+        <v>1579200</v>
       </c>
       <c r="J43" s="3" t="s">
         <v>5</v>
@@ -2288,28 +2380,31 @@
       <c r="R43" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>975000</v>
+        <v>848200</v>
       </c>
       <c r="E44" s="3">
-        <v>832100</v>
+        <v>978000</v>
       </c>
       <c r="F44" s="3">
-        <v>825700</v>
+        <v>834700</v>
       </c>
       <c r="G44" s="3">
-        <v>784500</v>
+        <v>828200</v>
       </c>
       <c r="H44" s="3">
-        <v>793800</v>
-      </c>
-      <c r="I44" s="3" t="s">
-        <v>5</v>
+        <v>786900</v>
+      </c>
+      <c r="I44" s="3">
+        <v>796300</v>
       </c>
       <c r="J44" s="3" t="s">
         <v>5</v>
@@ -2338,25 +2433,28 @@
       <c r="R44" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>1467600</v>
+        <v>121900</v>
       </c>
       <c r="E45" s="3">
-        <v>1830900</v>
+        <v>1472100</v>
       </c>
       <c r="F45" s="3">
-        <v>2404400</v>
+        <v>1836600</v>
       </c>
       <c r="G45" s="3">
-        <v>135200</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>5</v>
+        <v>2411900</v>
+      </c>
+      <c r="H45" s="3">
+        <v>135600</v>
       </c>
       <c r="I45" s="3" t="s">
         <v>5</v>
@@ -2388,28 +2486,31 @@
       <c r="R45" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>5862900</v>
+        <v>4408000</v>
       </c>
       <c r="E46" s="3">
-        <v>4983900</v>
+        <v>5881000</v>
       </c>
       <c r="F46" s="3">
-        <v>6765100</v>
+        <v>4999300</v>
       </c>
       <c r="G46" s="3">
-        <v>3332400</v>
+        <v>6786000</v>
       </c>
       <c r="H46" s="3">
-        <v>3587100</v>
-      </c>
-      <c r="I46" s="3" t="s">
-        <v>5</v>
+        <v>3342700</v>
+      </c>
+      <c r="I46" s="3">
+        <v>3598200</v>
       </c>
       <c r="J46" s="3" t="s">
         <v>5</v>
@@ -2438,28 +2539,31 @@
       <c r="R46" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>1178300</v>
+        <v>922200</v>
       </c>
       <c r="E47" s="3">
-        <v>939900</v>
+        <v>1181900</v>
       </c>
       <c r="F47" s="3">
-        <v>1143600</v>
+        <v>942800</v>
       </c>
       <c r="G47" s="3">
-        <v>909100</v>
+        <v>1147200</v>
       </c>
       <c r="H47" s="3">
-        <v>986500</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>5</v>
+        <v>911900</v>
+      </c>
+      <c r="I47" s="3">
+        <v>989500</v>
       </c>
       <c r="J47" s="3" t="s">
         <v>5</v>
@@ -2488,28 +2592,31 @@
       <c r="R47" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>3433000</v>
+        <v>3562400</v>
       </c>
       <c r="E48" s="3">
-        <v>3445800</v>
+        <v>3443600</v>
       </c>
       <c r="F48" s="3">
-        <v>3444300</v>
+        <v>3456400</v>
       </c>
       <c r="G48" s="3">
-        <v>3877800</v>
+        <v>3455000</v>
       </c>
       <c r="H48" s="3">
-        <v>3886800</v>
-      </c>
-      <c r="I48" s="3" t="s">
-        <v>5</v>
+        <v>3889800</v>
+      </c>
+      <c r="I48" s="3">
+        <v>3898900</v>
       </c>
       <c r="J48" s="3" t="s">
         <v>5</v>
@@ -2538,28 +2645,31 @@
       <c r="R48" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>7134700</v>
+        <v>7167100</v>
       </c>
       <c r="E49" s="3">
-        <v>7162900</v>
+        <v>7156800</v>
       </c>
       <c r="F49" s="3">
-        <v>7312100</v>
+        <v>7185100</v>
       </c>
       <c r="G49" s="3">
-        <v>9964500</v>
+        <v>7334700</v>
       </c>
       <c r="H49" s="3">
-        <v>9883100</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>5</v>
+        <v>9995300</v>
+      </c>
+      <c r="I49" s="3">
+        <v>9913700</v>
       </c>
       <c r="J49" s="3" t="s">
         <v>5</v>
@@ -2588,8 +2698,11 @@
       <c r="R49" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2638,8 +2751,11 @@
       <c r="R50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2688,25 +2804,28 @@
       <c r="R51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E52" s="3">
-        <v>251900</v>
-      </c>
-      <c r="F52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G52" s="3">
-        <v>307500</v>
-      </c>
-      <c r="H52" s="3" t="s">
-        <v>5</v>
+      <c r="D52" s="3">
+        <v>264200</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F52" s="3">
+        <v>252700</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H52" s="3">
+        <v>308400</v>
       </c>
       <c r="I52" s="3" t="s">
         <v>5</v>
@@ -2738,8 +2857,11 @@
       <c r="R52" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2788,28 +2910,31 @@
       <c r="R53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>17608800</v>
+        <v>16324000</v>
       </c>
       <c r="E54" s="3">
-        <v>16784400</v>
+        <v>17663200</v>
       </c>
       <c r="F54" s="3">
-        <v>18665100</v>
+        <v>16836300</v>
       </c>
       <c r="G54" s="3">
-        <v>18391300</v>
+        <v>18722800</v>
       </c>
       <c r="H54" s="3">
-        <v>18343500</v>
-      </c>
-      <c r="I54" s="3" t="s">
-        <v>5</v>
+        <v>18448100</v>
+      </c>
+      <c r="I54" s="3">
+        <v>18400200</v>
       </c>
       <c r="J54" s="3" t="s">
         <v>5</v>
@@ -2838,8 +2963,11 @@
       <c r="R54" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2858,8 +2986,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2878,28 +3007,29 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>3645900</v>
+        <v>3234500</v>
       </c>
       <c r="E57" s="3">
-        <v>3189400</v>
+        <v>3657100</v>
       </c>
       <c r="F57" s="3">
-        <v>3546800</v>
+        <v>3199200</v>
       </c>
       <c r="G57" s="3">
-        <v>3003800</v>
+        <v>3557700</v>
       </c>
       <c r="H57" s="3">
-        <v>3118500</v>
-      </c>
-      <c r="I57" s="3" t="s">
-        <v>5</v>
+        <v>3013100</v>
+      </c>
+      <c r="I57" s="3">
+        <v>3128100</v>
       </c>
       <c r="J57" s="3" t="s">
         <v>5</v>
@@ -2928,28 +3058,31 @@
       <c r="R57" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>1982000</v>
+        <v>1217100</v>
       </c>
       <c r="E58" s="3">
-        <v>841300</v>
+        <v>1988100</v>
       </c>
       <c r="F58" s="3">
-        <v>1458000</v>
+        <v>843900</v>
       </c>
       <c r="G58" s="3">
-        <v>897400</v>
+        <v>1462500</v>
       </c>
       <c r="H58" s="3">
-        <v>240700</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>5</v>
+        <v>900200</v>
+      </c>
+      <c r="I58" s="3">
+        <v>241400</v>
       </c>
       <c r="J58" s="3" t="s">
         <v>5</v>
@@ -2978,28 +3111,31 @@
       <c r="R58" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>3208300</v>
+        <v>2442500</v>
       </c>
       <c r="E59" s="3">
-        <v>3063100</v>
+        <v>3218200</v>
       </c>
       <c r="F59" s="3">
-        <v>3458100</v>
+        <v>3072500</v>
       </c>
       <c r="G59" s="3">
-        <v>2397200</v>
+        <v>3468800</v>
       </c>
       <c r="H59" s="3">
-        <v>1885800</v>
-      </c>
-      <c r="I59" s="3" t="s">
-        <v>5</v>
+        <v>2404600</v>
+      </c>
+      <c r="I59" s="3">
+        <v>1891600</v>
       </c>
       <c r="J59" s="3" t="s">
         <v>5</v>
@@ -3028,28 +3164,31 @@
       <c r="R59" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>8836100</v>
+        <v>6894200</v>
       </c>
       <c r="E60" s="3">
-        <v>7093700</v>
+        <v>8863400</v>
       </c>
       <c r="F60" s="3">
-        <v>8462900</v>
+        <v>7115600</v>
       </c>
       <c r="G60" s="3">
-        <v>6298400</v>
+        <v>8489000</v>
       </c>
       <c r="H60" s="3">
-        <v>5245000</v>
-      </c>
-      <c r="I60" s="3" t="s">
-        <v>5</v>
+        <v>6317900</v>
+      </c>
+      <c r="I60" s="3">
+        <v>5261200</v>
       </c>
       <c r="J60" s="3" t="s">
         <v>5</v>
@@ -3078,28 +3217,31 @@
       <c r="R60" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>3081400</v>
+        <v>4490500</v>
       </c>
       <c r="E61" s="3">
-        <v>3327300</v>
+        <v>3090900</v>
       </c>
       <c r="F61" s="3">
-        <v>3304000</v>
+        <v>3337600</v>
       </c>
       <c r="G61" s="3">
-        <v>3311300</v>
+        <v>3314200</v>
       </c>
       <c r="H61" s="3">
-        <v>4132200</v>
+        <v>3321500</v>
       </c>
       <c r="I61" s="3">
-        <v>0</v>
+        <v>4145000</v>
       </c>
       <c r="J61" s="3">
         <v>0</v>
@@ -3128,28 +3270,31 @@
       <c r="R61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1221600</v>
+        <v>1180800</v>
       </c>
       <c r="E62" s="3">
-        <v>1310700</v>
+        <v>1225400</v>
       </c>
       <c r="F62" s="3">
-        <v>1411400</v>
+        <v>1314800</v>
       </c>
       <c r="G62" s="3">
-        <v>1686600</v>
+        <v>1415800</v>
       </c>
       <c r="H62" s="3">
-        <v>2395000</v>
-      </c>
-      <c r="I62" s="3" t="s">
-        <v>5</v>
+        <v>1691800</v>
+      </c>
+      <c r="I62" s="3">
+        <v>2402400</v>
       </c>
       <c r="J62" s="3" t="s">
         <v>5</v>
@@ -3178,8 +3323,11 @@
       <c r="R62" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3228,8 +3376,11 @@
       <c r="R63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3278,8 +3429,11 @@
       <c r="R64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3328,28 +3482,31 @@
       <c r="R65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>13492600</v>
+        <v>12932500</v>
       </c>
       <c r="E66" s="3">
-        <v>12142000</v>
+        <v>13534300</v>
       </c>
       <c r="F66" s="3">
-        <v>13803000</v>
+        <v>12179600</v>
       </c>
       <c r="G66" s="3">
-        <v>11997000</v>
+        <v>13845700</v>
       </c>
       <c r="H66" s="3">
-        <v>12407900</v>
-      </c>
-      <c r="I66" s="3" t="s">
-        <v>5</v>
+        <v>12034100</v>
+      </c>
+      <c r="I66" s="3">
+        <v>12446300</v>
       </c>
       <c r="J66" s="3" t="s">
         <v>5</v>
@@ -3378,8 +3535,11 @@
       <c r="R66" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3398,8 +3558,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3448,8 +3609,11 @@
       <c r="R68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3498,8 +3662,11 @@
       <c r="R69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3548,8 +3715,11 @@
       <c r="R70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3598,28 +3768,31 @@
       <c r="R71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>10110400</v>
+        <v>3402000</v>
       </c>
       <c r="E72" s="3">
-        <v>10299300</v>
+        <v>10141700</v>
       </c>
       <c r="F72" s="3">
-        <v>9975000</v>
+        <v>10331200</v>
       </c>
       <c r="G72" s="3">
-        <v>11474700</v>
+        <v>10005800</v>
       </c>
       <c r="H72" s="3">
-        <v>11245500</v>
-      </c>
-      <c r="I72" s="3" t="s">
-        <v>5</v>
+        <v>11510200</v>
+      </c>
+      <c r="I72" s="3">
+        <v>11280300</v>
       </c>
       <c r="J72" s="3" t="s">
         <v>5</v>
@@ -3648,8 +3821,11 @@
       <c r="R72" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3698,8 +3874,11 @@
       <c r="R73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3748,8 +3927,11 @@
       <c r="R74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3798,28 +3980,31 @@
       <c r="R75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>4116200</v>
+        <v>3391500</v>
       </c>
       <c r="E76" s="3">
-        <v>4642400</v>
+        <v>4128900</v>
       </c>
       <c r="F76" s="3">
-        <v>4862100</v>
+        <v>4656700</v>
       </c>
       <c r="G76" s="3">
-        <v>6394300</v>
+        <v>4877100</v>
       </c>
       <c r="H76" s="3">
-        <v>5935600</v>
-      </c>
-      <c r="I76" s="3" t="s">
-        <v>5</v>
+        <v>6414100</v>
+      </c>
+      <c r="I76" s="3">
+        <v>5954000</v>
       </c>
       <c r="J76" s="3" t="s">
         <v>5</v>
@@ -3848,8 +4033,11 @@
       <c r="R76" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3898,113 +4086,122 @@
       <c r="R77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E81" s="3">
-        <v>508600</v>
-      </c>
-      <c r="F81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G81" s="3">
-        <v>613100</v>
-      </c>
-      <c r="H81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I81" s="3">
-        <v>-767800</v>
-      </c>
-      <c r="J81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K81" s="3">
+      <c r="D81" s="3">
+        <v>-6464000</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F81" s="3">
+        <v>510200</v>
+      </c>
+      <c r="G81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H81" s="3">
+        <v>615000</v>
+      </c>
+      <c r="I81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J81" s="3">
+        <v>-770100</v>
+      </c>
+      <c r="K81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L81" s="3">
         <v>555700</v>
       </c>
-      <c r="L81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M81" s="3">
+      <c r="M81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N81" s="3">
         <v>430400</v>
       </c>
-      <c r="N81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O81" s="3">
+      <c r="O81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P81" s="3">
         <v>425800</v>
       </c>
-      <c r="P81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q81" s="3">
+      <c r="Q81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R81" s="3">
         <v>418800</v>
       </c>
-      <c r="R81" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4023,8 +4220,9 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4043,38 +4241,41 @@
       <c r="H83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I83" s="3">
-        <v>309700</v>
-      </c>
-      <c r="J83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K83" s="3">
+      <c r="I83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J83" s="3">
+        <v>310600</v>
+      </c>
+      <c r="K83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L83" s="3">
         <v>671000</v>
       </c>
-      <c r="L83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M83" s="3">
+      <c r="M83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N83" s="3">
         <v>303500</v>
       </c>
-      <c r="N83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O83" s="3">
+      <c r="O83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P83" s="3">
         <v>588200</v>
       </c>
-      <c r="P83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q83" s="3">
+      <c r="Q83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R83" s="3">
         <v>320100</v>
       </c>
-      <c r="R83" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4123,8 +4324,11 @@
       <c r="R84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4173,8 +4377,11 @@
       <c r="R85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4223,8 +4430,11 @@
       <c r="R86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4273,8 +4483,11 @@
       <c r="R87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4323,8 +4536,11 @@
       <c r="R88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -4343,38 +4559,41 @@
       <c r="H89" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I89" s="3">
-        <v>1219500</v>
-      </c>
-      <c r="J89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K89" s="3">
+      <c r="I89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J89" s="3">
+        <v>1223200</v>
+      </c>
+      <c r="K89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L89" s="3">
         <v>1929200</v>
       </c>
-      <c r="L89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M89" s="3">
+      <c r="M89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N89" s="3">
         <v>950500</v>
       </c>
-      <c r="N89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O89" s="3">
+      <c r="O89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P89" s="3">
         <v>1465600</v>
       </c>
-      <c r="P89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q89" s="3">
+      <c r="Q89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R89" s="3">
         <v>749900</v>
       </c>
-      <c r="R89" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4393,26 +4612,27 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-2451000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1792000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-2412000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1606000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-2244000</v>
       </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
       <c r="I91" s="3">
         <v>0</v>
       </c>
@@ -4426,25 +4646,28 @@
         <v>0</v>
       </c>
       <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3">
         <v>-235900</v>
       </c>
-      <c r="N91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O91" s="3">
+      <c r="O91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P91" s="3">
         <v>-589500</v>
       </c>
-      <c r="P91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q91" s="3">
+      <c r="Q91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R91" s="3">
         <v>-363900</v>
       </c>
-      <c r="R91" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4493,8 +4716,11 @@
       <c r="R92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4543,8 +4769,11 @@
       <c r="R93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -4563,38 +4792,41 @@
       <c r="H94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I94" s="3">
-        <v>-158000</v>
-      </c>
-      <c r="J94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K94" s="3">
+      <c r="I94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J94" s="3">
+        <v>-158500</v>
+      </c>
+      <c r="K94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L94" s="3">
         <v>-591700</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M94" s="3">
+      <c r="M94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N94" s="3">
         <v>-179600</v>
       </c>
-      <c r="N94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O94" s="3">
+      <c r="O94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P94" s="3">
         <v>-787400</v>
       </c>
-      <c r="P94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q94" s="3">
+      <c r="Q94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R94" s="3">
         <v>-289100</v>
       </c>
-      <c r="R94" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4613,8 +4845,9 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4634,37 +4867,40 @@
         <v>0</v>
       </c>
       <c r="I96" s="3">
-        <v>-493200</v>
+        <v>0</v>
       </c>
       <c r="J96" s="3">
-        <v>0</v>
+        <v>-494700</v>
       </c>
       <c r="K96" s="3">
+        <v>0</v>
+      </c>
+      <c r="L96" s="3">
         <v>-463700</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
       <c r="M96" s="3">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3">
         <v>-453200</v>
       </c>
-      <c r="N96" s="3">
-        <v>0</v>
-      </c>
       <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3">
         <v>-414800</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
-      </c>
       <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3">
         <v>-453700</v>
       </c>
-      <c r="R96" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4713,8 +4949,11 @@
       <c r="R97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4763,8 +5002,11 @@
       <c r="R98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4813,8 +5055,11 @@
       <c r="R99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -4833,38 +5078,41 @@
       <c r="H100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I100" s="3">
-        <v>-327100</v>
-      </c>
-      <c r="J100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K100" s="3">
+      <c r="I100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J100" s="3">
+        <v>-328100</v>
+      </c>
+      <c r="K100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L100" s="3">
         <v>-1301500</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M100" s="3">
+      <c r="M100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N100" s="3">
         <v>-713100</v>
       </c>
-      <c r="N100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O100" s="3">
+      <c r="O100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P100" s="3">
         <v>-242700</v>
       </c>
-      <c r="P100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q100" s="3">
+      <c r="Q100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R100" s="3">
         <v>-73200</v>
       </c>
-      <c r="R100" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4883,38 +5131,41 @@
       <c r="H101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I101" s="3">
-        <v>56900</v>
-      </c>
-      <c r="J101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K101" s="3">
+      <c r="I101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J101" s="3">
+        <v>57100</v>
+      </c>
+      <c r="K101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L101" s="3">
         <v>66600</v>
       </c>
-      <c r="L101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M101" s="3">
+      <c r="M101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N101" s="3">
         <v>22600</v>
       </c>
-      <c r="N101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O101" s="3">
+      <c r="O101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P101" s="3">
         <v>-58700</v>
       </c>
-      <c r="P101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q101" s="3">
+      <c r="Q101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R101" s="3">
         <v>-16700</v>
       </c>
-      <c r="R101" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -4933,34 +5184,37 @@
       <c r="H102" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I102" s="3">
-        <v>791200</v>
-      </c>
-      <c r="J102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K102" s="3">
+      <c r="I102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J102" s="3">
+        <v>793600</v>
+      </c>
+      <c r="K102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L102" s="3">
         <v>56200</v>
       </c>
-      <c r="L102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M102" s="3">
+      <c r="M102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N102" s="3">
         <v>59400</v>
       </c>
-      <c r="N102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O102" s="3">
+      <c r="O102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P102" s="3">
         <v>376700</v>
       </c>
-      <c r="P102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q102" s="3">
+      <c r="Q102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R102" s="3">
         <v>370800</v>
       </c>
-      <c r="R102" s="3" t="s">
+      <c r="S102" s="3" t="s">
         <v>5</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CABGY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CABGY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="508" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="546" uniqueCount="92">
   <si>
     <t>CABGY</t>
   </si>
@@ -656,250 +656,263 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:S102"/>
+  <dimension ref="A5:T102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>5225300</v>
+        <v>2482600</v>
       </c>
       <c r="E8" s="3">
-        <v>2962300</v>
+        <v>5187700</v>
       </c>
       <c r="F8" s="3">
-        <v>5515900</v>
+        <v>2941000</v>
       </c>
       <c r="G8" s="3">
-        <v>2394600</v>
+        <v>5476200</v>
       </c>
       <c r="H8" s="3">
-        <v>5082400</v>
+        <v>2377400</v>
       </c>
       <c r="I8" s="3">
-        <v>2954100</v>
+        <v>5045800</v>
       </c>
       <c r="J8" s="3">
+        <v>2932900</v>
+      </c>
+      <c r="K8" s="3">
         <v>5174200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2173500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>4572300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2586000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>4077200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1620100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>3984500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2407800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>4229100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1899000</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="3">
-        <v>2897100</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F9" s="3">
-        <v>3051600</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H9" s="3">
-        <v>2795600</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J9" s="3">
+      <c r="D9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E9" s="3">
+        <v>2876200</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G9" s="3">
+        <v>3029700</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I9" s="3">
+        <v>2775500</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K9" s="3">
         <v>2780100</v>
       </c>
-      <c r="K9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L9" s="3">
+      <c r="L9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M9" s="3">
         <v>2415700</v>
       </c>
-      <c r="M9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N9" s="3">
+      <c r="N9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O9" s="3">
         <v>2122300</v>
       </c>
-      <c r="O9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P9" s="3">
+      <c r="P9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q9" s="3">
         <v>2061000</v>
       </c>
-      <c r="Q9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R9" s="3">
+      <c r="R9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S9" s="3">
         <v>2172800</v>
       </c>
-      <c r="S9" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3">
-        <v>2328200</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F10" s="3">
-        <v>2464300</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H10" s="3">
-        <v>2286800</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J10" s="3">
+      <c r="D10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E10" s="3">
+        <v>2311500</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G10" s="3">
+        <v>2446500</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I10" s="3">
+        <v>2270300</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K10" s="3">
         <v>2394100</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L10" s="3">
+      <c r="L10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M10" s="3">
         <v>2156600</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N10" s="3">
+      <c r="N10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O10" s="3">
         <v>1954800</v>
       </c>
-      <c r="O10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P10" s="3">
+      <c r="P10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q10" s="3">
         <v>1923500</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R10" s="3">
+      <c r="R10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S10" s="3">
         <v>2056300</v>
       </c>
-      <c r="S10" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -919,8 +932,9 @@
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T11" s="3"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -972,8 +986,11 @@
       <c r="S12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1025,61 +1042,67 @@
       <c r="S13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>38200</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F14" s="3">
-        <v>24700</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H14" s="3">
-        <v>-10100</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E14" s="3">
+        <v>38000</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G14" s="3">
+        <v>24500</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I14" s="3">
+        <v>-10000</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K14" s="3">
         <v>124500</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M14" s="3">
         <v>-34900</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N14" s="3">
+      <c r="N14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O14" s="3">
         <v>28200</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P14" s="3">
+      <c r="P14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q14" s="3">
         <v>38500</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R14" s="3">
+      <c r="R14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S14" s="3">
         <v>1800</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T14" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1131,8 +1154,11 @@
       <c r="S15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1149,114 +1175,121 @@
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
-    </row>
-    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T16" s="3"/>
+    </row>
+    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3">
-        <v>4558100</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F17" s="3">
-        <v>4625100</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H17" s="3">
-        <v>4338400</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J17" s="3">
+      <c r="D17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E17" s="3">
+        <v>4525300</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G17" s="3">
+        <v>4591800</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I17" s="3">
+        <v>4307200</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K17" s="3">
         <v>4358400</v>
       </c>
-      <c r="K17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L17" s="3">
+      <c r="L17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M17" s="3">
         <v>3608300</v>
       </c>
-      <c r="M17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N17" s="3">
+      <c r="N17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O17" s="3">
         <v>3427400</v>
       </c>
-      <c r="O17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P17" s="3">
+      <c r="P17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q17" s="3">
         <v>3341200</v>
       </c>
-      <c r="Q17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R17" s="3">
+      <c r="R17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S17" s="3">
         <v>3553900</v>
       </c>
-      <c r="S17" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T17" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3">
-        <v>667200</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F18" s="3">
-        <v>890900</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H18" s="3">
-        <v>744000</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J18" s="3">
+      <c r="D18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E18" s="3">
+        <v>662400</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G18" s="3">
+        <v>884400</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I18" s="3">
+        <v>738700</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K18" s="3">
         <v>815800</v>
       </c>
-      <c r="K18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L18" s="3">
+      <c r="L18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M18" s="3">
         <v>964100</v>
       </c>
-      <c r="M18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N18" s="3">
+      <c r="N18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O18" s="3">
         <v>649700</v>
       </c>
-      <c r="O18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P18" s="3">
+      <c r="P18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q18" s="3">
         <v>643300</v>
       </c>
-      <c r="Q18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R18" s="3">
+      <c r="R18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S18" s="3">
         <v>675200</v>
       </c>
-      <c r="S18" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T18" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1276,273 +1309,289 @@
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
-    </row>
-    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T19" s="3"/>
+    </row>
+    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>-8900</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E20" s="3">
+        <v>-8800</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G20" s="3">
         <v>-1000</v>
       </c>
-      <c r="G20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H20" s="3">
-        <v>11800</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J20" s="3">
+      <c r="H20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I20" s="3">
+        <v>11700</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K20" s="3">
         <v>-38800</v>
       </c>
-      <c r="K20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L20" s="3">
+      <c r="L20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M20" s="3">
         <v>-33300</v>
       </c>
-      <c r="M20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N20" s="3">
+      <c r="N20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O20" s="3">
         <v>-1600</v>
       </c>
-      <c r="O20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P20" s="3">
+      <c r="P20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q20" s="3">
         <v>13400</v>
       </c>
-      <c r="Q20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R20" s="3">
+      <c r="R20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S20" s="3">
         <v>5300</v>
       </c>
-      <c r="S20" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T20" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E21" s="3" t="s">
-        <v>5</v>
+      <c r="E21" s="3">
+        <v>1244000</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G21" s="3" t="s">
-        <v>5</v>
+      <c r="G21" s="3">
+        <v>1167000</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J21" s="3">
+      <c r="I21" s="3">
+        <v>1357200</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K21" s="3">
         <v>1087600</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L21" s="3">
+      <c r="L21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M21" s="3">
         <v>1547400</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N21" s="3">
+      <c r="N21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O21" s="3">
         <v>926400</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P21" s="3">
+      <c r="P21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q21" s="3">
         <v>1244900</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R21" s="3">
+      <c r="R21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S21" s="3">
         <v>1000600</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T21" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>65800</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F22" s="3">
-        <v>47400</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H22" s="3">
-        <v>41700</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J22" s="3">
+      <c r="D22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E22" s="3">
+        <v>65400</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G22" s="3">
+        <v>47100</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I22" s="3">
+        <v>41400</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K22" s="3">
         <v>37100</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L22" s="3">
+      <c r="L22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M22" s="3">
         <v>37100</v>
       </c>
-      <c r="M22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N22" s="3">
+      <c r="N22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O22" s="3">
         <v>36000</v>
       </c>
-      <c r="O22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P22" s="3">
+      <c r="P22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q22" s="3">
         <v>34900</v>
       </c>
-      <c r="Q22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R22" s="3">
+      <c r="R22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S22" s="3">
         <v>34500</v>
       </c>
-      <c r="S22" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T22" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3">
-        <v>592500</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F23" s="3">
-        <v>842400</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H23" s="3">
-        <v>714100</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J23" s="3">
+      <c r="D23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E23" s="3">
+        <v>588200</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G23" s="3">
+        <v>836300</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I23" s="3">
+        <v>708900</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K23" s="3">
         <v>739900</v>
       </c>
-      <c r="K23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L23" s="3">
+      <c r="L23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M23" s="3">
         <v>893700</v>
       </c>
-      <c r="M23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N23" s="3">
+      <c r="N23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O23" s="3">
         <v>612200</v>
       </c>
-      <c r="O23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P23" s="3">
+      <c r="P23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q23" s="3">
         <v>621900</v>
       </c>
-      <c r="Q23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R23" s="3">
+      <c r="R23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S23" s="3">
         <v>646000</v>
       </c>
-      <c r="S23" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T23" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>94400</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F24" s="3">
-        <v>176900</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H24" s="3">
-        <v>96800</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J24" s="3">
+      <c r="D24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E24" s="3">
+        <v>93800</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G24" s="3">
+        <v>175600</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I24" s="3">
+        <v>96100</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K24" s="3">
         <v>162800</v>
       </c>
-      <c r="K24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L24" s="3">
+      <c r="L24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M24" s="3">
         <v>152500</v>
       </c>
-      <c r="M24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N24" s="3">
+      <c r="N24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O24" s="3">
         <v>157300</v>
       </c>
-      <c r="O24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P24" s="3">
+      <c r="P24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q24" s="3">
         <v>145900</v>
       </c>
-      <c r="Q24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R24" s="3">
+      <c r="R24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S24" s="3">
         <v>168000</v>
       </c>
-      <c r="S24" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T24" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1594,114 +1643,123 @@
       <c r="S25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3">
-        <v>498000</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F26" s="3">
-        <v>665500</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H26" s="3">
-        <v>617300</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J26" s="3">
+      <c r="D26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E26" s="3">
+        <v>494500</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G26" s="3">
+        <v>660700</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I26" s="3">
+        <v>612900</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K26" s="3">
         <v>577200</v>
       </c>
-      <c r="K26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L26" s="3">
+      <c r="L26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M26" s="3">
         <v>741200</v>
       </c>
-      <c r="M26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N26" s="3">
+      <c r="N26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O26" s="3">
         <v>454900</v>
       </c>
-      <c r="O26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P26" s="3">
+      <c r="P26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q26" s="3">
         <v>476000</v>
       </c>
-      <c r="Q26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R26" s="3">
+      <c r="R26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S26" s="3">
         <v>478100</v>
       </c>
-      <c r="S26" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T26" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3">
-        <v>446800</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F27" s="3">
-        <v>569100</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H27" s="3">
-        <v>535700</v>
-      </c>
-      <c r="I27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J27" s="3">
+      <c r="D27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E27" s="3">
+        <v>443600</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G27" s="3">
+        <v>565000</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I27" s="3">
+        <v>531900</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K27" s="3">
         <v>487800</v>
       </c>
-      <c r="K27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L27" s="3">
+      <c r="L27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M27" s="3">
         <v>642700</v>
       </c>
-      <c r="M27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N27" s="3">
+      <c r="N27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O27" s="3">
         <v>385800</v>
       </c>
-      <c r="O27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P27" s="3">
+      <c r="P27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q27" s="3">
         <v>425800</v>
       </c>
-      <c r="Q27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R27" s="3">
+      <c r="R27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S27" s="3">
         <v>418800</v>
       </c>
-      <c r="S27" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T27" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1753,52 +1811,55 @@
       <c r="S28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3">
-        <v>-6910800</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F29" s="3">
-        <v>-59000</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H29" s="3">
-        <v>79300</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J29" s="3">
+      <c r="D29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E29" s="3">
+        <v>-6861100</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G29" s="3">
+        <v>-58500</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I29" s="3">
+        <v>78700</v>
+      </c>
+      <c r="J29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K29" s="3">
         <v>-1258000</v>
       </c>
-      <c r="K29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L29" s="3">
+      <c r="L29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M29" s="3">
         <v>-87000</v>
       </c>
-      <c r="M29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N29" s="3">
+      <c r="N29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O29" s="3">
         <v>44700</v>
       </c>
-      <c r="O29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q29" s="3">
-        <v>0</v>
+      <c r="Q29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R29" s="3">
         <v>0</v>
@@ -1806,8 +1867,11 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1859,8 +1923,11 @@
       <c r="S30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1912,114 +1979,123 @@
       <c r="S31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>8900</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E32" s="3">
+        <v>8800</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G32" s="3">
         <v>1000</v>
       </c>
-      <c r="G32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H32" s="3">
-        <v>-11800</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J32" s="3">
+      <c r="H32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I32" s="3">
+        <v>-11700</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K32" s="3">
         <v>38800</v>
       </c>
-      <c r="K32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L32" s="3">
+      <c r="L32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M32" s="3">
         <v>33300</v>
       </c>
-      <c r="M32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N32" s="3">
+      <c r="N32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O32" s="3">
         <v>1600</v>
       </c>
-      <c r="O32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P32" s="3">
+      <c r="P32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-13400</v>
       </c>
-      <c r="Q32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R32" s="3">
+      <c r="R32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S32" s="3">
         <v>-5300</v>
       </c>
-      <c r="S32" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T32" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3">
-        <v>-6464000</v>
-      </c>
-      <c r="E33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F33" s="3">
-        <v>510200</v>
-      </c>
-      <c r="G33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H33" s="3">
-        <v>615000</v>
-      </c>
-      <c r="I33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J33" s="3">
+      <c r="D33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-6417500</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G33" s="3">
+        <v>506500</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I33" s="3">
+        <v>610500</v>
+      </c>
+      <c r="J33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K33" s="3">
         <v>-770100</v>
       </c>
-      <c r="K33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L33" s="3">
+      <c r="L33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M33" s="3">
         <v>555700</v>
       </c>
-      <c r="M33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N33" s="3">
+      <c r="N33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O33" s="3">
         <v>430400</v>
       </c>
-      <c r="O33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P33" s="3">
+      <c r="P33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q33" s="3">
         <v>425800</v>
       </c>
-      <c r="Q33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R33" s="3">
+      <c r="R33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S33" s="3">
         <v>418800</v>
       </c>
-      <c r="S33" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T33" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2071,119 +2147,128 @@
       <c r="S34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3">
-        <v>-6464000</v>
-      </c>
-      <c r="E35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F35" s="3">
-        <v>510200</v>
-      </c>
-      <c r="G35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H35" s="3">
-        <v>615000</v>
-      </c>
-      <c r="I35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J35" s="3">
+      <c r="D35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-6417500</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G35" s="3">
+        <v>506500</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I35" s="3">
+        <v>610500</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K35" s="3">
         <v>-770100</v>
       </c>
-      <c r="K35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L35" s="3">
+      <c r="L35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M35" s="3">
         <v>555700</v>
       </c>
-      <c r="M35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N35" s="3">
+      <c r="N35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O35" s="3">
         <v>430400</v>
       </c>
-      <c r="O35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P35" s="3">
+      <c r="P35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q35" s="3">
         <v>425800</v>
       </c>
-      <c r="Q35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R35" s="3">
+      <c r="R35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S35" s="3">
         <v>418800</v>
       </c>
-      <c r="S35" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T35" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2203,8 +2288,9 @@
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
-    </row>
-    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T39" s="3"/>
+    </row>
+    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2224,28 +2310,29 @@
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
-    </row>
-    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T40" s="3"/>
+    </row>
+    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>1953400</v>
+        <v>1939300</v>
       </c>
       <c r="E41" s="3">
-        <v>1640300</v>
+        <v>1628500</v>
       </c>
       <c r="F41" s="3">
-        <v>1191600</v>
+        <v>1183000</v>
       </c>
       <c r="G41" s="3">
-        <v>1939500</v>
+        <v>1925600</v>
       </c>
       <c r="H41" s="3">
-        <v>1218000</v>
-      </c>
-      <c r="I41" s="3">
-        <v>1222600</v>
+        <v>1209200</v>
+      </c>
+      <c r="I41" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J41" s="3" t="s">
         <v>5</v>
@@ -2277,13 +2364,16 @@
       <c r="S41" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T41" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>326400</v>
+        <v>324000</v>
       </c>
       <c r="E42" s="3" t="s">
         <v>5</v>
@@ -2303,8 +2393,8 @@
       <c r="J42" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K42" s="3">
-        <v>0</v>
+      <c r="K42" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L42" s="3">
         <v>0</v>
@@ -2330,28 +2420,31 @@
       <c r="S42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>1158100</v>
+        <v>1149800</v>
       </c>
       <c r="E43" s="3">
-        <v>1790600</v>
+        <v>1777700</v>
       </c>
       <c r="F43" s="3">
-        <v>1136500</v>
+        <v>1128300</v>
       </c>
       <c r="G43" s="3">
-        <v>1606400</v>
+        <v>1594800</v>
       </c>
       <c r="H43" s="3">
-        <v>1202200</v>
-      </c>
-      <c r="I43" s="3">
-        <v>1579200</v>
+        <v>1193600</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J43" s="3" t="s">
         <v>5</v>
@@ -2383,28 +2476,31 @@
       <c r="S43" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T43" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>848200</v>
+        <v>842100</v>
       </c>
       <c r="E44" s="3">
-        <v>978000</v>
+        <v>971000</v>
       </c>
       <c r="F44" s="3">
-        <v>834700</v>
+        <v>828700</v>
       </c>
       <c r="G44" s="3">
-        <v>828200</v>
+        <v>822300</v>
       </c>
       <c r="H44" s="3">
-        <v>786900</v>
-      </c>
-      <c r="I44" s="3">
-        <v>796300</v>
+        <v>781300</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J44" s="3" t="s">
         <v>5</v>
@@ -2436,25 +2532,28 @@
       <c r="S44" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T44" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>121900</v>
+        <v>121000</v>
       </c>
       <c r="E45" s="3">
-        <v>1472100</v>
+        <v>1461500</v>
       </c>
       <c r="F45" s="3">
-        <v>1836600</v>
+        <v>1823400</v>
       </c>
       <c r="G45" s="3">
-        <v>2411900</v>
+        <v>2394500</v>
       </c>
       <c r="H45" s="3">
-        <v>135600</v>
+        <v>134600</v>
       </c>
       <c r="I45" s="3" t="s">
         <v>5</v>
@@ -2489,28 +2588,31 @@
       <c r="S45" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T45" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>4408000</v>
+        <v>4376300</v>
       </c>
       <c r="E46" s="3">
-        <v>5881000</v>
+        <v>5838700</v>
       </c>
       <c r="F46" s="3">
-        <v>4999300</v>
+        <v>4963400</v>
       </c>
       <c r="G46" s="3">
-        <v>6786000</v>
+        <v>6737200</v>
       </c>
       <c r="H46" s="3">
-        <v>3342700</v>
-      </c>
-      <c r="I46" s="3">
-        <v>3598200</v>
+        <v>3318700</v>
+      </c>
+      <c r="I46" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J46" s="3" t="s">
         <v>5</v>
@@ -2542,28 +2644,31 @@
       <c r="S46" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T46" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>922200</v>
+        <v>915600</v>
       </c>
       <c r="E47" s="3">
-        <v>1181900</v>
+        <v>1173400</v>
       </c>
       <c r="F47" s="3">
-        <v>942800</v>
+        <v>936000</v>
       </c>
       <c r="G47" s="3">
-        <v>1147200</v>
+        <v>1138900</v>
       </c>
       <c r="H47" s="3">
-        <v>911900</v>
-      </c>
-      <c r="I47" s="3">
-        <v>989500</v>
+        <v>905300</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J47" s="3" t="s">
         <v>5</v>
@@ -2595,28 +2700,31 @@
       <c r="S47" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T47" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>3562400</v>
+        <v>3536800</v>
       </c>
       <c r="E48" s="3">
-        <v>3443600</v>
+        <v>3418800</v>
       </c>
       <c r="F48" s="3">
-        <v>3456400</v>
+        <v>3431600</v>
       </c>
       <c r="G48" s="3">
-        <v>3455000</v>
+        <v>3430100</v>
       </c>
       <c r="H48" s="3">
-        <v>3889800</v>
-      </c>
-      <c r="I48" s="3">
-        <v>3898900</v>
+        <v>3861800</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J48" s="3" t="s">
         <v>5</v>
@@ -2648,28 +2756,31 @@
       <c r="S48" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T48" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>7167100</v>
+        <v>7115600</v>
       </c>
       <c r="E49" s="3">
-        <v>7156800</v>
+        <v>7105300</v>
       </c>
       <c r="F49" s="3">
-        <v>7185100</v>
+        <v>7133400</v>
       </c>
       <c r="G49" s="3">
-        <v>7334700</v>
+        <v>7281900</v>
       </c>
       <c r="H49" s="3">
-        <v>9995300</v>
-      </c>
-      <c r="I49" s="3">
-        <v>9913700</v>
+        <v>9923400</v>
+      </c>
+      <c r="I49" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J49" s="3" t="s">
         <v>5</v>
@@ -2701,8 +2812,11 @@
       <c r="S49" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T49" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2754,8 +2868,11 @@
       <c r="S50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2807,25 +2924,28 @@
       <c r="S51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>264200</v>
+        <v>262300</v>
       </c>
       <c r="E52" s="3" t="s">
         <v>5</v>
       </c>
       <c r="F52" s="3">
-        <v>252700</v>
+        <v>250900</v>
       </c>
       <c r="G52" s="3" t="s">
         <v>5</v>
       </c>
       <c r="H52" s="3">
-        <v>308400</v>
+        <v>306200</v>
       </c>
       <c r="I52" s="3" t="s">
         <v>5</v>
@@ -2860,8 +2980,11 @@
       <c r="S52" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T52" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2913,28 +3036,31 @@
       <c r="S53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>16324000</v>
+        <v>16206500</v>
       </c>
       <c r="E54" s="3">
-        <v>17663200</v>
+        <v>17536200</v>
       </c>
       <c r="F54" s="3">
-        <v>16836300</v>
+        <v>16715200</v>
       </c>
       <c r="G54" s="3">
-        <v>18722800</v>
+        <v>18588200</v>
       </c>
       <c r="H54" s="3">
-        <v>18448100</v>
-      </c>
-      <c r="I54" s="3">
-        <v>18400200</v>
+        <v>18315400</v>
+      </c>
+      <c r="I54" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J54" s="3" t="s">
         <v>5</v>
@@ -2966,8 +3092,11 @@
       <c r="S54" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T54" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2987,8 +3116,9 @@
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
-    </row>
-    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T55" s="3"/>
+    </row>
+    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3008,28 +3138,29 @@
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
-    </row>
-    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T56" s="3"/>
+    </row>
+    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>3234500</v>
+        <v>3211300</v>
       </c>
       <c r="E57" s="3">
-        <v>3657100</v>
+        <v>3630800</v>
       </c>
       <c r="F57" s="3">
-        <v>3199200</v>
+        <v>3176200</v>
       </c>
       <c r="G57" s="3">
-        <v>3557700</v>
+        <v>3532100</v>
       </c>
       <c r="H57" s="3">
-        <v>3013100</v>
-      </c>
-      <c r="I57" s="3">
-        <v>3128100</v>
+        <v>2991400</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J57" s="3" t="s">
         <v>5</v>
@@ -3061,28 +3192,31 @@
       <c r="S57" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T57" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>1217100</v>
+        <v>1208300</v>
       </c>
       <c r="E58" s="3">
-        <v>1988100</v>
+        <v>1973800</v>
       </c>
       <c r="F58" s="3">
-        <v>843900</v>
+        <v>837800</v>
       </c>
       <c r="G58" s="3">
-        <v>1462500</v>
+        <v>1452000</v>
       </c>
       <c r="H58" s="3">
-        <v>900200</v>
-      </c>
-      <c r="I58" s="3">
-        <v>241400</v>
+        <v>893700</v>
+      </c>
+      <c r="I58" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J58" s="3" t="s">
         <v>5</v>
@@ -3114,28 +3248,31 @@
       <c r="S58" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T58" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>2442500</v>
+        <v>2424900</v>
       </c>
       <c r="E59" s="3">
-        <v>3218200</v>
+        <v>3195100</v>
       </c>
       <c r="F59" s="3">
-        <v>3072500</v>
+        <v>3050400</v>
       </c>
       <c r="G59" s="3">
-        <v>3468800</v>
+        <v>3443900</v>
       </c>
       <c r="H59" s="3">
-        <v>2404600</v>
-      </c>
-      <c r="I59" s="3">
-        <v>1891600</v>
+        <v>2387300</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J59" s="3" t="s">
         <v>5</v>
@@ -3167,28 +3304,31 @@
       <c r="S59" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T59" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>6894200</v>
+        <v>6844600</v>
       </c>
       <c r="E60" s="3">
-        <v>8863400</v>
+        <v>8799700</v>
       </c>
       <c r="F60" s="3">
-        <v>7115600</v>
+        <v>7064400</v>
       </c>
       <c r="G60" s="3">
-        <v>8489000</v>
+        <v>8428000</v>
       </c>
       <c r="H60" s="3">
-        <v>6317900</v>
-      </c>
-      <c r="I60" s="3">
-        <v>5261200</v>
+        <v>6272400</v>
+      </c>
+      <c r="I60" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J60" s="3" t="s">
         <v>5</v>
@@ -3220,28 +3360,31 @@
       <c r="S60" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T60" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>4490500</v>
+        <v>4458200</v>
       </c>
       <c r="E61" s="3">
-        <v>3090900</v>
+        <v>3068700</v>
       </c>
       <c r="F61" s="3">
-        <v>3337600</v>
+        <v>3313600</v>
       </c>
       <c r="G61" s="3">
-        <v>3314200</v>
+        <v>3290400</v>
       </c>
       <c r="H61" s="3">
-        <v>3321500</v>
+        <v>3297700</v>
       </c>
       <c r="I61" s="3">
-        <v>4145000</v>
+        <v>0</v>
       </c>
       <c r="J61" s="3">
         <v>0</v>
@@ -3273,28 +3416,31 @@
       <c r="S61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1180800</v>
+        <v>1172300</v>
       </c>
       <c r="E62" s="3">
-        <v>1225400</v>
+        <v>1216600</v>
       </c>
       <c r="F62" s="3">
-        <v>1314800</v>
+        <v>1305300</v>
       </c>
       <c r="G62" s="3">
-        <v>1415800</v>
+        <v>1405600</v>
       </c>
       <c r="H62" s="3">
-        <v>1691800</v>
-      </c>
-      <c r="I62" s="3">
-        <v>2402400</v>
+        <v>1679600</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J62" s="3" t="s">
         <v>5</v>
@@ -3326,8 +3472,11 @@
       <c r="S62" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T62" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3379,8 +3528,11 @@
       <c r="S63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3432,8 +3584,11 @@
       <c r="S64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3485,28 +3640,31 @@
       <c r="S65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>12932500</v>
+        <v>12839500</v>
       </c>
       <c r="E66" s="3">
-        <v>13534300</v>
+        <v>13437000</v>
       </c>
       <c r="F66" s="3">
-        <v>12179600</v>
+        <v>12092000</v>
       </c>
       <c r="G66" s="3">
-        <v>13845700</v>
+        <v>13746100</v>
       </c>
       <c r="H66" s="3">
-        <v>12034100</v>
-      </c>
-      <c r="I66" s="3">
-        <v>12446300</v>
+        <v>11947500</v>
+      </c>
+      <c r="I66" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J66" s="3" t="s">
         <v>5</v>
@@ -3538,8 +3696,11 @@
       <c r="S66" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T66" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3559,8 +3720,9 @@
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
-    </row>
-    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T67" s="3"/>
+    </row>
+    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3612,8 +3774,11 @@
       <c r="S68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3665,8 +3830,11 @@
       <c r="S69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3718,8 +3886,11 @@
       <c r="S70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3771,28 +3942,31 @@
       <c r="S71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>3402000</v>
+        <v>3377500</v>
       </c>
       <c r="E72" s="3">
-        <v>10141700</v>
+        <v>10068800</v>
       </c>
       <c r="F72" s="3">
-        <v>10331200</v>
+        <v>10256900</v>
       </c>
       <c r="G72" s="3">
-        <v>10005800</v>
+        <v>9933800</v>
       </c>
       <c r="H72" s="3">
-        <v>11510200</v>
-      </c>
-      <c r="I72" s="3">
-        <v>11280300</v>
+        <v>11427400</v>
+      </c>
+      <c r="I72" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J72" s="3" t="s">
         <v>5</v>
@@ -3824,8 +3998,11 @@
       <c r="S72" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T72" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3877,8 +4054,11 @@
       <c r="S73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3930,8 +4110,11 @@
       <c r="S74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3983,28 +4166,31 @@
       <c r="S75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>3391500</v>
+        <v>3367100</v>
       </c>
       <c r="E76" s="3">
-        <v>4128900</v>
+        <v>4099200</v>
       </c>
       <c r="F76" s="3">
-        <v>4656700</v>
+        <v>4623200</v>
       </c>
       <c r="G76" s="3">
-        <v>4877100</v>
+        <v>4842100</v>
       </c>
       <c r="H76" s="3">
-        <v>6414100</v>
-      </c>
-      <c r="I76" s="3">
-        <v>5954000</v>
+        <v>6367900</v>
+      </c>
+      <c r="I76" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J76" s="3" t="s">
         <v>5</v>
@@ -4036,8 +4222,11 @@
       <c r="S76" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T76" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4089,119 +4278,128 @@
       <c r="S77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3">
-        <v>-6464000</v>
-      </c>
-      <c r="E81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F81" s="3">
-        <v>510200</v>
-      </c>
-      <c r="G81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H81" s="3">
-        <v>615000</v>
-      </c>
-      <c r="I81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J81" s="3">
+      <c r="D81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-6417500</v>
+      </c>
+      <c r="F81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G81" s="3">
+        <v>506500</v>
+      </c>
+      <c r="H81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I81" s="3">
+        <v>610500</v>
+      </c>
+      <c r="J81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K81" s="3">
         <v>-770100</v>
       </c>
-      <c r="K81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L81" s="3">
+      <c r="L81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M81" s="3">
         <v>555700</v>
       </c>
-      <c r="M81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N81" s="3">
+      <c r="N81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O81" s="3">
         <v>430400</v>
       </c>
-      <c r="O81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P81" s="3">
+      <c r="P81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q81" s="3">
         <v>425800</v>
       </c>
-      <c r="Q81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R81" s="3">
+      <c r="R81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S81" s="3">
         <v>418800</v>
       </c>
-      <c r="S81" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T81" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4221,61 +4419,65 @@
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
-    </row>
-    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T82" s="3"/>
+    </row>
+    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E83" s="3" t="s">
-        <v>5</v>
+      <c r="E83" s="3">
+        <v>590400</v>
       </c>
       <c r="F83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G83" s="3" t="s">
-        <v>5</v>
+      <c r="G83" s="3">
+        <v>283600</v>
       </c>
       <c r="H83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J83" s="3">
+      <c r="I83" s="3">
+        <v>606800</v>
+      </c>
+      <c r="J83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K83" s="3">
         <v>310600</v>
       </c>
-      <c r="K83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L83" s="3">
+      <c r="L83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M83" s="3">
         <v>671000</v>
       </c>
-      <c r="M83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N83" s="3">
+      <c r="N83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O83" s="3">
         <v>303500</v>
       </c>
-      <c r="O83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P83" s="3">
+      <c r="P83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q83" s="3">
         <v>588200</v>
       </c>
-      <c r="Q83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R83" s="3">
+      <c r="R83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S83" s="3">
         <v>320100</v>
       </c>
-      <c r="S83" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T83" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4327,8 +4529,11 @@
       <c r="S84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4380,8 +4585,11 @@
       <c r="S85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4433,8 +4641,11 @@
       <c r="S86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4486,8 +4697,11 @@
       <c r="S87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4539,61 +4753,67 @@
       <c r="S88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E89" s="3" t="s">
-        <v>5</v>
+      <c r="E89" s="3">
+        <v>1682100</v>
       </c>
       <c r="F89" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G89" s="3" t="s">
-        <v>5</v>
+      <c r="G89" s="3">
+        <v>885200</v>
       </c>
       <c r="H89" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J89" s="3">
+      <c r="I89" s="3">
+        <v>1876600</v>
+      </c>
+      <c r="J89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K89" s="3">
         <v>1223200</v>
       </c>
-      <c r="K89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L89" s="3">
+      <c r="L89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M89" s="3">
         <v>1929200</v>
       </c>
-      <c r="M89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N89" s="3">
+      <c r="N89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O89" s="3">
         <v>950500</v>
       </c>
-      <c r="O89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P89" s="3">
+      <c r="P89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q89" s="3">
         <v>1465600</v>
       </c>
-      <c r="Q89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R89" s="3">
+      <c r="R89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S89" s="3">
         <v>749900</v>
       </c>
-      <c r="S89" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T89" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4613,8 +4833,9 @@
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
-    </row>
-    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T90" s="3"/>
+    </row>
+    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4649,25 +4870,28 @@
         <v>0</v>
       </c>
       <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3">
         <v>-235900</v>
       </c>
-      <c r="O91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P91" s="3">
+      <c r="P91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-589500</v>
       </c>
-      <c r="Q91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R91" s="3">
+      <c r="R91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S91" s="3">
         <v>-363900</v>
       </c>
-      <c r="S91" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T91" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4719,8 +4943,11 @@
       <c r="S92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4772,61 +4999,67 @@
       <c r="S93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E94" s="3" t="s">
-        <v>5</v>
+      <c r="E94" s="3">
+        <v>-975200</v>
       </c>
       <c r="F94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G94" s="3" t="s">
-        <v>5</v>
+      <c r="G94" s="3">
+        <v>-336800</v>
       </c>
       <c r="H94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J94" s="3">
+      <c r="I94" s="3">
+        <v>-444200</v>
+      </c>
+      <c r="J94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K94" s="3">
         <v>-158500</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L94" s="3">
+      <c r="L94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M94" s="3">
         <v>-591700</v>
       </c>
-      <c r="M94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N94" s="3">
+      <c r="N94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O94" s="3">
         <v>-179600</v>
       </c>
-      <c r="O94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P94" s="3">
+      <c r="P94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q94" s="3">
         <v>-787400</v>
       </c>
-      <c r="Q94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R94" s="3">
+      <c r="R94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S94" s="3">
         <v>-289100</v>
       </c>
-      <c r="S94" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T94" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4846,8 +5079,9 @@
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
-    </row>
-    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T95" s="3"/>
+    </row>
+    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4855,52 +5089,55 @@
         <v>0</v>
       </c>
       <c r="E96" s="3">
-        <v>0</v>
+        <v>-535500</v>
       </c>
       <c r="F96" s="3">
         <v>0</v>
       </c>
       <c r="G96" s="3">
-        <v>0</v>
+        <v>-535500</v>
       </c>
       <c r="H96" s="3">
         <v>0</v>
       </c>
       <c r="I96" s="3">
-        <v>0</v>
+        <v>-491100</v>
       </c>
       <c r="J96" s="3">
+        <v>0</v>
+      </c>
+      <c r="K96" s="3">
         <v>-494700</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
       <c r="L96" s="3">
+        <v>0</v>
+      </c>
+      <c r="M96" s="3">
         <v>-463700</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
       <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3">
         <v>-453200</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
       <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3">
         <v>-414800</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
-      </c>
       <c r="R96" s="3">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3">
         <v>-453700</v>
       </c>
-      <c r="S96" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4952,8 +5189,11 @@
       <c r="S97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5005,8 +5245,11 @@
       <c r="S98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5058,163 +5301,175 @@
       <c r="S99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E100" s="3" t="s">
-        <v>5</v>
+      <c r="E100" s="3">
+        <v>198500</v>
       </c>
       <c r="F100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G100" s="3" t="s">
-        <v>5</v>
+      <c r="G100" s="3">
+        <v>-43500</v>
       </c>
       <c r="H100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J100" s="3">
+      <c r="I100" s="3">
+        <v>-1443300</v>
+      </c>
+      <c r="J100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K100" s="3">
         <v>-328100</v>
       </c>
-      <c r="K100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L100" s="3">
+      <c r="L100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M100" s="3">
         <v>-1301500</v>
       </c>
-      <c r="M100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N100" s="3">
+      <c r="N100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O100" s="3">
         <v>-713100</v>
       </c>
-      <c r="O100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P100" s="3">
+      <c r="P100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q100" s="3">
         <v>-242700</v>
       </c>
-      <c r="Q100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R100" s="3">
+      <c r="R100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S100" s="3">
         <v>-73200</v>
       </c>
-      <c r="S100" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T100" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E101" s="3" t="s">
-        <v>5</v>
+      <c r="E101" s="3">
+        <v>-178100</v>
       </c>
       <c r="F101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G101" s="3" t="s">
-        <v>5</v>
+      <c r="G101" s="3">
+        <v>25900</v>
       </c>
       <c r="H101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J101" s="3">
+      <c r="I101" s="3">
+        <v>-99000</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K101" s="3">
         <v>57100</v>
       </c>
-      <c r="K101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L101" s="3">
+      <c r="L101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M101" s="3">
         <v>66600</v>
       </c>
-      <c r="M101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N101" s="3">
+      <c r="N101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O101" s="3">
         <v>22600</v>
       </c>
-      <c r="O101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P101" s="3">
+      <c r="P101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q101" s="3">
         <v>-58700</v>
       </c>
-      <c r="Q101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R101" s="3">
+      <c r="R101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S101" s="3">
         <v>-16700</v>
       </c>
-      <c r="S101" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T101" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E102" s="3" t="s">
-        <v>5</v>
+      <c r="E102" s="3">
+        <v>727400</v>
       </c>
       <c r="F102" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G102" s="3" t="s">
-        <v>5</v>
+      <c r="G102" s="3">
+        <v>530800</v>
       </c>
       <c r="H102" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J102" s="3">
+      <c r="I102" s="3">
+        <v>-109800</v>
+      </c>
+      <c r="J102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K102" s="3">
         <v>793600</v>
       </c>
-      <c r="K102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L102" s="3">
+      <c r="L102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M102" s="3">
         <v>56200</v>
       </c>
-      <c r="M102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N102" s="3">
+      <c r="N102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O102" s="3">
         <v>59400</v>
       </c>
-      <c r="O102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P102" s="3">
+      <c r="P102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q102" s="3">
         <v>376700</v>
       </c>
-      <c r="Q102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R102" s="3">
+      <c r="R102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S102" s="3">
         <v>370800</v>
       </c>
-      <c r="S102" s="3" t="s">
+      <c r="T102" s="3" t="s">
         <v>5</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CABGY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CABGY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="546" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="92">
   <si>
     <t>CABGY</t>
   </si>
@@ -656,263 +656,276 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:T102"/>
+  <dimension ref="A5:U102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>2482600</v>
+        <v>5754000</v>
       </c>
       <c r="E8" s="3">
-        <v>5187700</v>
+        <v>2542800</v>
       </c>
       <c r="F8" s="3">
-        <v>2941000</v>
+        <v>5313300</v>
       </c>
       <c r="G8" s="3">
-        <v>5476200</v>
+        <v>3012200</v>
       </c>
       <c r="H8" s="3">
-        <v>2377400</v>
+        <v>5608900</v>
       </c>
       <c r="I8" s="3">
-        <v>5045800</v>
+        <v>2435000</v>
       </c>
       <c r="J8" s="3">
+        <v>5168000</v>
+      </c>
+      <c r="K8" s="3">
         <v>2932900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>5174200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2173500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>4572300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2586000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>4077200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1620100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>3984500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2407800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>4229100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1899000</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E9" s="3">
-        <v>2876200</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G9" s="3">
-        <v>3029700</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I9" s="3">
-        <v>2775500</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K9" s="3">
+      <c r="D9" s="3">
+        <v>3090500</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F9" s="3">
+        <v>2945900</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H9" s="3">
+        <v>3103100</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J9" s="3">
+        <v>2842700</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L9" s="3">
         <v>2780100</v>
       </c>
-      <c r="L9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M9" s="3">
+      <c r="M9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N9" s="3">
         <v>2415700</v>
       </c>
-      <c r="N9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O9" s="3">
+      <c r="O9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P9" s="3">
         <v>2122300</v>
       </c>
-      <c r="P9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q9" s="3">
+      <c r="Q9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R9" s="3">
         <v>2061000</v>
       </c>
-      <c r="R9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S9" s="3">
+      <c r="S9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T9" s="3">
         <v>2172800</v>
       </c>
-      <c r="T9" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E10" s="3">
-        <v>2311500</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G10" s="3">
-        <v>2446500</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I10" s="3">
-        <v>2270300</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K10" s="3">
+      <c r="D10" s="3">
+        <v>2663600</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F10" s="3">
+        <v>2367500</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H10" s="3">
+        <v>2505800</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J10" s="3">
+        <v>2325300</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L10" s="3">
         <v>2394100</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M10" s="3">
+      <c r="M10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N10" s="3">
         <v>2156600</v>
       </c>
-      <c r="N10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O10" s="3">
+      <c r="O10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P10" s="3">
         <v>1954800</v>
       </c>
-      <c r="P10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q10" s="3">
+      <c r="Q10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R10" s="3">
         <v>1923500</v>
       </c>
-      <c r="R10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S10" s="3">
+      <c r="S10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T10" s="3">
         <v>2056300</v>
       </c>
-      <c r="T10" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -933,8 +946,9 @@
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U11" s="3"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -989,8 +1003,11 @@
       <c r="T12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1045,64 +1062,70 @@
       <c r="T13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E14" s="3">
-        <v>38000</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G14" s="3">
-        <v>24500</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I14" s="3">
-        <v>-10000</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K14" s="3">
+      <c r="D14" s="3">
+        <v>20600</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F14" s="3">
+        <v>38900</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H14" s="3">
+        <v>25100</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J14" s="3">
+        <v>-10200</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L14" s="3">
         <v>124500</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M14" s="3">
+      <c r="M14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N14" s="3">
         <v>-34900</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O14" s="3">
+      <c r="O14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P14" s="3">
         <v>28200</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q14" s="3">
+      <c r="Q14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R14" s="3">
         <v>38500</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S14" s="3">
+      <c r="S14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T14" s="3">
         <v>1800</v>
       </c>
-      <c r="T14" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U14" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1157,8 +1180,11 @@
       <c r="T15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1176,120 +1202,127 @@
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
-    </row>
-    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U16" s="3"/>
+    </row>
+    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E17" s="3">
-        <v>4525300</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G17" s="3">
-        <v>4591800</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I17" s="3">
-        <v>4307200</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K17" s="3">
+      <c r="D17" s="3">
+        <v>4834200</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F17" s="3">
+        <v>4634900</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H17" s="3">
+        <v>4703000</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J17" s="3">
+        <v>4411500</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L17" s="3">
         <v>4358400</v>
       </c>
-      <c r="L17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M17" s="3">
+      <c r="M17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N17" s="3">
         <v>3608300</v>
       </c>
-      <c r="N17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O17" s="3">
+      <c r="O17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P17" s="3">
         <v>3427400</v>
       </c>
-      <c r="P17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q17" s="3">
+      <c r="Q17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R17" s="3">
         <v>3341200</v>
       </c>
-      <c r="R17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S17" s="3">
+      <c r="S17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T17" s="3">
         <v>3553900</v>
       </c>
-      <c r="T17" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U17" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E18" s="3">
-        <v>662400</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G18" s="3">
-        <v>884400</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I18" s="3">
-        <v>738700</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K18" s="3">
+      <c r="D18" s="3">
+        <v>919800</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F18" s="3">
+        <v>678500</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H18" s="3">
+        <v>905900</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J18" s="3">
+        <v>756500</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L18" s="3">
         <v>815800</v>
       </c>
-      <c r="L18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M18" s="3">
+      <c r="M18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N18" s="3">
         <v>964100</v>
       </c>
-      <c r="N18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O18" s="3">
+      <c r="O18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P18" s="3">
         <v>649700</v>
       </c>
-      <c r="P18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q18" s="3">
+      <c r="Q18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R18" s="3">
         <v>643300</v>
       </c>
-      <c r="R18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S18" s="3">
+      <c r="S18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T18" s="3">
         <v>675200</v>
       </c>
-      <c r="T18" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U18" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1310,288 +1343,304 @@
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
-    </row>
-    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U19" s="3"/>
+    </row>
+    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E20" s="3">
-        <v>-8800</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G20" s="3">
+      <c r="D20" s="3">
         <v>-1000</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I20" s="3">
-        <v>11700</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K20" s="3">
+      <c r="E20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F20" s="3">
+        <v>-9100</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H20" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J20" s="3">
+        <v>12000</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L20" s="3">
         <v>-38800</v>
       </c>
-      <c r="L20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M20" s="3">
+      <c r="M20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N20" s="3">
         <v>-33300</v>
       </c>
-      <c r="N20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O20" s="3">
+      <c r="O20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P20" s="3">
         <v>-1600</v>
       </c>
-      <c r="P20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q20" s="3">
+      <c r="Q20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R20" s="3">
         <v>13400</v>
       </c>
-      <c r="R20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S20" s="3">
+      <c r="S20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T20" s="3">
         <v>5300</v>
       </c>
-      <c r="T20" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U20" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E21" s="3">
-        <v>1244000</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G21" s="3">
-        <v>1167000</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I21" s="3">
-        <v>1357200</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K21" s="3">
+      <c r="D21" s="3">
+        <v>1218500</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F21" s="3">
+        <v>1274100</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H21" s="3">
+        <v>1195300</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J21" s="3">
+        <v>1390000</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L21" s="3">
         <v>1087600</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M21" s="3">
+      <c r="M21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N21" s="3">
         <v>1547400</v>
       </c>
-      <c r="N21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O21" s="3">
+      <c r="O21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P21" s="3">
         <v>926400</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q21" s="3">
+      <c r="Q21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R21" s="3">
         <v>1244900</v>
       </c>
-      <c r="R21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S21" s="3">
+      <c r="S21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T21" s="3">
         <v>1000600</v>
       </c>
-      <c r="T21" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U21" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E22" s="3">
-        <v>65400</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G22" s="3">
-        <v>47100</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I22" s="3">
-        <v>41400</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K22" s="3">
+      <c r="D22" s="3">
+        <v>80600</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F22" s="3">
+        <v>66900</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H22" s="3">
+        <v>48200</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J22" s="3">
+        <v>42500</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L22" s="3">
         <v>37100</v>
       </c>
-      <c r="L22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M22" s="3">
+      <c r="M22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N22" s="3">
         <v>37100</v>
       </c>
-      <c r="N22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O22" s="3">
+      <c r="O22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P22" s="3">
         <v>36000</v>
       </c>
-      <c r="P22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q22" s="3">
+      <c r="Q22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R22" s="3">
         <v>34900</v>
       </c>
-      <c r="R22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S22" s="3">
+      <c r="S22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T22" s="3">
         <v>34500</v>
       </c>
-      <c r="T22" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U22" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E23" s="3">
-        <v>588200</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G23" s="3">
-        <v>836300</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I23" s="3">
-        <v>708900</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K23" s="3">
+      <c r="D23" s="3">
+        <v>838200</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F23" s="3">
+        <v>602500</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H23" s="3">
+        <v>856600</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J23" s="3">
+        <v>726100</v>
+      </c>
+      <c r="K23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L23" s="3">
         <v>739900</v>
       </c>
-      <c r="L23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M23" s="3">
+      <c r="M23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N23" s="3">
         <v>893700</v>
       </c>
-      <c r="N23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O23" s="3">
+      <c r="O23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P23" s="3">
         <v>612200</v>
       </c>
-      <c r="P23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q23" s="3">
+      <c r="Q23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R23" s="3">
         <v>621900</v>
       </c>
-      <c r="R23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S23" s="3">
+      <c r="S23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T23" s="3">
         <v>646000</v>
       </c>
-      <c r="T23" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U23" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E24" s="3">
-        <v>93800</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G24" s="3">
-        <v>175600</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I24" s="3">
-        <v>96100</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K24" s="3">
+      <c r="D24" s="3">
+        <v>178000</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F24" s="3">
+        <v>96000</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H24" s="3">
+        <v>179900</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J24" s="3">
+        <v>98400</v>
+      </c>
+      <c r="K24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L24" s="3">
         <v>162800</v>
       </c>
-      <c r="L24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M24" s="3">
+      <c r="M24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N24" s="3">
         <v>152500</v>
       </c>
-      <c r="N24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O24" s="3">
+      <c r="O24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P24" s="3">
         <v>157300</v>
       </c>
-      <c r="P24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q24" s="3">
+      <c r="Q24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R24" s="3">
         <v>145900</v>
       </c>
-      <c r="R24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S24" s="3">
+      <c r="S24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T24" s="3">
         <v>168000</v>
       </c>
-      <c r="T24" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U24" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1646,120 +1695,129 @@
       <c r="T25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E26" s="3">
-        <v>494500</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G26" s="3">
-        <v>660700</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I26" s="3">
-        <v>612900</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K26" s="3">
+      <c r="D26" s="3">
+        <v>660200</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F26" s="3">
+        <v>506400</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H26" s="3">
+        <v>676700</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J26" s="3">
+        <v>627700</v>
+      </c>
+      <c r="K26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L26" s="3">
         <v>577200</v>
       </c>
-      <c r="L26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M26" s="3">
+      <c r="M26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N26" s="3">
         <v>741200</v>
       </c>
-      <c r="N26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O26" s="3">
+      <c r="O26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P26" s="3">
         <v>454900</v>
       </c>
-      <c r="P26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q26" s="3">
+      <c r="Q26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R26" s="3">
         <v>476000</v>
       </c>
-      <c r="R26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S26" s="3">
+      <c r="S26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T26" s="3">
         <v>478100</v>
       </c>
-      <c r="T26" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U26" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E27" s="3">
-        <v>443600</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G27" s="3">
-        <v>565000</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I27" s="3">
-        <v>531900</v>
-      </c>
-      <c r="J27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K27" s="3">
+      <c r="D27" s="3">
+        <v>554700</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F27" s="3">
+        <v>454300</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H27" s="3">
+        <v>578700</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J27" s="3">
+        <v>544700</v>
+      </c>
+      <c r="K27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L27" s="3">
         <v>487800</v>
       </c>
-      <c r="L27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M27" s="3">
+      <c r="M27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N27" s="3">
         <v>642700</v>
       </c>
-      <c r="N27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O27" s="3">
+      <c r="O27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P27" s="3">
         <v>385800</v>
       </c>
-      <c r="P27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q27" s="3">
+      <c r="Q27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R27" s="3">
         <v>425800</v>
       </c>
-      <c r="R27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S27" s="3">
+      <c r="S27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T27" s="3">
         <v>418800</v>
       </c>
-      <c r="T27" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U27" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1814,55 +1872,58 @@
       <c r="T28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E29" s="3">
-        <v>-6861100</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G29" s="3">
-        <v>-58500</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I29" s="3">
-        <v>78700</v>
-      </c>
-      <c r="J29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K29" s="3">
+      <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F29" s="3">
+        <v>-7027300</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H29" s="3">
+        <v>-60000</v>
+      </c>
+      <c r="I29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J29" s="3">
+        <v>80600</v>
+      </c>
+      <c r="K29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L29" s="3">
         <v>-1258000</v>
       </c>
-      <c r="L29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M29" s="3">
+      <c r="M29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N29" s="3">
         <v>-87000</v>
       </c>
-      <c r="N29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O29" s="3">
+      <c r="O29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P29" s="3">
         <v>44700</v>
       </c>
-      <c r="P29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R29" s="3">
-        <v>0</v>
+      <c r="R29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="S29" s="3">
         <v>0</v>
@@ -1870,8 +1931,11 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1926,8 +1990,11 @@
       <c r="T30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1982,120 +2049,129 @@
       <c r="T31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E32" s="3">
-        <v>8800</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G32" s="3">
+      <c r="D32" s="3">
         <v>1000</v>
       </c>
-      <c r="H32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I32" s="3">
-        <v>-11700</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K32" s="3">
+      <c r="E32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F32" s="3">
+        <v>9100</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H32" s="3">
+        <v>1000</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J32" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="K32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L32" s="3">
         <v>38800</v>
       </c>
-      <c r="L32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M32" s="3">
+      <c r="M32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N32" s="3">
         <v>33300</v>
       </c>
-      <c r="N32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O32" s="3">
+      <c r="O32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P32" s="3">
         <v>1600</v>
       </c>
-      <c r="P32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q32" s="3">
+      <c r="Q32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R32" s="3">
         <v>-13400</v>
       </c>
-      <c r="R32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S32" s="3">
+      <c r="S32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T32" s="3">
         <v>-5300</v>
       </c>
-      <c r="T32" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U32" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E33" s="3">
-        <v>-6417500</v>
-      </c>
-      <c r="F33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G33" s="3">
-        <v>506500</v>
-      </c>
-      <c r="H33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I33" s="3">
-        <v>610500</v>
-      </c>
-      <c r="J33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K33" s="3">
+      <c r="D33" s="3">
+        <v>554700</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F33" s="3">
+        <v>-6572900</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H33" s="3">
+        <v>518800</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J33" s="3">
+        <v>625300</v>
+      </c>
+      <c r="K33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L33" s="3">
         <v>-770100</v>
       </c>
-      <c r="L33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M33" s="3">
+      <c r="M33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N33" s="3">
         <v>555700</v>
       </c>
-      <c r="N33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O33" s="3">
+      <c r="O33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P33" s="3">
         <v>430400</v>
       </c>
-      <c r="P33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q33" s="3">
+      <c r="Q33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R33" s="3">
         <v>425800</v>
       </c>
-      <c r="R33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S33" s="3">
+      <c r="S33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T33" s="3">
         <v>418800</v>
       </c>
-      <c r="T33" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U33" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2150,125 +2226,134 @@
       <c r="T34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E35" s="3">
-        <v>-6417500</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G35" s="3">
-        <v>506500</v>
-      </c>
-      <c r="H35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I35" s="3">
-        <v>610500</v>
-      </c>
-      <c r="J35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K35" s="3">
+      <c r="D35" s="3">
+        <v>554700</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F35" s="3">
+        <v>-6572900</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H35" s="3">
+        <v>518800</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J35" s="3">
+        <v>625300</v>
+      </c>
+      <c r="K35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L35" s="3">
         <v>-770100</v>
       </c>
-      <c r="L35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M35" s="3">
+      <c r="M35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N35" s="3">
         <v>555700</v>
       </c>
-      <c r="N35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O35" s="3">
+      <c r="O35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P35" s="3">
         <v>430400</v>
       </c>
-      <c r="P35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q35" s="3">
+      <c r="Q35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R35" s="3">
         <v>425800</v>
       </c>
-      <c r="R35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S35" s="3">
+      <c r="S35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T35" s="3">
         <v>418800</v>
       </c>
-      <c r="T35" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U35" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2289,8 +2374,9 @@
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
-    </row>
-    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U39" s="3"/>
+    </row>
+    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2311,28 +2397,29 @@
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
-    </row>
-    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U40" s="3"/>
+    </row>
+    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>1939300</v>
+        <v>1589500</v>
       </c>
       <c r="E41" s="3">
-        <v>1628500</v>
+        <v>1986300</v>
       </c>
       <c r="F41" s="3">
-        <v>1183000</v>
+        <v>1667900</v>
       </c>
       <c r="G41" s="3">
-        <v>1925600</v>
+        <v>1211600</v>
       </c>
       <c r="H41" s="3">
-        <v>1209200</v>
-      </c>
-      <c r="I41" s="3" t="s">
-        <v>5</v>
+        <v>1972200</v>
+      </c>
+      <c r="I41" s="3">
+        <v>1238500</v>
       </c>
       <c r="J41" s="3" t="s">
         <v>5</v>
@@ -2367,16 +2454,19 @@
       <c r="T41" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U41" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>324000</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>5</v>
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
+        <v>331900</v>
       </c>
       <c r="F42" s="3" t="s">
         <v>5</v>
@@ -2396,8 +2486,8 @@
       <c r="K42" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L42" s="3">
-        <v>0</v>
+      <c r="L42" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M42" s="3">
         <v>0</v>
@@ -2423,28 +2513,31 @@
       <c r="T42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>1149800</v>
+        <v>1823300</v>
       </c>
       <c r="E43" s="3">
-        <v>1777700</v>
+        <v>1177600</v>
       </c>
       <c r="F43" s="3">
-        <v>1128300</v>
+        <v>1820800</v>
       </c>
       <c r="G43" s="3">
-        <v>1594800</v>
+        <v>1155700</v>
       </c>
       <c r="H43" s="3">
-        <v>1193600</v>
-      </c>
-      <c r="I43" s="3" t="s">
-        <v>5</v>
+        <v>1633500</v>
+      </c>
+      <c r="I43" s="3">
+        <v>1222500</v>
       </c>
       <c r="J43" s="3" t="s">
         <v>5</v>
@@ -2479,28 +2572,31 @@
       <c r="T43" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U43" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>842100</v>
+        <v>967900</v>
       </c>
       <c r="E44" s="3">
-        <v>971000</v>
+        <v>862500</v>
       </c>
       <c r="F44" s="3">
-        <v>828700</v>
+        <v>994500</v>
       </c>
       <c r="G44" s="3">
-        <v>822300</v>
+        <v>848700</v>
       </c>
       <c r="H44" s="3">
-        <v>781300</v>
-      </c>
-      <c r="I44" s="3" t="s">
-        <v>5</v>
+        <v>842200</v>
+      </c>
+      <c r="I44" s="3">
+        <v>800200</v>
       </c>
       <c r="J44" s="3" t="s">
         <v>5</v>
@@ -2535,28 +2631,31 @@
       <c r="T44" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U44" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>121000</v>
+        <v>0</v>
       </c>
       <c r="E45" s="3">
-        <v>1461500</v>
+        <v>123900</v>
       </c>
       <c r="F45" s="3">
-        <v>1823400</v>
+        <v>1496900</v>
       </c>
       <c r="G45" s="3">
-        <v>2394500</v>
+        <v>1867500</v>
       </c>
       <c r="H45" s="3">
-        <v>134600</v>
-      </c>
-      <c r="I45" s="3" t="s">
-        <v>5</v>
+        <v>2452500</v>
+      </c>
+      <c r="I45" s="3">
+        <v>137900</v>
       </c>
       <c r="J45" s="3" t="s">
         <v>5</v>
@@ -2591,28 +2690,31 @@
       <c r="T45" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U45" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>4376300</v>
+        <v>4380800</v>
       </c>
       <c r="E46" s="3">
-        <v>5838700</v>
+        <v>4482300</v>
       </c>
       <c r="F46" s="3">
-        <v>4963400</v>
+        <v>5980100</v>
       </c>
       <c r="G46" s="3">
-        <v>6737200</v>
+        <v>5083600</v>
       </c>
       <c r="H46" s="3">
-        <v>3318700</v>
-      </c>
-      <c r="I46" s="3" t="s">
-        <v>5</v>
+        <v>6900400</v>
+      </c>
+      <c r="I46" s="3">
+        <v>3399000</v>
       </c>
       <c r="J46" s="3" t="s">
         <v>5</v>
@@ -2647,28 +2749,31 @@
       <c r="T46" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U46" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>915600</v>
+        <v>1257800</v>
       </c>
       <c r="E47" s="3">
-        <v>1173400</v>
+        <v>937800</v>
       </c>
       <c r="F47" s="3">
-        <v>936000</v>
+        <v>1201800</v>
       </c>
       <c r="G47" s="3">
-        <v>1138900</v>
+        <v>958700</v>
       </c>
       <c r="H47" s="3">
-        <v>905300</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>5</v>
+        <v>1166500</v>
+      </c>
+      <c r="I47" s="3">
+        <v>927200</v>
       </c>
       <c r="J47" s="3" t="s">
         <v>5</v>
@@ -2703,28 +2808,31 @@
       <c r="T47" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U47" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>3536800</v>
+        <v>3722200</v>
       </c>
       <c r="E48" s="3">
-        <v>3418800</v>
+        <v>3622400</v>
       </c>
       <c r="F48" s="3">
-        <v>3431600</v>
+        <v>3501600</v>
       </c>
       <c r="G48" s="3">
-        <v>3430100</v>
+        <v>3514700</v>
       </c>
       <c r="H48" s="3">
-        <v>3861800</v>
-      </c>
-      <c r="I48" s="3" t="s">
-        <v>5</v>
+        <v>3513200</v>
+      </c>
+      <c r="I48" s="3">
+        <v>3955400</v>
       </c>
       <c r="J48" s="3" t="s">
         <v>5</v>
@@ -2759,28 +2867,31 @@
       <c r="T48" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U48" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>7115600</v>
+        <v>7304100</v>
       </c>
       <c r="E49" s="3">
-        <v>7105300</v>
+        <v>7287900</v>
       </c>
       <c r="F49" s="3">
-        <v>7133400</v>
+        <v>7277400</v>
       </c>
       <c r="G49" s="3">
-        <v>7281900</v>
+        <v>7306200</v>
       </c>
       <c r="H49" s="3">
-        <v>9923400</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>5</v>
+        <v>7458300</v>
+      </c>
+      <c r="I49" s="3">
+        <v>10163700</v>
       </c>
       <c r="J49" s="3" t="s">
         <v>5</v>
@@ -2815,8 +2926,11 @@
       <c r="T49" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U49" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2871,8 +2985,11 @@
       <c r="T50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2927,28 +3044,31 @@
       <c r="T51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
-        <v>262300</v>
-      </c>
-      <c r="E52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F52" s="3">
-        <v>250900</v>
-      </c>
-      <c r="G52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H52" s="3">
-        <v>306200</v>
-      </c>
-      <c r="I52" s="3" t="s">
-        <v>5</v>
+      <c r="D52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E52" s="3">
+        <v>268700</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G52" s="3">
+        <v>256900</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I52" s="3">
+        <v>313600</v>
       </c>
       <c r="J52" s="3" t="s">
         <v>5</v>
@@ -2983,8 +3103,11 @@
       <c r="T52" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U52" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3039,28 +3162,31 @@
       <c r="T53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>16206500</v>
+        <v>16664800</v>
       </c>
       <c r="E54" s="3">
-        <v>17536200</v>
+        <v>16599100</v>
       </c>
       <c r="F54" s="3">
-        <v>16715200</v>
+        <v>17960900</v>
       </c>
       <c r="G54" s="3">
-        <v>18588200</v>
+        <v>17120100</v>
       </c>
       <c r="H54" s="3">
-        <v>18315400</v>
-      </c>
-      <c r="I54" s="3" t="s">
-        <v>5</v>
+        <v>19038400</v>
+      </c>
+      <c r="I54" s="3">
+        <v>18759000</v>
       </c>
       <c r="J54" s="3" t="s">
         <v>5</v>
@@ -3095,8 +3221,11 @@
       <c r="T54" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U54" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3117,8 +3246,9 @@
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
-    </row>
-    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U55" s="3"/>
+    </row>
+    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3139,28 +3269,29 @@
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
-    </row>
-    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U56" s="3"/>
+    </row>
+    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>3211300</v>
+        <v>3829900</v>
       </c>
       <c r="E57" s="3">
-        <v>3630800</v>
+        <v>3289100</v>
       </c>
       <c r="F57" s="3">
-        <v>3176200</v>
+        <v>3718800</v>
       </c>
       <c r="G57" s="3">
-        <v>3532100</v>
+        <v>3253100</v>
       </c>
       <c r="H57" s="3">
-        <v>2991400</v>
-      </c>
-      <c r="I57" s="3" t="s">
-        <v>5</v>
+        <v>3617700</v>
+      </c>
+      <c r="I57" s="3">
+        <v>3063900</v>
       </c>
       <c r="J57" s="3" t="s">
         <v>5</v>
@@ -3195,28 +3326,31 @@
       <c r="T57" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U57" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>1208300</v>
+        <v>932700</v>
       </c>
       <c r="E58" s="3">
-        <v>1973800</v>
+        <v>1237600</v>
       </c>
       <c r="F58" s="3">
-        <v>837800</v>
+        <v>2021600</v>
       </c>
       <c r="G58" s="3">
-        <v>1452000</v>
+        <v>858100</v>
       </c>
       <c r="H58" s="3">
-        <v>893700</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>5</v>
+        <v>1487100</v>
+      </c>
+      <c r="I58" s="3">
+        <v>915400</v>
       </c>
       <c r="J58" s="3" t="s">
         <v>5</v>
@@ -3251,28 +3385,31 @@
       <c r="T58" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U58" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>2424900</v>
+        <v>2619600</v>
       </c>
       <c r="E59" s="3">
-        <v>3195100</v>
+        <v>2483700</v>
       </c>
       <c r="F59" s="3">
-        <v>3050400</v>
+        <v>3272400</v>
       </c>
       <c r="G59" s="3">
-        <v>3443900</v>
+        <v>3124300</v>
       </c>
       <c r="H59" s="3">
-        <v>2387300</v>
-      </c>
-      <c r="I59" s="3" t="s">
-        <v>5</v>
+        <v>3527300</v>
+      </c>
+      <c r="I59" s="3">
+        <v>2445100</v>
       </c>
       <c r="J59" s="3" t="s">
         <v>5</v>
@@ -3307,28 +3444,31 @@
       <c r="T59" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U59" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>6844600</v>
+        <v>7382300</v>
       </c>
       <c r="E60" s="3">
-        <v>8799700</v>
+        <v>7010300</v>
       </c>
       <c r="F60" s="3">
-        <v>7064400</v>
+        <v>9012800</v>
       </c>
       <c r="G60" s="3">
-        <v>8428000</v>
+        <v>7235500</v>
       </c>
       <c r="H60" s="3">
-        <v>6272400</v>
-      </c>
-      <c r="I60" s="3" t="s">
-        <v>5</v>
+        <v>8632100</v>
+      </c>
+      <c r="I60" s="3">
+        <v>6424300</v>
       </c>
       <c r="J60" s="3" t="s">
         <v>5</v>
@@ -3363,28 +3503,31 @@
       <c r="T60" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U60" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>4458200</v>
+        <v>4570800</v>
       </c>
       <c r="E61" s="3">
-        <v>3068700</v>
+        <v>4566200</v>
       </c>
       <c r="F61" s="3">
-        <v>3313600</v>
+        <v>3143000</v>
       </c>
       <c r="G61" s="3">
-        <v>3290400</v>
+        <v>3393900</v>
       </c>
       <c r="H61" s="3">
-        <v>3297700</v>
+        <v>3370100</v>
       </c>
       <c r="I61" s="3">
-        <v>0</v>
+        <v>3377500</v>
       </c>
       <c r="J61" s="3">
         <v>0</v>
@@ -3419,28 +3562,31 @@
       <c r="T61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1172300</v>
+        <v>1149100</v>
       </c>
       <c r="E62" s="3">
-        <v>1216600</v>
+        <v>1200700</v>
       </c>
       <c r="F62" s="3">
-        <v>1305300</v>
+        <v>1246100</v>
       </c>
       <c r="G62" s="3">
-        <v>1405600</v>
+        <v>1336900</v>
       </c>
       <c r="H62" s="3">
-        <v>1679600</v>
-      </c>
-      <c r="I62" s="3" t="s">
-        <v>5</v>
+        <v>1439600</v>
+      </c>
+      <c r="I62" s="3">
+        <v>1720300</v>
       </c>
       <c r="J62" s="3" t="s">
         <v>5</v>
@@ -3475,8 +3621,11 @@
       <c r="T62" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U62" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3531,8 +3680,11 @@
       <c r="T63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3587,8 +3739,11 @@
       <c r="T64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3643,28 +3798,31 @@
       <c r="T65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>12839500</v>
+        <v>13449700</v>
       </c>
       <c r="E66" s="3">
-        <v>13437000</v>
+        <v>13150500</v>
       </c>
       <c r="F66" s="3">
-        <v>12092000</v>
+        <v>13762400</v>
       </c>
       <c r="G66" s="3">
-        <v>13746100</v>
+        <v>12384900</v>
       </c>
       <c r="H66" s="3">
-        <v>11947500</v>
-      </c>
-      <c r="I66" s="3" t="s">
-        <v>5</v>
+        <v>14079000</v>
+      </c>
+      <c r="I66" s="3">
+        <v>12236900</v>
       </c>
       <c r="J66" s="3" t="s">
         <v>5</v>
@@ -3699,8 +3857,11 @@
       <c r="T66" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U66" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3721,8 +3882,9 @@
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
-    </row>
-    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U67" s="3"/>
+    </row>
+    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3777,8 +3939,11 @@
       <c r="T68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3833,8 +3998,11 @@
       <c r="T69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3889,8 +4057,11 @@
       <c r="T70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3945,28 +4116,31 @@
       <c r="T71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>3377500</v>
+        <v>3188900</v>
       </c>
       <c r="E72" s="3">
-        <v>10068800</v>
+        <v>3459300</v>
       </c>
       <c r="F72" s="3">
-        <v>10256900</v>
+        <v>10312600</v>
       </c>
       <c r="G72" s="3">
-        <v>9933800</v>
+        <v>10505300</v>
       </c>
       <c r="H72" s="3">
-        <v>11427400</v>
-      </c>
-      <c r="I72" s="3" t="s">
-        <v>5</v>
+        <v>10174400</v>
+      </c>
+      <c r="I72" s="3">
+        <v>11704200</v>
       </c>
       <c r="J72" s="3" t="s">
         <v>5</v>
@@ -4001,8 +4175,11 @@
       <c r="T72" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U72" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4057,8 +4234,11 @@
       <c r="T73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4113,8 +4293,11 @@
       <c r="T74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4169,28 +4352,31 @@
       <c r="T75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>3367100</v>
+        <v>3215100</v>
       </c>
       <c r="E76" s="3">
-        <v>4099200</v>
+        <v>3448600</v>
       </c>
       <c r="F76" s="3">
-        <v>4623200</v>
+        <v>4198500</v>
       </c>
       <c r="G76" s="3">
-        <v>4842100</v>
+        <v>4735200</v>
       </c>
       <c r="H76" s="3">
-        <v>6367900</v>
-      </c>
-      <c r="I76" s="3" t="s">
-        <v>5</v>
+        <v>4959300</v>
+      </c>
+      <c r="I76" s="3">
+        <v>6522200</v>
       </c>
       <c r="J76" s="3" t="s">
         <v>5</v>
@@ -4225,8 +4411,11 @@
       <c r="T76" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U76" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4281,125 +4470,134 @@
       <c r="T77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E81" s="3">
-        <v>-6417500</v>
-      </c>
-      <c r="F81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G81" s="3">
-        <v>506500</v>
-      </c>
-      <c r="H81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I81" s="3">
-        <v>610500</v>
-      </c>
-      <c r="J81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K81" s="3">
+      <c r="D81" s="3">
+        <v>554700</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F81" s="3">
+        <v>-6572900</v>
+      </c>
+      <c r="G81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H81" s="3">
+        <v>518800</v>
+      </c>
+      <c r="I81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J81" s="3">
+        <v>625300</v>
+      </c>
+      <c r="K81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L81" s="3">
         <v>-770100</v>
       </c>
-      <c r="L81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M81" s="3">
+      <c r="M81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N81" s="3">
         <v>555700</v>
       </c>
-      <c r="N81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O81" s="3">
+      <c r="O81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P81" s="3">
         <v>430400</v>
       </c>
-      <c r="P81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q81" s="3">
+      <c r="Q81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R81" s="3">
         <v>425800</v>
       </c>
-      <c r="R81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S81" s="3">
+      <c r="S81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T81" s="3">
         <v>418800</v>
       </c>
-      <c r="T81" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U81" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4420,64 +4618,68 @@
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
-    </row>
-    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U82" s="3"/>
+    </row>
+    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E83" s="3">
-        <v>590400</v>
-      </c>
-      <c r="F83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G83" s="3">
-        <v>283600</v>
-      </c>
-      <c r="H83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I83" s="3">
-        <v>606800</v>
-      </c>
-      <c r="J83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K83" s="3">
+      <c r="D83" s="3">
+        <v>299700</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F83" s="3">
+        <v>604700</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H83" s="3">
+        <v>290500</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J83" s="3">
+        <v>621500</v>
+      </c>
+      <c r="K83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L83" s="3">
         <v>310600</v>
       </c>
-      <c r="L83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M83" s="3">
+      <c r="M83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N83" s="3">
         <v>671000</v>
       </c>
-      <c r="N83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O83" s="3">
+      <c r="O83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P83" s="3">
         <v>303500</v>
       </c>
-      <c r="P83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q83" s="3">
+      <c r="Q83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R83" s="3">
         <v>588200</v>
       </c>
-      <c r="R83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S83" s="3">
+      <c r="S83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T83" s="3">
         <v>320100</v>
       </c>
-      <c r="T83" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U83" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4532,8 +4734,11 @@
       <c r="T84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4588,8 +4793,11 @@
       <c r="T85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4644,8 +4852,11 @@
       <c r="T86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4700,8 +4911,11 @@
       <c r="T87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4756,64 +4970,70 @@
       <c r="T88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E89" s="3">
-        <v>1682100</v>
-      </c>
-      <c r="F89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G89" s="3">
-        <v>885200</v>
-      </c>
-      <c r="H89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I89" s="3">
-        <v>1876600</v>
-      </c>
-      <c r="J89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K89" s="3">
+      <c r="D89" s="3">
+        <v>872900</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F89" s="3">
+        <v>1722800</v>
+      </c>
+      <c r="G89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H89" s="3">
+        <v>906600</v>
+      </c>
+      <c r="I89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J89" s="3">
+        <v>1922000</v>
+      </c>
+      <c r="K89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L89" s="3">
         <v>1223200</v>
       </c>
-      <c r="L89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M89" s="3">
+      <c r="M89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N89" s="3">
         <v>1929200</v>
       </c>
-      <c r="N89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O89" s="3">
+      <c r="O89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P89" s="3">
         <v>950500</v>
       </c>
-      <c r="P89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q89" s="3">
+      <c r="Q89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R89" s="3">
         <v>1465600</v>
       </c>
-      <c r="R89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S89" s="3">
+      <c r="S89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T89" s="3">
         <v>749900</v>
       </c>
-      <c r="T89" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U89" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4834,29 +5054,30 @@
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
-    </row>
-    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U90" s="3"/>
+    </row>
+    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-2279000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-2451000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1792000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-2412000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1606000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-2244000</v>
       </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
       <c r="J91" s="3">
         <v>0</v>
       </c>
@@ -4873,25 +5094,28 @@
         <v>0</v>
       </c>
       <c r="O91" s="3">
+        <v>0</v>
+      </c>
+      <c r="P91" s="3">
         <v>-235900</v>
       </c>
-      <c r="P91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q91" s="3">
+      <c r="Q91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R91" s="3">
         <v>-589500</v>
       </c>
-      <c r="R91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S91" s="3">
+      <c r="S91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T91" s="3">
         <v>-363900</v>
       </c>
-      <c r="T91" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U91" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4946,8 +5170,11 @@
       <c r="T92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5002,64 +5229,70 @@
       <c r="T93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E94" s="3">
-        <v>-975200</v>
-      </c>
-      <c r="F94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G94" s="3">
-        <v>-336800</v>
-      </c>
-      <c r="H94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I94" s="3">
-        <v>-444200</v>
-      </c>
-      <c r="J94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K94" s="3">
+      <c r="D94" s="3">
+        <v>18100</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F94" s="3">
+        <v>-998800</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H94" s="3">
+        <v>-345000</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J94" s="3">
+        <v>-454900</v>
+      </c>
+      <c r="K94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L94" s="3">
         <v>-158500</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M94" s="3">
+      <c r="M94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N94" s="3">
         <v>-591700</v>
       </c>
-      <c r="N94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O94" s="3">
+      <c r="O94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P94" s="3">
         <v>-179600</v>
       </c>
-      <c r="P94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q94" s="3">
+      <c r="Q94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R94" s="3">
         <v>-787400</v>
       </c>
-      <c r="R94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S94" s="3">
+      <c r="S94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T94" s="3">
         <v>-289100</v>
       </c>
-      <c r="T94" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U94" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5080,64 +5313,68 @@
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
-    </row>
-    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U95" s="3"/>
+    </row>
+    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>0</v>
+        <v>-534500</v>
       </c>
       <c r="E96" s="3">
-        <v>-535500</v>
+        <v>0</v>
       </c>
       <c r="F96" s="3">
-        <v>0</v>
+        <v>-548400</v>
       </c>
       <c r="G96" s="3">
-        <v>-535500</v>
+        <v>0</v>
       </c>
       <c r="H96" s="3">
-        <v>0</v>
+        <v>-548400</v>
       </c>
       <c r="I96" s="3">
-        <v>-491100</v>
+        <v>0</v>
       </c>
       <c r="J96" s="3">
-        <v>0</v>
+        <v>-503000</v>
       </c>
       <c r="K96" s="3">
+        <v>0</v>
+      </c>
+      <c r="L96" s="3">
         <v>-494700</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
       <c r="M96" s="3">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3">
         <v>-463700</v>
       </c>
-      <c r="N96" s="3">
-        <v>0</v>
-      </c>
       <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3">
         <v>-453200</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
-      </c>
       <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3">
         <v>-414800</v>
       </c>
-      <c r="R96" s="3">
-        <v>0</v>
-      </c>
       <c r="S96" s="3">
+        <v>0</v>
+      </c>
+      <c r="T96" s="3">
         <v>-453700</v>
       </c>
-      <c r="T96" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5192,8 +5429,11 @@
       <c r="T97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5248,8 +5488,11 @@
       <c r="T98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5304,172 +5547,184 @@
       <c r="T99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E100" s="3">
-        <v>198500</v>
-      </c>
-      <c r="F100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G100" s="3">
-        <v>-43500</v>
-      </c>
-      <c r="H100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I100" s="3">
-        <v>-1443300</v>
-      </c>
-      <c r="J100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K100" s="3">
+      <c r="D100" s="3">
+        <v>-1290700</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F100" s="3">
+        <v>203300</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H100" s="3">
+        <v>-44500</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J100" s="3">
+        <v>-1478200</v>
+      </c>
+      <c r="K100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L100" s="3">
         <v>-328100</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M100" s="3">
+      <c r="M100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N100" s="3">
         <v>-1301500</v>
       </c>
-      <c r="N100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O100" s="3">
+      <c r="O100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P100" s="3">
         <v>-713100</v>
       </c>
-      <c r="P100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q100" s="3">
+      <c r="Q100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R100" s="3">
         <v>-242700</v>
       </c>
-      <c r="R100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S100" s="3">
+      <c r="S100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T100" s="3">
         <v>-73200</v>
       </c>
-      <c r="T100" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U100" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E101" s="3">
-        <v>-178100</v>
-      </c>
-      <c r="F101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G101" s="3">
-        <v>25900</v>
-      </c>
-      <c r="H101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I101" s="3">
-        <v>-99000</v>
-      </c>
-      <c r="J101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K101" s="3">
+      <c r="D101" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F101" s="3">
+        <v>-182400</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H101" s="3">
+        <v>26600</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J101" s="3">
+        <v>-101400</v>
+      </c>
+      <c r="K101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L101" s="3">
         <v>57100</v>
       </c>
-      <c r="L101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M101" s="3">
+      <c r="M101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N101" s="3">
         <v>66600</v>
       </c>
-      <c r="N101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O101" s="3">
+      <c r="O101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P101" s="3">
         <v>22600</v>
       </c>
-      <c r="P101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q101" s="3">
+      <c r="Q101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R101" s="3">
         <v>-58700</v>
       </c>
-      <c r="R101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S101" s="3">
+      <c r="S101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T101" s="3">
         <v>-16700</v>
       </c>
-      <c r="T101" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U101" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E102" s="3">
-        <v>727400</v>
-      </c>
-      <c r="F102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G102" s="3">
-        <v>530800</v>
-      </c>
-      <c r="H102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I102" s="3">
-        <v>-109800</v>
-      </c>
-      <c r="J102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K102" s="3">
+      <c r="D102" s="3">
+        <v>-402700</v>
+      </c>
+      <c r="E102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F102" s="3">
+        <v>745000</v>
+      </c>
+      <c r="G102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H102" s="3">
+        <v>543700</v>
+      </c>
+      <c r="I102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J102" s="3">
+        <v>-112500</v>
+      </c>
+      <c r="K102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L102" s="3">
         <v>793600</v>
       </c>
-      <c r="L102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M102" s="3">
+      <c r="M102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N102" s="3">
         <v>56200</v>
       </c>
-      <c r="N102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O102" s="3">
+      <c r="O102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P102" s="3">
         <v>59400</v>
       </c>
-      <c r="P102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q102" s="3">
+      <c r="Q102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R102" s="3">
         <v>376700</v>
       </c>
-      <c r="R102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S102" s="3">
+      <c r="S102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T102" s="3">
         <v>370800</v>
       </c>
-      <c r="T102" s="3" t="s">
+      <c r="U102" s="3" t="s">
         <v>5</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CABGY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CABGY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="613" uniqueCount="92">
   <si>
     <t>CABGY</t>
   </si>
@@ -752,26 +752,26 @@
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3">
-        <v>5754000</v>
-      </c>
-      <c r="E8" s="3">
-        <v>2542800</v>
-      </c>
-      <c r="F8" s="3">
-        <v>5313300</v>
-      </c>
-      <c r="G8" s="3">
-        <v>3012200</v>
-      </c>
-      <c r="H8" s="3">
-        <v>5608900</v>
-      </c>
-      <c r="I8" s="3">
-        <v>2435000</v>
-      </c>
-      <c r="J8" s="3">
-        <v>5168000</v>
+      <c r="D8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K8" s="3">
         <v>2932900</v>
@@ -811,26 +811,26 @@
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="3">
-        <v>3090500</v>
+      <c r="D9" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F9" s="3">
-        <v>2945900</v>
+      <c r="F9" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H9" s="3">
-        <v>3103100</v>
+      <c r="H9" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="I9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J9" s="3">
-        <v>2842700</v>
+      <c r="J9" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>5</v>
@@ -870,26 +870,26 @@
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3">
-        <v>2663600</v>
+      <c r="D10" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F10" s="3">
-        <v>2367500</v>
+      <c r="F10" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H10" s="3">
-        <v>2505800</v>
+      <c r="H10" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="I10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J10" s="3">
-        <v>2325300</v>
+      <c r="J10" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>5</v>
@@ -1070,26 +1070,26 @@
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>20600</v>
+      <c r="D14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F14" s="3">
-        <v>38900</v>
+      <c r="F14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H14" s="3">
-        <v>25100</v>
+      <c r="H14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J14" s="3">
-        <v>-10200</v>
+      <c r="J14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>5</v>
@@ -1129,26 +1129,26 @@
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="3">
-        <v>0</v>
-      </c>
-      <c r="E15" s="3">
-        <v>0</v>
-      </c>
-      <c r="F15" s="3">
-        <v>0</v>
-      </c>
-      <c r="G15" s="3">
-        <v>0</v>
-      </c>
-      <c r="H15" s="3">
-        <v>0</v>
-      </c>
-      <c r="I15" s="3">
-        <v>0</v>
-      </c>
-      <c r="J15" s="3">
-        <v>0</v>
+      <c r="D15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1208,26 +1208,26 @@
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3">
-        <v>4834200</v>
+      <c r="D17" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F17" s="3">
-        <v>4634900</v>
+      <c r="F17" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H17" s="3">
-        <v>4703000</v>
+      <c r="H17" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="I17" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J17" s="3">
-        <v>4411500</v>
+      <c r="J17" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K17" s="3" t="s">
         <v>5</v>
@@ -1267,26 +1267,26 @@
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3">
-        <v>919800</v>
+      <c r="D18" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F18" s="3">
-        <v>678500</v>
+      <c r="F18" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H18" s="3">
-        <v>905900</v>
+      <c r="H18" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="I18" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J18" s="3">
-        <v>756500</v>
+      <c r="J18" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K18" s="3" t="s">
         <v>5</v>
@@ -1349,26 +1349,26 @@
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>-1000</v>
+      <c r="D20" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F20" s="3">
-        <v>-9100</v>
+      <c r="F20" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H20" s="3">
-        <v>-1000</v>
+      <c r="H20" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="I20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J20" s="3">
-        <v>12000</v>
+      <c r="J20" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K20" s="3" t="s">
         <v>5</v>
@@ -1408,26 +1408,26 @@
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3">
-        <v>1218500</v>
+      <c r="D21" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F21" s="3">
-        <v>1274100</v>
+      <c r="F21" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H21" s="3">
-        <v>1195300</v>
+      <c r="H21" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="I21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J21" s="3">
-        <v>1390000</v>
+      <c r="J21" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>5</v>
@@ -1467,26 +1467,26 @@
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>80600</v>
+      <c r="D22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F22" s="3">
-        <v>66900</v>
+      <c r="F22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H22" s="3">
-        <v>48200</v>
+      <c r="H22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="I22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J22" s="3">
-        <v>42500</v>
+      <c r="J22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K22" s="3" t="s">
         <v>5</v>
@@ -1526,26 +1526,26 @@
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3">
-        <v>838200</v>
+      <c r="D23" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F23" s="3">
-        <v>602500</v>
+      <c r="F23" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H23" s="3">
-        <v>856600</v>
+      <c r="H23" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="I23" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J23" s="3">
-        <v>726100</v>
+      <c r="J23" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K23" s="3" t="s">
         <v>5</v>
@@ -1585,26 +1585,26 @@
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>178000</v>
+      <c r="D24" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F24" s="3">
-        <v>96000</v>
+      <c r="F24" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H24" s="3">
-        <v>179900</v>
+      <c r="H24" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="I24" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J24" s="3">
-        <v>98400</v>
+      <c r="J24" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K24" s="3" t="s">
         <v>5</v>
@@ -1703,26 +1703,26 @@
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3">
-        <v>660200</v>
+      <c r="D26" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F26" s="3">
-        <v>506400</v>
+      <c r="F26" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H26" s="3">
-        <v>676700</v>
+      <c r="H26" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="I26" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J26" s="3">
-        <v>627700</v>
+      <c r="J26" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K26" s="3" t="s">
         <v>5</v>
@@ -1762,26 +1762,26 @@
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3">
-        <v>554700</v>
+      <c r="D27" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F27" s="3">
-        <v>454300</v>
+      <c r="F27" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H27" s="3">
-        <v>578700</v>
+      <c r="H27" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="I27" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J27" s="3">
-        <v>544700</v>
+      <c r="J27" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K27" s="3" t="s">
         <v>5</v>
@@ -1880,26 +1880,26 @@
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3">
-        <v>0</v>
+      <c r="D29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F29" s="3">
-        <v>-7027300</v>
+      <c r="F29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H29" s="3">
-        <v>-60000</v>
+      <c r="H29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="I29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J29" s="3">
-        <v>80600</v>
+      <c r="J29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>5</v>
@@ -2057,26 +2057,26 @@
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>1000</v>
+      <c r="D32" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F32" s="3">
-        <v>9100</v>
+      <c r="F32" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H32" s="3">
-        <v>1000</v>
+      <c r="H32" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="I32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J32" s="3">
-        <v>-12000</v>
+      <c r="J32" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K32" s="3" t="s">
         <v>5</v>
@@ -2116,26 +2116,26 @@
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3">
-        <v>554700</v>
+      <c r="D33" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E33" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F33" s="3">
-        <v>-6572900</v>
+      <c r="F33" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H33" s="3">
-        <v>518800</v>
+      <c r="H33" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="I33" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J33" s="3">
-        <v>625300</v>
+      <c r="J33" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K33" s="3" t="s">
         <v>5</v>
@@ -2234,26 +2234,26 @@
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3">
-        <v>554700</v>
+      <c r="D35" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E35" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F35" s="3">
-        <v>-6572900</v>
+      <c r="F35" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="G35" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H35" s="3">
-        <v>518800</v>
+      <c r="H35" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="I35" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J35" s="3">
-        <v>625300</v>
+      <c r="J35" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K35" s="3" t="s">
         <v>5</v>
@@ -2404,25 +2404,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>1589500</v>
+        <v>1538600</v>
       </c>
       <c r="E41" s="3">
-        <v>1986300</v>
+        <v>1548900</v>
       </c>
       <c r="F41" s="3">
-        <v>1667900</v>
+        <v>1984500</v>
       </c>
       <c r="G41" s="3">
-        <v>1211600</v>
+        <v>1898100</v>
       </c>
       <c r="H41" s="3">
-        <v>1972200</v>
+        <v>1647100</v>
       </c>
       <c r="I41" s="3">
-        <v>1238500</v>
-      </c>
-      <c r="J41" s="3" t="s">
-        <v>5</v>
+        <v>1638800</v>
+      </c>
+      <c r="J41" s="3">
+        <v>1172800</v>
       </c>
       <c r="K41" s="3" t="s">
         <v>5</v>
@@ -2466,22 +2466,22 @@
         <v>0</v>
       </c>
       <c r="E42" s="3">
-        <v>331900</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>5</v>
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
+        <v>331600</v>
+      </c>
+      <c r="G42" s="3">
+        <v>317100</v>
+      </c>
+      <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
+        <v>0</v>
       </c>
       <c r="K42" s="3" t="s">
         <v>5</v>
@@ -2522,25 +2522,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>1823300</v>
+        <v>1764900</v>
       </c>
       <c r="E43" s="3">
-        <v>1177600</v>
+        <v>1776700</v>
       </c>
       <c r="F43" s="3">
-        <v>1820800</v>
+        <v>1176600</v>
       </c>
       <c r="G43" s="3">
-        <v>1155700</v>
+        <v>1125300</v>
       </c>
       <c r="H43" s="3">
-        <v>1633500</v>
+        <v>1798100</v>
       </c>
       <c r="I43" s="3">
-        <v>1222500</v>
-      </c>
-      <c r="J43" s="3" t="s">
-        <v>5</v>
+        <v>1789000</v>
+      </c>
+      <c r="J43" s="3">
+        <v>1118700</v>
       </c>
       <c r="K43" s="3" t="s">
         <v>5</v>
@@ -2581,25 +2581,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>967900</v>
+        <v>936900</v>
       </c>
       <c r="E44" s="3">
-        <v>862500</v>
+        <v>943100</v>
       </c>
       <c r="F44" s="3">
-        <v>994500</v>
+        <v>861800</v>
       </c>
       <c r="G44" s="3">
-        <v>848700</v>
+        <v>824200</v>
       </c>
       <c r="H44" s="3">
-        <v>842200</v>
+        <v>982100</v>
       </c>
       <c r="I44" s="3">
-        <v>800200</v>
-      </c>
-      <c r="J44" s="3" t="s">
-        <v>5</v>
+        <v>977100</v>
+      </c>
+      <c r="J44" s="3">
+        <v>821600</v>
       </c>
       <c r="K44" s="3" t="s">
         <v>5</v>
@@ -2639,26 +2639,26 @@
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>0</v>
-      </c>
-      <c r="E45" s="3">
-        <v>123900</v>
-      </c>
-      <c r="F45" s="3">
-        <v>1496900</v>
-      </c>
-      <c r="G45" s="3">
-        <v>1867500</v>
+      <c r="D45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H45" s="3">
-        <v>2452500</v>
+        <v>1478200</v>
       </c>
       <c r="I45" s="3">
-        <v>137900</v>
-      </c>
-      <c r="J45" s="3" t="s">
-        <v>5</v>
+        <v>1470800</v>
+      </c>
+      <c r="J45" s="3">
+        <v>1669300</v>
       </c>
       <c r="K45" s="3" t="s">
         <v>5</v>
@@ -2699,25 +2699,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>4380800</v>
+        <v>4240400</v>
       </c>
       <c r="E46" s="3">
-        <v>4482300</v>
+        <v>4268600</v>
       </c>
       <c r="F46" s="3">
-        <v>5980100</v>
+        <v>4478300</v>
       </c>
       <c r="G46" s="3">
-        <v>5083600</v>
+        <v>4283200</v>
       </c>
       <c r="H46" s="3">
-        <v>6900400</v>
+        <v>5905500</v>
       </c>
       <c r="I46" s="3">
-        <v>3399000</v>
-      </c>
-      <c r="J46" s="3" t="s">
-        <v>5</v>
+        <v>5875600</v>
+      </c>
+      <c r="J46" s="3">
+        <v>4920800</v>
       </c>
       <c r="K46" s="3" t="s">
         <v>5</v>
@@ -2757,26 +2757,26 @@
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>1257800</v>
-      </c>
-      <c r="E47" s="3">
-        <v>937800</v>
+      <c r="D47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="F47" s="3">
-        <v>1201800</v>
+        <v>806300</v>
       </c>
       <c r="G47" s="3">
-        <v>958700</v>
-      </c>
-      <c r="H47" s="3">
-        <v>1166500</v>
-      </c>
-      <c r="I47" s="3">
-        <v>927200</v>
-      </c>
-      <c r="J47" s="3" t="s">
-        <v>5</v>
+        <v>771200</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J47" s="3">
+        <v>793500</v>
       </c>
       <c r="K47" s="3" t="s">
         <v>5</v>
@@ -2817,25 +2817,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>3722200</v>
+        <v>3602900</v>
       </c>
       <c r="E48" s="3">
-        <v>3622400</v>
+        <v>3626900</v>
       </c>
       <c r="F48" s="3">
-        <v>3501600</v>
+        <v>3619200</v>
       </c>
       <c r="G48" s="3">
-        <v>3514700</v>
+        <v>3461500</v>
       </c>
       <c r="H48" s="3">
-        <v>3513200</v>
+        <v>3457900</v>
       </c>
       <c r="I48" s="3">
-        <v>3955400</v>
-      </c>
-      <c r="J48" s="3" t="s">
-        <v>5</v>
+        <v>3440400</v>
+      </c>
+      <c r="J48" s="3">
+        <v>3402200</v>
       </c>
       <c r="K48" s="3" t="s">
         <v>5</v>
@@ -2876,25 +2876,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>7304100</v>
+        <v>7070000</v>
       </c>
       <c r="E49" s="3">
-        <v>7287900</v>
+        <v>7117200</v>
       </c>
       <c r="F49" s="3">
-        <v>7277400</v>
+        <v>7281400</v>
       </c>
       <c r="G49" s="3">
-        <v>7306200</v>
+        <v>6964200</v>
       </c>
       <c r="H49" s="3">
-        <v>7458300</v>
+        <v>7186600</v>
       </c>
       <c r="I49" s="3">
-        <v>10163700</v>
-      </c>
-      <c r="J49" s="3" t="s">
-        <v>5</v>
+        <v>7150200</v>
+      </c>
+      <c r="J49" s="3">
+        <v>7072300</v>
       </c>
       <c r="K49" s="3" t="s">
         <v>5</v>
@@ -3052,26 +3052,26 @@
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3" t="s">
-        <v>5</v>
+      <c r="D52" s="3">
+        <v>1217500</v>
       </c>
       <c r="E52" s="3">
-        <v>268700</v>
-      </c>
-      <c r="F52" s="3" t="s">
-        <v>5</v>
+        <v>1225600</v>
+      </c>
+      <c r="F52" s="3">
+        <v>33200</v>
       </c>
       <c r="G52" s="3">
-        <v>256900</v>
-      </c>
-      <c r="H52" s="3" t="s">
-        <v>5</v>
+        <v>31800</v>
+      </c>
+      <c r="H52" s="3">
+        <v>1186800</v>
       </c>
       <c r="I52" s="3">
-        <v>313600</v>
-      </c>
-      <c r="J52" s="3" t="s">
-        <v>5</v>
+        <v>1180800</v>
+      </c>
+      <c r="J52" s="3">
+        <v>42000</v>
       </c>
       <c r="K52" s="3" t="s">
         <v>5</v>
@@ -3171,25 +3171,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>16664800</v>
+        <v>16130800</v>
       </c>
       <c r="E54" s="3">
-        <v>16599100</v>
+        <v>16238300</v>
       </c>
       <c r="F54" s="3">
-        <v>17960900</v>
+        <v>16584200</v>
       </c>
       <c r="G54" s="3">
-        <v>17120100</v>
+        <v>15861800</v>
       </c>
       <c r="H54" s="3">
-        <v>19038400</v>
+        <v>17736800</v>
       </c>
       <c r="I54" s="3">
-        <v>18759000</v>
-      </c>
-      <c r="J54" s="3" t="s">
-        <v>5</v>
+        <v>17647100</v>
+      </c>
+      <c r="J54" s="3">
+        <v>16572000</v>
       </c>
       <c r="K54" s="3" t="s">
         <v>5</v>
@@ -3276,25 +3276,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>3829900</v>
+        <v>3707200</v>
       </c>
       <c r="E57" s="3">
-        <v>3289100</v>
+        <v>3731900</v>
       </c>
       <c r="F57" s="3">
-        <v>3718800</v>
+        <v>3286100</v>
       </c>
       <c r="G57" s="3">
-        <v>3253100</v>
+        <v>3143000</v>
       </c>
       <c r="H57" s="3">
-        <v>3617700</v>
+        <v>3672400</v>
       </c>
       <c r="I57" s="3">
-        <v>3063900</v>
-      </c>
-      <c r="J57" s="3" t="s">
-        <v>5</v>
+        <v>3653800</v>
+      </c>
+      <c r="J57" s="3">
+        <v>3149000</v>
       </c>
       <c r="K57" s="3" t="s">
         <v>5</v>
@@ -3335,25 +3335,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>932700</v>
+        <v>902800</v>
       </c>
       <c r="E58" s="3">
-        <v>1237600</v>
+        <v>908900</v>
       </c>
       <c r="F58" s="3">
-        <v>2021600</v>
+        <v>1236500</v>
       </c>
       <c r="G58" s="3">
-        <v>858100</v>
+        <v>1182600</v>
       </c>
       <c r="H58" s="3">
-        <v>1487100</v>
+        <v>1996400</v>
       </c>
       <c r="I58" s="3">
-        <v>915400</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>5</v>
+        <v>1986300</v>
+      </c>
+      <c r="J58" s="3">
+        <v>830600</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>5</v>
@@ -3394,25 +3394,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>2619600</v>
+        <v>2535700</v>
       </c>
       <c r="E59" s="3">
-        <v>2483700</v>
+        <v>2552600</v>
       </c>
       <c r="F59" s="3">
-        <v>3272400</v>
+        <v>2481500</v>
       </c>
       <c r="G59" s="3">
-        <v>3124300</v>
+        <v>2373400</v>
       </c>
       <c r="H59" s="3">
-        <v>3527300</v>
+        <v>3231600</v>
       </c>
       <c r="I59" s="3">
-        <v>2445100</v>
-      </c>
-      <c r="J59" s="3" t="s">
-        <v>5</v>
+        <v>3215200</v>
+      </c>
+      <c r="J59" s="3">
+        <v>3024300</v>
       </c>
       <c r="K59" s="3" t="s">
         <v>5</v>
@@ -3453,25 +3453,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>7382300</v>
+        <v>7145800</v>
       </c>
       <c r="E60" s="3">
-        <v>7010300</v>
+        <v>7193400</v>
       </c>
       <c r="F60" s="3">
-        <v>9012800</v>
+        <v>7004100</v>
       </c>
       <c r="G60" s="3">
-        <v>7235500</v>
+        <v>6699000</v>
       </c>
       <c r="H60" s="3">
-        <v>8632100</v>
+        <v>8900400</v>
       </c>
       <c r="I60" s="3">
-        <v>6424300</v>
-      </c>
-      <c r="J60" s="3" t="s">
-        <v>5</v>
+        <v>8855300</v>
+      </c>
+      <c r="J60" s="3">
+        <v>7003900</v>
       </c>
       <c r="K60" s="3" t="s">
         <v>5</v>
@@ -3512,25 +3512,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>4570800</v>
+        <v>4424300</v>
       </c>
       <c r="E61" s="3">
-        <v>4566200</v>
+        <v>4453800</v>
       </c>
       <c r="F61" s="3">
-        <v>3143000</v>
+        <v>4562100</v>
       </c>
       <c r="G61" s="3">
-        <v>3393900</v>
+        <v>4363300</v>
       </c>
       <c r="H61" s="3">
-        <v>3370100</v>
+        <v>3103800</v>
       </c>
       <c r="I61" s="3">
-        <v>3377500</v>
+        <v>3088100</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>3285200</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -3571,25 +3571,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1149100</v>
+        <v>1112300</v>
       </c>
       <c r="E62" s="3">
-        <v>1200700</v>
+        <v>1119700</v>
       </c>
       <c r="F62" s="3">
-        <v>1246100</v>
+        <v>278700</v>
       </c>
       <c r="G62" s="3">
-        <v>1336900</v>
+        <v>266500</v>
       </c>
       <c r="H62" s="3">
-        <v>1439600</v>
+        <v>1230500</v>
       </c>
       <c r="I62" s="3">
-        <v>1720300</v>
-      </c>
-      <c r="J62" s="3" t="s">
-        <v>5</v>
+        <v>1224300</v>
+      </c>
+      <c r="J62" s="3">
+        <v>374900</v>
       </c>
       <c r="K62" s="3" t="s">
         <v>5</v>
@@ -3807,25 +3807,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>13449700</v>
+        <v>12682400</v>
       </c>
       <c r="E66" s="3">
-        <v>13150500</v>
+        <v>12766900</v>
       </c>
       <c r="F66" s="3">
-        <v>13762400</v>
+        <v>12765700</v>
       </c>
       <c r="G66" s="3">
-        <v>12384900</v>
+        <v>12209600</v>
       </c>
       <c r="H66" s="3">
-        <v>14079000</v>
+        <v>13234700</v>
       </c>
       <c r="I66" s="3">
-        <v>12236900</v>
-      </c>
-      <c r="J66" s="3" t="s">
-        <v>5</v>
+        <v>13167700</v>
+      </c>
+      <c r="J66" s="3">
+        <v>11583200</v>
       </c>
       <c r="K66" s="3" t="s">
         <v>5</v>
@@ -4125,25 +4125,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>3188900</v>
+        <v>3086700</v>
       </c>
       <c r="E72" s="3">
-        <v>3459300</v>
+        <v>3107300</v>
       </c>
       <c r="F72" s="3">
-        <v>10312600</v>
+        <v>3456200</v>
       </c>
       <c r="G72" s="3">
-        <v>10505300</v>
+        <v>3305700</v>
       </c>
       <c r="H72" s="3">
-        <v>10174400</v>
+        <v>10183900</v>
       </c>
       <c r="I72" s="3">
-        <v>11704200</v>
-      </c>
-      <c r="J72" s="3" t="s">
-        <v>5</v>
+        <v>10132400</v>
+      </c>
+      <c r="J72" s="3">
+        <v>10169000</v>
       </c>
       <c r="K72" s="3" t="s">
         <v>5</v>
@@ -4361,25 +4361,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>3215100</v>
+        <v>3112100</v>
       </c>
       <c r="E76" s="3">
-        <v>3448600</v>
+        <v>3132900</v>
       </c>
       <c r="F76" s="3">
-        <v>4198500</v>
+        <v>3445500</v>
       </c>
       <c r="G76" s="3">
-        <v>4735200</v>
+        <v>3295400</v>
       </c>
       <c r="H76" s="3">
-        <v>4959300</v>
+        <v>4146100</v>
       </c>
       <c r="I76" s="3">
-        <v>6522200</v>
-      </c>
-      <c r="J76" s="3" t="s">
-        <v>5</v>
+        <v>4125100</v>
+      </c>
+      <c r="J76" s="3">
+        <v>4583600</v>
       </c>
       <c r="K76" s="3" t="s">
         <v>5</v>
@@ -4542,26 +4542,26 @@
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3">
-        <v>554700</v>
+      <c r="D81" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E81" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F81" s="3">
-        <v>-6572900</v>
+      <c r="F81" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="G81" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H81" s="3">
-        <v>518800</v>
+      <c r="H81" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="I81" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J81" s="3">
-        <v>625300</v>
+      <c r="J81" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K81" s="3" t="s">
         <v>5</v>
@@ -4625,25 +4625,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>299700</v>
-      </c>
-      <c r="E83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F83" s="3">
-        <v>604700</v>
+        <v>143400</v>
+      </c>
+      <c r="E83" s="3">
+        <v>142700</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="G83" s="3" t="s">
         <v>5</v>
       </c>
       <c r="H83" s="3">
-        <v>290500</v>
-      </c>
-      <c r="I83" s="3" t="s">
-        <v>5</v>
+        <v>149700</v>
+      </c>
+      <c r="I83" s="3">
+        <v>158800</v>
       </c>
       <c r="J83" s="3">
-        <v>621500</v>
+        <v>169300</v>
       </c>
       <c r="K83" s="3" t="s">
         <v>5</v>
@@ -4979,25 +4979,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>872900</v>
-      </c>
-      <c r="E89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F89" s="3">
-        <v>1722800</v>
+        <v>422500</v>
+      </c>
+      <c r="E89" s="3">
+        <v>425300</v>
+      </c>
+      <c r="F89" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="G89" s="3" t="s">
         <v>5</v>
       </c>
       <c r="H89" s="3">
-        <v>906600</v>
-      </c>
-      <c r="I89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J89" s="3">
-        <v>1922000</v>
+        <v>596100</v>
+      </c>
+      <c r="I89" s="3">
+        <v>593100</v>
+      </c>
+      <c r="J89" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K89" s="3" t="s">
         <v>5</v>
@@ -5061,25 +5061,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-2279000</v>
+        <v>-163700</v>
       </c>
       <c r="E91" s="3">
-        <v>-2451000</v>
-      </c>
-      <c r="F91" s="3">
-        <v>-1792000</v>
-      </c>
-      <c r="G91" s="3">
-        <v>-2412000</v>
+        <v>-164800</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H91" s="3">
-        <v>-1606000</v>
+        <v>-131300</v>
       </c>
       <c r="I91" s="3">
-        <v>-2244000</v>
-      </c>
-      <c r="J91" s="3">
-        <v>0</v>
+        <v>-130700</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K91" s="3">
         <v>0</v>
@@ -5238,25 +5238,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>18100</v>
-      </c>
-      <c r="E94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F94" s="3">
-        <v>-998800</v>
+        <v>8800</v>
+      </c>
+      <c r="E94" s="3">
+        <v>8800</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="G94" s="3" t="s">
         <v>5</v>
       </c>
       <c r="H94" s="3">
-        <v>-345000</v>
-      </c>
-      <c r="I94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J94" s="3">
-        <v>-454900</v>
+        <v>-170300</v>
+      </c>
+      <c r="I94" s="3">
+        <v>-169500</v>
+      </c>
+      <c r="J94" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K94" s="3" t="s">
         <v>5</v>
@@ -5320,25 +5320,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-534500</v>
+        <v>258700</v>
       </c>
       <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>-548400</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
+        <v>260400</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H96" s="3">
-        <v>-548400</v>
+        <v>270800</v>
       </c>
       <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>-503000</v>
+        <v>269400</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -5556,25 +5556,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-1290700</v>
-      </c>
-      <c r="E100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F100" s="3">
-        <v>203300</v>
+        <v>-624700</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-628900</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="G100" s="3" t="s">
         <v>5</v>
       </c>
       <c r="H100" s="3">
-        <v>-44500</v>
-      </c>
-      <c r="I100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J100" s="3">
-        <v>-1478200</v>
+        <v>-22000</v>
+      </c>
+      <c r="I100" s="3">
+        <v>-21900</v>
+      </c>
+      <c r="J100" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K100" s="3" t="s">
         <v>5</v>
@@ -5615,25 +5615,25 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-3000</v>
-      </c>
-      <c r="E101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F101" s="3">
-        <v>-182400</v>
+        <v>-74400</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-74000</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="G101" s="3" t="s">
         <v>5</v>
       </c>
       <c r="H101" s="3">
-        <v>26600</v>
-      </c>
-      <c r="I101" s="3" t="s">
-        <v>5</v>
+        <v>27500</v>
+      </c>
+      <c r="I101" s="3">
+        <v>29200</v>
       </c>
       <c r="J101" s="3">
-        <v>-101400</v>
+        <v>22900</v>
       </c>
       <c r="K101" s="3" t="s">
         <v>5</v>
@@ -5674,25 +5674,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-402700</v>
-      </c>
-      <c r="E102" s="3" t="s">
-        <v>5</v>
+        <v>-192000</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-193300</v>
       </c>
       <c r="F102" s="3">
-        <v>745000</v>
-      </c>
-      <c r="G102" s="3" t="s">
-        <v>5</v>
+        <v>0</v>
+      </c>
+      <c r="G102" s="3">
+        <v>0</v>
       </c>
       <c r="H102" s="3">
-        <v>543700</v>
-      </c>
-      <c r="I102" s="3" t="s">
-        <v>5</v>
+        <v>329400</v>
+      </c>
+      <c r="I102" s="3">
+        <v>327800</v>
       </c>
       <c r="J102" s="3">
-        <v>-112500</v>
+        <v>0</v>
       </c>
       <c r="K102" s="3" t="s">
         <v>5</v>

--- a/AAII_Financials/Quarterly/CABGY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CABGY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="613" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="655" uniqueCount="92">
   <si>
     <t>CABGY</t>
   </si>
@@ -656,99 +656,106 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:U102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -773,41 +780,47 @@
       <c r="J8" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K8" s="3">
+      <c r="K8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M8" s="3">
         <v>2932900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>5174200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>2173500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>4572300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>2586000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>4077200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>1620100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>3984500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>2407800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>4229100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>1899000</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -835,38 +848,44 @@
       <c r="K9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L9" s="3">
+      <c r="L9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N9" s="3">
         <v>2780100</v>
       </c>
-      <c r="M9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P9" s="3">
         <v>2415700</v>
       </c>
-      <c r="O9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R9" s="3">
         <v>2122300</v>
       </c>
-      <c r="Q9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T9" s="3">
         <v>2061000</v>
       </c>
-      <c r="S9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V9" s="3">
         <v>2172800</v>
       </c>
-      <c r="U9" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="W9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -894,38 +913,44 @@
       <c r="K10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L10" s="3">
+      <c r="L10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N10" s="3">
         <v>2394100</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P10" s="3">
         <v>2156600</v>
       </c>
-      <c r="O10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R10" s="3">
         <v>1954800</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T10" s="3">
         <v>1923500</v>
       </c>
-      <c r="S10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V10" s="3">
         <v>2056300</v>
       </c>
-      <c r="U10" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="W10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -947,8 +972,10 @@
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V11" s="3"/>
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1006,8 +1033,14 @@
       <c r="U12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1065,8 +1098,14 @@
       <c r="U13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1094,38 +1133,44 @@
       <c r="K14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N14" s="3">
         <v>124500</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P14" s="3">
         <v>-34900</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R14" s="3">
         <v>28200</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T14" s="3">
         <v>38500</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V14" s="3">
         <v>1800</v>
       </c>
-      <c r="U14" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="W14" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1150,11 +1195,11 @@
       <c r="J15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
-      <c r="L15" s="3">
-        <v>0</v>
+      <c r="K15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L15" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M15" s="3">
         <v>0</v>
@@ -1183,8 +1228,14 @@
       <c r="U15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V15" s="3">
+        <v>0</v>
+      </c>
+      <c r="W15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1203,8 +1254,10 @@
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
-    </row>
-    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V16" s="3"/>
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1232,38 +1285,44 @@
       <c r="K17" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L17" s="3">
+      <c r="L17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N17" s="3">
         <v>4358400</v>
       </c>
-      <c r="M17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P17" s="3">
         <v>3608300</v>
       </c>
-      <c r="O17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R17" s="3">
         <v>3427400</v>
       </c>
-      <c r="Q17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T17" s="3">
         <v>3341200</v>
       </c>
-      <c r="S17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V17" s="3">
         <v>3553900</v>
       </c>
-      <c r="U17" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="W17" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1291,38 +1350,44 @@
       <c r="K18" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L18" s="3">
+      <c r="L18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N18" s="3">
         <v>815800</v>
       </c>
-      <c r="M18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P18" s="3">
         <v>964100</v>
       </c>
-      <c r="O18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R18" s="3">
         <v>649700</v>
       </c>
-      <c r="Q18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T18" s="3">
         <v>643300</v>
       </c>
-      <c r="S18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V18" s="3">
         <v>675200</v>
       </c>
-      <c r="U18" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="W18" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1344,8 +1409,10 @@
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
-    </row>
-    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V19" s="3"/>
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1373,38 +1440,44 @@
       <c r="K20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L20" s="3">
+      <c r="L20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N20" s="3">
         <v>-38800</v>
       </c>
-      <c r="M20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P20" s="3">
         <v>-33300</v>
       </c>
-      <c r="O20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R20" s="3">
         <v>-1600</v>
       </c>
-      <c r="Q20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T20" s="3">
         <v>13400</v>
       </c>
-      <c r="S20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V20" s="3">
         <v>5300</v>
       </c>
-      <c r="U20" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="W20" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1432,38 +1505,44 @@
       <c r="K21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L21" s="3">
+      <c r="L21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N21" s="3">
         <v>1087600</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P21" s="3">
         <v>1547400</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R21" s="3">
         <v>926400</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T21" s="3">
         <v>1244900</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V21" s="3">
         <v>1000600</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="W21" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1491,8 +1570,8 @@
       <c r="K22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L22" s="3">
-        <v>37100</v>
+      <c r="L22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M22" s="3" t="s">
         <v>5</v>
@@ -1504,25 +1583,31 @@
         <v>5</v>
       </c>
       <c r="P22" s="3">
+        <v>37100</v>
+      </c>
+      <c r="Q22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R22" s="3">
         <v>36000</v>
       </c>
-      <c r="Q22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T22" s="3">
         <v>34900</v>
       </c>
-      <c r="S22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V22" s="3">
         <v>34500</v>
       </c>
-      <c r="U22" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="W22" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1550,38 +1635,44 @@
       <c r="K23" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L23" s="3">
+      <c r="L23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N23" s="3">
         <v>739900</v>
       </c>
-      <c r="M23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P23" s="3">
         <v>893700</v>
       </c>
-      <c r="O23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R23" s="3">
         <v>612200</v>
       </c>
-      <c r="Q23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T23" s="3">
         <v>621900</v>
       </c>
-      <c r="S23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V23" s="3">
         <v>646000</v>
       </c>
-      <c r="U23" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="W23" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1609,38 +1700,44 @@
       <c r="K24" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L24" s="3">
+      <c r="L24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N24" s="3">
         <v>162800</v>
       </c>
-      <c r="M24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P24" s="3">
         <v>152500</v>
       </c>
-      <c r="O24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R24" s="3">
         <v>157300</v>
       </c>
-      <c r="Q24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T24" s="3">
         <v>145900</v>
       </c>
-      <c r="S24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V24" s="3">
         <v>168000</v>
       </c>
-      <c r="U24" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="W24" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1698,8 +1795,14 @@
       <c r="U25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1727,38 +1830,44 @@
       <c r="K26" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L26" s="3">
+      <c r="L26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N26" s="3">
         <v>577200</v>
       </c>
-      <c r="M26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P26" s="3">
         <v>741200</v>
       </c>
-      <c r="O26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R26" s="3">
         <v>454900</v>
       </c>
-      <c r="Q26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T26" s="3">
         <v>476000</v>
       </c>
-      <c r="S26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V26" s="3">
         <v>478100</v>
       </c>
-      <c r="U26" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="W26" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1786,38 +1895,44 @@
       <c r="K27" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L27" s="3">
+      <c r="L27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N27" s="3">
         <v>487800</v>
       </c>
-      <c r="M27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P27" s="3">
         <v>642700</v>
       </c>
-      <c r="O27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R27" s="3">
         <v>385800</v>
       </c>
-      <c r="Q27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T27" s="3">
         <v>425800</v>
       </c>
-      <c r="S27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V27" s="3">
         <v>418800</v>
       </c>
-      <c r="U27" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="W27" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1875,8 +1990,14 @@
       <c r="U28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1904,38 +2025,44 @@
       <c r="K29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L29" s="3">
+      <c r="L29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N29" s="3">
         <v>-1258000</v>
       </c>
-      <c r="M29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P29" s="3">
         <v>-87000</v>
       </c>
-      <c r="O29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R29" s="3">
         <v>44700</v>
       </c>
-      <c r="Q29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S29" s="3">
-        <v>0</v>
-      </c>
-      <c r="T29" s="3">
-        <v>0</v>
+      <c r="S29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="U29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1993,8 +2120,14 @@
       <c r="U30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2052,8 +2185,14 @@
       <c r="U31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2081,38 +2220,44 @@
       <c r="K32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L32" s="3">
+      <c r="L32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N32" s="3">
         <v>38800</v>
       </c>
-      <c r="M32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P32" s="3">
         <v>33300</v>
       </c>
-      <c r="O32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R32" s="3">
         <v>1600</v>
       </c>
-      <c r="Q32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T32" s="3">
         <v>-13400</v>
       </c>
-      <c r="S32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V32" s="3">
         <v>-5300</v>
       </c>
-      <c r="U32" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="W32" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -2140,38 +2285,44 @@
       <c r="K33" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L33" s="3">
+      <c r="L33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N33" s="3">
         <v>-770100</v>
       </c>
-      <c r="M33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P33" s="3">
         <v>555700</v>
       </c>
-      <c r="O33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R33" s="3">
         <v>430400</v>
       </c>
-      <c r="Q33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T33" s="3">
         <v>425800</v>
       </c>
-      <c r="S33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V33" s="3">
         <v>418800</v>
       </c>
-      <c r="U33" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="W33" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2229,8 +2380,14 @@
       <c r="U34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -2258,102 +2415,114 @@
       <c r="K35" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L35" s="3">
+      <c r="L35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N35" s="3">
         <v>-770100</v>
       </c>
-      <c r="M35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P35" s="3">
         <v>555700</v>
       </c>
-      <c r="O35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R35" s="3">
         <v>430400</v>
       </c>
-      <c r="Q35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T35" s="3">
         <v>425800</v>
       </c>
-      <c r="S35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V35" s="3">
         <v>418800</v>
       </c>
-      <c r="U35" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="W35" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2375,8 +2544,10 @@
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
-    </row>
-    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V39" s="3"/>
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2398,38 +2569,40 @@
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
-    </row>
-    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V40" s="3"/>
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1602300</v>
+      </c>
+      <c r="E41" s="3">
+        <v>1726300</v>
+      </c>
+      <c r="F41" s="3">
         <v>1538600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>1548900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>1984500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>1898100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>1647100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>1638800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>1172800</v>
       </c>
-      <c r="K41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L41" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M41" s="3" t="s">
         <v>5</v>
       </c>
@@ -2457,43 +2630,49 @@
       <c r="U41" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W41" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>8200</v>
       </c>
       <c r="E42" s="3">
-        <v>0</v>
+        <v>8800</v>
       </c>
       <c r="F42" s="3">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3">
         <v>331600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>317100</v>
       </c>
-      <c r="H42" s="3">
-        <v>0</v>
-      </c>
-      <c r="I42" s="3">
-        <v>0</v>
-      </c>
       <c r="J42" s="3">
         <v>0</v>
       </c>
-      <c r="K42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M42" s="3">
-        <v>0</v>
-      </c>
-      <c r="N42" s="3">
-        <v>0</v>
+      <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N42" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="O42" s="3">
         <v>0</v>
@@ -2516,38 +2695,44 @@
       <c r="U42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V42" s="3">
+        <v>0</v>
+      </c>
+      <c r="W42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1056200</v>
+      </c>
+      <c r="E43" s="3">
+        <v>1137900</v>
+      </c>
+      <c r="F43" s="3">
         <v>1764900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>1776700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>1176600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>1125300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>1798100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>1789000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>1118700</v>
       </c>
-      <c r="K43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L43" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M43" s="3" t="s">
         <v>5</v>
       </c>
@@ -2575,38 +2760,44 @@
       <c r="U43" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W43" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>826400</v>
+      </c>
+      <c r="E44" s="3">
+        <v>890300</v>
+      </c>
+      <c r="F44" s="3">
         <v>936900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>943100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>861800</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>824200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>982100</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>977100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>821600</v>
       </c>
-      <c r="K44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L44" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M44" s="3" t="s">
         <v>5</v>
       </c>
@@ -2634,8 +2825,14 @@
       <c r="U44" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W44" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2651,21 +2848,21 @@
       <c r="G45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H45" s="3">
+      <c r="H45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J45" s="3">
         <v>1478200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>1470800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>1669300</v>
       </c>
-      <c r="K45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L45" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M45" s="3" t="s">
         <v>5</v>
       </c>
@@ -2693,38 +2890,44 @@
       <c r="U45" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W45" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3657500</v>
+      </c>
+      <c r="E46" s="3">
+        <v>3940500</v>
+      </c>
+      <c r="F46" s="3">
         <v>4240400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>4268600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>4478300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>4283200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>5905500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>5875600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>4920800</v>
       </c>
-      <c r="K46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L46" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M46" s="3" t="s">
         <v>5</v>
       </c>
@@ -2752,38 +2955,44 @@
       <c r="U46" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W46" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F47" s="3">
+      <c r="D47" s="3">
+        <v>648900</v>
+      </c>
+      <c r="E47" s="3">
+        <v>699100</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H47" s="3">
         <v>806300</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>771200</v>
       </c>
-      <c r="H47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J47" s="3">
+      <c r="J47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L47" s="3">
         <v>793500</v>
       </c>
-      <c r="K47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L47" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M47" s="3" t="s">
         <v>5</v>
       </c>
@@ -2811,38 +3020,44 @@
       <c r="U47" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W47" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3755100</v>
+      </c>
+      <c r="E48" s="3">
+        <v>4045700</v>
+      </c>
+      <c r="F48" s="3">
         <v>3602900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>3626900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>3619200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>3461500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>3457900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>3440400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>3402200</v>
       </c>
-      <c r="K48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M48" s="3" t="s">
         <v>5</v>
       </c>
@@ -2870,38 +3085,44 @@
       <c r="U48" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W48" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>7272500</v>
+      </c>
+      <c r="E49" s="3">
+        <v>7835200</v>
+      </c>
+      <c r="F49" s="3">
         <v>7070000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>7117200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>7281400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>6964200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>7186600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>7150200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>7072300</v>
       </c>
-      <c r="K49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L49" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M49" s="3" t="s">
         <v>5</v>
       </c>
@@ -2929,8 +3150,14 @@
       <c r="U49" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W49" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2988,8 +3215,14 @@
       <c r="U50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3047,38 +3280,44 @@
       <c r="U51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>27300</v>
+      </c>
+      <c r="E52" s="3">
+        <v>29500</v>
+      </c>
+      <c r="F52" s="3">
         <v>1217500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>1225600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>33200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>31800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>1186800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>1180800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>42000</v>
       </c>
-      <c r="K52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M52" s="3" t="s">
         <v>5</v>
       </c>
@@ -3106,8 +3345,14 @@
       <c r="U52" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W52" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3165,38 +3410,44 @@
       <c r="U53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>15732400</v>
+      </c>
+      <c r="E54" s="3">
+        <v>16949700</v>
+      </c>
+      <c r="F54" s="3">
         <v>16130800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>16238300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>16584200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>15861800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>17736800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>17647100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>16572000</v>
       </c>
-      <c r="K54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L54" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M54" s="3" t="s">
         <v>5</v>
       </c>
@@ -3224,8 +3475,14 @@
       <c r="U54" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W54" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3247,8 +3504,10 @@
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
-    </row>
-    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V55" s="3"/>
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3270,38 +3529,40 @@
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
-    </row>
-    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V56" s="3"/>
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3236900</v>
+      </c>
+      <c r="E57" s="3">
+        <v>3487400</v>
+      </c>
+      <c r="F57" s="3">
         <v>3707200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>3731900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>3286100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>3143000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>3672400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>3653800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>3149000</v>
       </c>
-      <c r="K57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M57" s="3" t="s">
         <v>5</v>
       </c>
@@ -3329,38 +3590,44 @@
       <c r="U57" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W57" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1492100</v>
+      </c>
+      <c r="E58" s="3">
+        <v>1607500</v>
+      </c>
+      <c r="F58" s="3">
         <v>902800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>908900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>1236500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>1182600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>1996400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>1986300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>830600</v>
       </c>
-      <c r="K58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L58" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M58" s="3" t="s">
         <v>5</v>
       </c>
@@ -3388,38 +3655,44 @@
       <c r="U58" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W58" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1663100</v>
+      </c>
+      <c r="E59" s="3">
+        <v>1791800</v>
+      </c>
+      <c r="F59" s="3">
         <v>2535700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>2552600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>2481500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>2373400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>3231600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>3215200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>3024300</v>
       </c>
-      <c r="K59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M59" s="3" t="s">
         <v>5</v>
       </c>
@@ -3447,38 +3720,44 @@
       <c r="U59" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W59" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>6392100</v>
+      </c>
+      <c r="E60" s="3">
+        <v>6886600</v>
+      </c>
+      <c r="F60" s="3">
         <v>7145800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>7193400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>7004100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>6699000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>8900400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>8855300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>7003900</v>
       </c>
-      <c r="K60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L60" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M60" s="3" t="s">
         <v>5</v>
       </c>
@@ -3506,38 +3785,44 @@
       <c r="U60" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W60" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>3802600</v>
+      </c>
+      <c r="E61" s="3">
+        <v>4096800</v>
+      </c>
+      <c r="F61" s="3">
         <v>4424300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>4453800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>4562100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>4363300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>3103800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>3088100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>3285200</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
@@ -3565,38 +3850,44 @@
       <c r="U61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V61" s="3">
+        <v>0</v>
+      </c>
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>448500</v>
+      </c>
+      <c r="E62" s="3">
+        <v>483200</v>
+      </c>
+      <c r="F62" s="3">
         <v>1112300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>1119700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>278700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>266500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>1230500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>1224300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>374900</v>
       </c>
-      <c r="K62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L62" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M62" s="3" t="s">
         <v>5</v>
       </c>
@@ -3624,8 +3915,14 @@
       <c r="U62" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W62" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3683,8 +3980,14 @@
       <c r="U63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3742,8 +4045,14 @@
       <c r="U64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3801,38 +4110,44 @@
       <c r="U65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>11482800</v>
+      </c>
+      <c r="E66" s="3">
+        <v>12371200</v>
+      </c>
+      <c r="F66" s="3">
         <v>12682400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>12766900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>12765700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>12209600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>13234700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>13167700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>11583200</v>
       </c>
-      <c r="K66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L66" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M66" s="3" t="s">
         <v>5</v>
       </c>
@@ -3860,8 +4175,14 @@
       <c r="U66" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W66" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3883,8 +4204,10 @@
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
-    </row>
-    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V67" s="3"/>
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3942,8 +4265,14 @@
       <c r="U68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4001,8 +4330,14 @@
       <c r="U69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4060,8 +4395,14 @@
       <c r="U70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V70" s="3">
+        <v>0</v>
+      </c>
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4119,38 +4460,44 @@
       <c r="U71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>3551300</v>
+      </c>
+      <c r="E72" s="3">
+        <v>3826100</v>
+      </c>
+      <c r="F72" s="3">
         <v>3086700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>3107300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>3456200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>3305700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>10183900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>10132400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>10169000</v>
       </c>
-      <c r="K72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M72" s="3" t="s">
         <v>5</v>
       </c>
@@ -4178,8 +4525,14 @@
       <c r="U72" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W72" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4237,8 +4590,14 @@
       <c r="U73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4296,8 +4655,14 @@
       <c r="U74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4355,38 +4720,44 @@
       <c r="U75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3855200</v>
+      </c>
+      <c r="E76" s="3">
+        <v>4153500</v>
+      </c>
+      <c r="F76" s="3">
         <v>3112100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>3132900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>3445500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>3295400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>4146100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>4125100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>4583600</v>
       </c>
-      <c r="K76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L76" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M76" s="3" t="s">
         <v>5</v>
       </c>
@@ -4414,8 +4785,14 @@
       <c r="U76" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W76" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4473,72 +4850,84 @@
       <c r="U77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -4566,38 +4955,44 @@
       <c r="K81" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L81" s="3">
+      <c r="L81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N81" s="3">
         <v>-770100</v>
       </c>
-      <c r="M81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P81" s="3">
         <v>555700</v>
       </c>
-      <c r="O81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R81" s="3">
         <v>430400</v>
       </c>
-      <c r="Q81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T81" s="3">
         <v>425800</v>
       </c>
-      <c r="S81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V81" s="3">
         <v>418800</v>
       </c>
-      <c r="U81" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="W81" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4619,67 +5014,75 @@
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
-    </row>
-    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V82" s="3"/>
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>136100</v>
+      </c>
+      <c r="E83" s="3">
+        <v>130200</v>
+      </c>
+      <c r="F83" s="3">
         <v>143400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>142700</v>
       </c>
-      <c r="F83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H83" s="3">
+      <c r="H83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J83" s="3">
         <v>149700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>158800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>169300</v>
       </c>
-      <c r="K83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N83" s="3">
         <v>310600</v>
       </c>
-      <c r="M83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P83" s="3">
         <v>671000</v>
       </c>
-      <c r="O83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R83" s="3">
         <v>303500</v>
       </c>
-      <c r="Q83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T83" s="3">
         <v>588200</v>
       </c>
-      <c r="S83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V83" s="3">
         <v>320100</v>
       </c>
-      <c r="U83" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="W83" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4737,8 +5140,14 @@
       <c r="U84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4796,8 +5205,14 @@
       <c r="U85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4855,8 +5270,14 @@
       <c r="U86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4914,8 +5335,14 @@
       <c r="U87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4973,67 +5400,79 @@
       <c r="U88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
+      <c r="D89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F89" s="3">
         <v>422500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>425300</v>
       </c>
-      <c r="F89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G89" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="H89" s="3">
+        <v>183800</v>
+      </c>
+      <c r="I89" s="3">
+        <v>175800</v>
+      </c>
+      <c r="J89" s="3">
         <v>596100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>593100</v>
       </c>
-      <c r="J89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L89" s="3">
+      <c r="L89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N89" s="3">
         <v>1223200</v>
       </c>
-      <c r="M89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P89" s="3">
         <v>1929200</v>
       </c>
-      <c r="O89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R89" s="3">
         <v>950500</v>
       </c>
-      <c r="Q89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T89" s="3">
         <v>1465600</v>
       </c>
-      <c r="S89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V89" s="3">
         <v>749900</v>
       </c>
-      <c r="U89" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="W89" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5055,37 +5494,39 @@
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
-    </row>
-    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V90" s="3"/>
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
+      <c r="D91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F91" s="3">
         <v>-163700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-164800</v>
       </c>
-      <c r="F91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G91" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="H91" s="3">
+        <v>-155300</v>
+      </c>
+      <c r="I91" s="3">
+        <v>-148600</v>
+      </c>
+      <c r="J91" s="3">
         <v>-131300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-130700</v>
       </c>
-      <c r="J91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K91" s="3">
-        <v>0</v>
-      </c>
-      <c r="L91" s="3">
-        <v>0</v>
+      <c r="L91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M91" s="3">
         <v>0</v>
@@ -5097,25 +5538,31 @@
         <v>0</v>
       </c>
       <c r="P91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+      <c r="R91" s="3">
         <v>-235900</v>
       </c>
-      <c r="Q91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T91" s="3">
         <v>-589500</v>
       </c>
-      <c r="S91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V91" s="3">
         <v>-363900</v>
       </c>
-      <c r="U91" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="W91" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5173,8 +5620,14 @@
       <c r="U92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5232,67 +5685,79 @@
       <c r="U93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
+      <c r="D94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F94" s="3">
         <v>8800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>8800</v>
       </c>
-      <c r="F94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G94" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="H94" s="3">
+        <v>-326600</v>
+      </c>
+      <c r="I94" s="3">
+        <v>-312400</v>
+      </c>
+      <c r="J94" s="3">
         <v>-170300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-169500</v>
       </c>
-      <c r="J94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L94" s="3">
+      <c r="L94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N94" s="3">
         <v>-158500</v>
       </c>
-      <c r="M94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P94" s="3">
         <v>-591700</v>
       </c>
-      <c r="O94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R94" s="3">
         <v>-179600</v>
       </c>
-      <c r="Q94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T94" s="3">
         <v>-787400</v>
       </c>
-      <c r="S94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V94" s="3">
         <v>-289100</v>
       </c>
-      <c r="U94" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="W94" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5314,67 +5779,75 @@
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
-    </row>
-    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V95" s="3"/>
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
+      <c r="D96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F96" s="3">
         <v>258700</v>
       </c>
-      <c r="E96" s="3">
+      <c r="G96" s="3">
         <v>260400</v>
       </c>
-      <c r="F96" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G96" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="H96" s="3">
+        <v>0</v>
+      </c>
+      <c r="I96" s="3">
+        <v>0</v>
+      </c>
+      <c r="J96" s="3">
         <v>270800</v>
       </c>
-      <c r="I96" s="3">
+      <c r="K96" s="3">
         <v>269400</v>
       </c>
-      <c r="J96" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
-      <c r="L96" s="3">
+      <c r="L96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M96" s="3">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3">
         <v>-494700</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3">
         <v>-463700</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3">
         <v>-453200</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
-      </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
+        <v>0</v>
+      </c>
+      <c r="T96" s="3">
         <v>-414800</v>
       </c>
-      <c r="S96" s="3">
-        <v>0</v>
-      </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+      <c r="V96" s="3">
         <v>-453700</v>
       </c>
-      <c r="U96" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5432,8 +5905,14 @@
       <c r="U97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5491,8 +5970,14 @@
       <c r="U98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5550,181 +6035,205 @@
       <c r="U99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
+      <c r="D100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F100" s="3">
         <v>-624700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-628900</v>
       </c>
-      <c r="F100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G100" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="H100" s="3">
+        <v>123800</v>
+      </c>
+      <c r="I100" s="3">
+        <v>118400</v>
+      </c>
+      <c r="J100" s="3">
         <v>-22000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-21900</v>
       </c>
-      <c r="J100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L100" s="3">
+      <c r="L100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N100" s="3">
         <v>-328100</v>
       </c>
-      <c r="M100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P100" s="3">
         <v>-1301500</v>
       </c>
-      <c r="O100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R100" s="3">
         <v>-713100</v>
       </c>
-      <c r="Q100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T100" s="3">
         <v>-242700</v>
       </c>
-      <c r="S100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V100" s="3">
         <v>-73200</v>
       </c>
-      <c r="U100" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="W100" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-15900</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-15200</v>
+      </c>
+      <c r="F101" s="3">
         <v>-74400</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-74000</v>
       </c>
-      <c r="F101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H101" s="3">
+      <c r="H101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J101" s="3">
         <v>27500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>29200</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>22900</v>
       </c>
-      <c r="K101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N101" s="3">
         <v>57100</v>
       </c>
-      <c r="M101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P101" s="3">
         <v>66600</v>
       </c>
-      <c r="O101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R101" s="3">
         <v>22600</v>
       </c>
-      <c r="Q101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T101" s="3">
         <v>-58700</v>
       </c>
-      <c r="S101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V101" s="3">
         <v>-16700</v>
       </c>
-      <c r="U101" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="W101" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3">
+        <v>0</v>
+      </c>
+      <c r="F102" s="3">
         <v>-192000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-193300</v>
       </c>
-      <c r="F102" s="3">
-        <v>0</v>
-      </c>
-      <c r="G102" s="3">
-        <v>0</v>
-      </c>
       <c r="H102" s="3">
+        <v>-34800</v>
+      </c>
+      <c r="I102" s="3">
+        <v>-33300</v>
+      </c>
+      <c r="J102" s="3">
         <v>329400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>327800</v>
       </c>
-      <c r="J102" s="3">
-        <v>0</v>
-      </c>
-      <c r="K102" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L102" s="3">
+        <v>0</v>
+      </c>
+      <c r="M102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N102" s="3">
         <v>793600</v>
       </c>
-      <c r="M102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P102" s="3">
         <v>56200</v>
       </c>
-      <c r="O102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R102" s="3">
         <v>59400</v>
       </c>
-      <c r="Q102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T102" s="3">
         <v>376700</v>
       </c>
-      <c r="S102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V102" s="3">
         <v>370800</v>
       </c>
-      <c r="U102" s="3" t="s">
+      <c r="W102" s="3" t="s">
         <v>5</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CABGY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CABGY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="655" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="699" uniqueCount="92">
   <si>
     <t>CABGY</t>
   </si>
@@ -656,106 +656,114 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:W102"/>
+  <dimension ref="A5:Y102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -786,41 +794,47 @@
       <c r="L8" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M8" s="3">
+      <c r="M8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O8" s="3">
         <v>2932900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>5174200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>2173500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>4572300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>2586000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>4077200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>1620100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>3984500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>2407800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>4229100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>1899000</v>
       </c>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -854,38 +868,44 @@
       <c r="M9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N9" s="3">
+      <c r="N9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P9" s="3">
         <v>2780100</v>
       </c>
-      <c r="O9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R9" s="3">
         <v>2415700</v>
       </c>
-      <c r="Q9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T9" s="3">
         <v>2122300</v>
       </c>
-      <c r="S9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V9" s="3">
         <v>2061000</v>
       </c>
-      <c r="U9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X9" s="3">
         <v>2172800</v>
       </c>
-      <c r="W9" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="Y9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -919,38 +939,44 @@
       <c r="M10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N10" s="3">
+      <c r="N10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P10" s="3">
         <v>2394100</v>
       </c>
-      <c r="O10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R10" s="3">
         <v>2156600</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T10" s="3">
         <v>1954800</v>
       </c>
-      <c r="S10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V10" s="3">
         <v>1923500</v>
       </c>
-      <c r="U10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X10" s="3">
         <v>2056300</v>
       </c>
-      <c r="W10" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="Y10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -974,8 +1000,10 @@
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X11" s="3"/>
+      <c r="Y11" s="3"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1039,8 +1067,14 @@
       <c r="W12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1104,8 +1138,14 @@
       <c r="W13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1139,38 +1179,44 @@
       <c r="M14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N14" s="3">
+      <c r="N14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P14" s="3">
         <v>124500</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R14" s="3">
         <v>-34900</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T14" s="3">
         <v>28200</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V14" s="3">
         <v>38500</v>
       </c>
-      <c r="U14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X14" s="3">
         <v>1800</v>
       </c>
-      <c r="W14" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="Y14" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1201,11 +1247,11 @@
       <c r="L15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M15" s="3">
-        <v>0</v>
-      </c>
-      <c r="N15" s="3">
-        <v>0</v>
+      <c r="M15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N15" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="O15" s="3">
         <v>0</v>
@@ -1234,8 +1280,14 @@
       <c r="W15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1256,8 +1308,10 @@
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
-    </row>
-    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X16" s="3"/>
+      <c r="Y16" s="3"/>
+    </row>
+    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1291,38 +1345,44 @@
       <c r="M17" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N17" s="3">
+      <c r="N17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P17" s="3">
         <v>4358400</v>
       </c>
-      <c r="O17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R17" s="3">
         <v>3608300</v>
       </c>
-      <c r="Q17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T17" s="3">
         <v>3427400</v>
       </c>
-      <c r="S17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V17" s="3">
         <v>3341200</v>
       </c>
-      <c r="U17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X17" s="3">
         <v>3553900</v>
       </c>
-      <c r="W17" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="Y17" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1356,38 +1416,44 @@
       <c r="M18" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N18" s="3">
+      <c r="N18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P18" s="3">
         <v>815800</v>
       </c>
-      <c r="O18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R18" s="3">
         <v>964100</v>
       </c>
-      <c r="Q18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T18" s="3">
         <v>649700</v>
       </c>
-      <c r="S18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V18" s="3">
         <v>643300</v>
       </c>
-      <c r="U18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X18" s="3">
         <v>675200</v>
       </c>
-      <c r="W18" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="Y18" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1411,8 +1477,10 @@
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
-    </row>
-    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X19" s="3"/>
+      <c r="Y19" s="3"/>
+    </row>
+    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1446,38 +1514,44 @@
       <c r="M20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N20" s="3">
+      <c r="N20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P20" s="3">
         <v>-38800</v>
       </c>
-      <c r="O20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R20" s="3">
         <v>-33300</v>
       </c>
-      <c r="Q20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T20" s="3">
         <v>-1600</v>
       </c>
-      <c r="S20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V20" s="3">
         <v>13400</v>
       </c>
-      <c r="U20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X20" s="3">
         <v>5300</v>
       </c>
-      <c r="W20" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="Y20" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1511,38 +1585,44 @@
       <c r="M21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N21" s="3">
+      <c r="N21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P21" s="3">
         <v>1087600</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R21" s="3">
         <v>1547400</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T21" s="3">
         <v>926400</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V21" s="3">
         <v>1244900</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X21" s="3">
         <v>1000600</v>
       </c>
-      <c r="W21" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="Y21" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1576,8 +1656,8 @@
       <c r="M22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N22" s="3">
-        <v>37100</v>
+      <c r="N22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="O22" s="3" t="s">
         <v>5</v>
@@ -1589,25 +1669,31 @@
         <v>5</v>
       </c>
       <c r="R22" s="3">
+        <v>37100</v>
+      </c>
+      <c r="S22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T22" s="3">
         <v>36000</v>
       </c>
-      <c r="S22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V22" s="3">
         <v>34900</v>
       </c>
-      <c r="U22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X22" s="3">
         <v>34500</v>
       </c>
-      <c r="W22" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="Y22" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1641,38 +1727,44 @@
       <c r="M23" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N23" s="3">
+      <c r="N23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P23" s="3">
         <v>739900</v>
       </c>
-      <c r="O23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R23" s="3">
         <v>893700</v>
       </c>
-      <c r="Q23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T23" s="3">
         <v>612200</v>
       </c>
-      <c r="S23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V23" s="3">
         <v>621900</v>
       </c>
-      <c r="U23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X23" s="3">
         <v>646000</v>
       </c>
-      <c r="W23" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="Y23" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1706,38 +1798,44 @@
       <c r="M24" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N24" s="3">
+      <c r="N24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P24" s="3">
         <v>162800</v>
       </c>
-      <c r="O24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R24" s="3">
         <v>152500</v>
       </c>
-      <c r="Q24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T24" s="3">
         <v>157300</v>
       </c>
-      <c r="S24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V24" s="3">
         <v>145900</v>
       </c>
-      <c r="U24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X24" s="3">
         <v>168000</v>
       </c>
-      <c r="W24" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="Y24" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1801,8 +1899,14 @@
       <c r="W25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1836,38 +1940,44 @@
       <c r="M26" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N26" s="3">
+      <c r="N26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P26" s="3">
         <v>577200</v>
       </c>
-      <c r="O26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R26" s="3">
         <v>741200</v>
       </c>
-      <c r="Q26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T26" s="3">
         <v>454900</v>
       </c>
-      <c r="S26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V26" s="3">
         <v>476000</v>
       </c>
-      <c r="U26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X26" s="3">
         <v>478100</v>
       </c>
-      <c r="W26" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="Y26" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1901,38 +2011,44 @@
       <c r="M27" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N27" s="3">
+      <c r="N27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P27" s="3">
         <v>487800</v>
       </c>
-      <c r="O27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R27" s="3">
         <v>642700</v>
       </c>
-      <c r="Q27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T27" s="3">
         <v>385800</v>
       </c>
-      <c r="S27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V27" s="3">
         <v>425800</v>
       </c>
-      <c r="U27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X27" s="3">
         <v>418800</v>
       </c>
-      <c r="W27" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="Y27" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1996,8 +2112,14 @@
       <c r="W28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2031,38 +2153,44 @@
       <c r="M29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N29" s="3">
+      <c r="N29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P29" s="3">
         <v>-1258000</v>
       </c>
-      <c r="O29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R29" s="3">
         <v>-87000</v>
       </c>
-      <c r="Q29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T29" s="3">
         <v>44700</v>
       </c>
-      <c r="S29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U29" s="3">
-        <v>0</v>
-      </c>
-      <c r="V29" s="3">
-        <v>0</v>
+      <c r="U29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="W29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2126,8 +2254,14 @@
       <c r="W30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2191,8 +2325,14 @@
       <c r="W31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2226,38 +2366,44 @@
       <c r="M32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N32" s="3">
+      <c r="N32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P32" s="3">
         <v>38800</v>
       </c>
-      <c r="O32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R32" s="3">
         <v>33300</v>
       </c>
-      <c r="Q32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T32" s="3">
         <v>1600</v>
       </c>
-      <c r="S32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V32" s="3">
         <v>-13400</v>
       </c>
-      <c r="U32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X32" s="3">
         <v>-5300</v>
       </c>
-      <c r="W32" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="Y32" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -2291,38 +2437,44 @@
       <c r="M33" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N33" s="3">
+      <c r="N33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P33" s="3">
         <v>-770100</v>
       </c>
-      <c r="O33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R33" s="3">
         <v>555700</v>
       </c>
-      <c r="Q33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T33" s="3">
         <v>430400</v>
       </c>
-      <c r="S33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V33" s="3">
         <v>425800</v>
       </c>
-      <c r="U33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X33" s="3">
         <v>418800</v>
       </c>
-      <c r="W33" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="Y33" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2386,8 +2538,14 @@
       <c r="W34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -2421,108 +2579,120 @@
       <c r="M35" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N35" s="3">
+      <c r="N35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P35" s="3">
         <v>-770100</v>
       </c>
-      <c r="O35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R35" s="3">
         <v>555700</v>
       </c>
-      <c r="Q35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T35" s="3">
         <v>430400</v>
       </c>
-      <c r="S35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V35" s="3">
         <v>425800</v>
       </c>
-      <c r="U35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X35" s="3">
         <v>418800</v>
       </c>
-      <c r="W35" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="Y35" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2546,8 +2716,10 @@
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
-    </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X39" s="3"/>
+      <c r="Y39" s="3"/>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2571,44 +2743,46 @@
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
-    </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X40" s="3"/>
+      <c r="Y40" s="3"/>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1487300</v>
+      </c>
+      <c r="E41" s="3">
+        <v>1368800</v>
+      </c>
+      <c r="F41" s="3">
         <v>1602300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>1726300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>1538600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>1548900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>1984500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>1898100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>1647100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>1638800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>1172800</v>
       </c>
-      <c r="M41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N41" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O41" s="3" t="s">
         <v>5</v>
       </c>
@@ -2636,49 +2810,55 @@
       <c r="W41" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y41" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>102800</v>
+      </c>
+      <c r="E42" s="3">
+        <v>94600</v>
+      </c>
+      <c r="F42" s="3">
         <v>8200</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>8800</v>
       </c>
-      <c r="F42" s="3">
-        <v>0</v>
-      </c>
-      <c r="G42" s="3">
-        <v>0</v>
-      </c>
       <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
         <v>331600</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>317100</v>
       </c>
-      <c r="J42" s="3">
-        <v>0</v>
-      </c>
-      <c r="K42" s="3">
-        <v>0</v>
-      </c>
       <c r="L42" s="3">
         <v>0</v>
       </c>
-      <c r="M42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O42" s="3">
-        <v>0</v>
-      </c>
-      <c r="P42" s="3">
-        <v>0</v>
+      <c r="M42" s="3">
+        <v>0</v>
+      </c>
+      <c r="N42" s="3">
+        <v>0</v>
+      </c>
+      <c r="O42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P42" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q42" s="3">
         <v>0</v>
@@ -2701,44 +2881,50 @@
       <c r="W42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2600900</v>
+      </c>
+      <c r="E43" s="3">
+        <v>2393700</v>
+      </c>
+      <c r="F43" s="3">
         <v>1056200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>1137900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>1764900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>1776700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>1176600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>1125300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>1798100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>1789000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>1118700</v>
       </c>
-      <c r="M43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N43" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O43" s="3" t="s">
         <v>5</v>
       </c>
@@ -2766,44 +2952,50 @@
       <c r="W43" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y43" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1262400</v>
+      </c>
+      <c r="E44" s="3">
+        <v>1161900</v>
+      </c>
+      <c r="F44" s="3">
         <v>826400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>890300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>936900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>943100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>861800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>824200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>982100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>977100</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>821600</v>
       </c>
-      <c r="M44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N44" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O44" s="3" t="s">
         <v>5</v>
       </c>
@@ -2831,8 +3023,14 @@
       <c r="W44" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y44" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2854,21 +3052,21 @@
       <c r="I45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J45" s="3">
+      <c r="J45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L45" s="3">
         <v>1478200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>1470800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>1669300</v>
       </c>
-      <c r="M45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N45" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O45" s="3" t="s">
         <v>5</v>
       </c>
@@ -2896,44 +3094,50 @@
       <c r="W45" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y45" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>5453400</v>
+      </c>
+      <c r="E46" s="3">
+        <v>5019000</v>
+      </c>
+      <c r="F46" s="3">
         <v>3657500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>3940500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>4240400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>4268600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>4478300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>4283200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>5905500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>5875600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>4920800</v>
       </c>
-      <c r="M46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N46" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O46" s="3" t="s">
         <v>5</v>
       </c>
@@ -2961,44 +3165,50 @@
       <c r="W46" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y46" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
+      <c r="D47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F47" s="3">
         <v>648900</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>699100</v>
       </c>
-      <c r="F47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H47" s="3">
+      <c r="H47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J47" s="3">
         <v>806300</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>771200</v>
       </c>
-      <c r="J47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L47" s="3">
+      <c r="L47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N47" s="3">
         <v>793500</v>
       </c>
-      <c r="M47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N47" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O47" s="3" t="s">
         <v>5</v>
       </c>
@@ -3026,44 +3236,50 @@
       <c r="W47" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y47" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>4874100</v>
+      </c>
+      <c r="E48" s="3">
+        <v>4485800</v>
+      </c>
+      <c r="F48" s="3">
         <v>3755100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>4045700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>3602900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>3626900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>3619200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>3461500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>3457900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>3440400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>3402200</v>
       </c>
-      <c r="M48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O48" s="3" t="s">
         <v>5</v>
       </c>
@@ -3091,44 +3307,50 @@
       <c r="W48" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y48" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>12758300</v>
+      </c>
+      <c r="E49" s="3">
+        <v>11741900</v>
+      </c>
+      <c r="F49" s="3">
         <v>7272500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>7835200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>7070000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>7117200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>7281400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>6964200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>7186600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>7150200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>7072300</v>
       </c>
-      <c r="M49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N49" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O49" s="3" t="s">
         <v>5</v>
       </c>
@@ -3156,8 +3378,14 @@
       <c r="W49" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y49" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3221,8 +3449,14 @@
       <c r="W50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3286,44 +3520,50 @@
       <c r="W51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1256500</v>
+      </c>
+      <c r="E52" s="3">
+        <v>1156400</v>
+      </c>
+      <c r="F52" s="3">
         <v>27300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>29500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>1217500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>1225600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>33200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>31800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>1186800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>1180800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>42000</v>
       </c>
-      <c r="M52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O52" s="3" t="s">
         <v>5</v>
       </c>
@@ -3351,8 +3591,14 @@
       <c r="W52" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y52" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3416,44 +3662,50 @@
       <c r="W53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>24342300</v>
+      </c>
+      <c r="E54" s="3">
+        <v>22403100</v>
+      </c>
+      <c r="F54" s="3">
         <v>15732400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>16949700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>16130800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>16238300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>16584200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>15861800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>17736800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>17647100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>16572000</v>
       </c>
-      <c r="M54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N54" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O54" s="3" t="s">
         <v>5</v>
       </c>
@@ -3481,8 +3733,14 @@
       <c r="W54" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y54" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3506,8 +3764,10 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
-    </row>
-    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X55" s="3"/>
+      <c r="Y55" s="3"/>
+    </row>
+    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3531,44 +3791,46 @@
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
-    </row>
-    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X56" s="3"/>
+      <c r="Y56" s="3"/>
+    </row>
+    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>4531800</v>
+      </c>
+      <c r="E57" s="3">
+        <v>4170800</v>
+      </c>
+      <c r="F57" s="3">
         <v>3236900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>3487400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>3707200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>3731900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>3286100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>3143000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>3672400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>3653800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>3149000</v>
       </c>
-      <c r="M57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O57" s="3" t="s">
         <v>5</v>
       </c>
@@ -3596,44 +3858,50 @@
       <c r="W57" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y57" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1144400</v>
+      </c>
+      <c r="E58" s="3">
+        <v>1053200</v>
+      </c>
+      <c r="F58" s="3">
         <v>1492100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>1607500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>902800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>908900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>1236500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>1182600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>1996400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>1986300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>830600</v>
       </c>
-      <c r="M58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N58" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O58" s="3" t="s">
         <v>5</v>
       </c>
@@ -3661,44 +3929,50 @@
       <c r="W58" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y58" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2143700</v>
+      </c>
+      <c r="E59" s="3">
+        <v>1973000</v>
+      </c>
+      <c r="F59" s="3">
         <v>1663100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>1791800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>2535700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>2552600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>2481500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>2373400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>3231600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>3215200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>3024300</v>
       </c>
-      <c r="M59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O59" s="3" t="s">
         <v>5</v>
       </c>
@@ -3726,44 +4000,50 @@
       <c r="W59" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y59" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>7819900</v>
+      </c>
+      <c r="E60" s="3">
+        <v>7197000</v>
+      </c>
+      <c r="F60" s="3">
         <v>6392100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>6886600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>7145800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>7193400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>7004100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>6699000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>8900400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>8855300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>7003900</v>
       </c>
-      <c r="M60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N60" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O60" s="3" t="s">
         <v>5</v>
       </c>
@@ -3791,44 +4071,50 @@
       <c r="W60" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y60" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>10518200</v>
+      </c>
+      <c r="E61" s="3">
+        <v>9680300</v>
+      </c>
+      <c r="F61" s="3">
         <v>3802600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>4096800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>4424300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>4453800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>4562100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>4363300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>3103800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>3088100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>3285200</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
       <c r="O61" s="3">
         <v>0</v>
       </c>
@@ -3856,44 +4142,50 @@
       <c r="W61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1632400</v>
+      </c>
+      <c r="E62" s="3">
+        <v>1502400</v>
+      </c>
+      <c r="F62" s="3">
         <v>448500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>483200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>1112300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>1119700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>278700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>266500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>1230500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>1224300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>374900</v>
       </c>
-      <c r="M62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N62" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O62" s="3" t="s">
         <v>5</v>
       </c>
@@ -3921,8 +4213,14 @@
       <c r="W62" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y62" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3986,8 +4284,14 @@
       <c r="W63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4051,8 +4355,14 @@
       <c r="W64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4116,44 +4426,50 @@
       <c r="W65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>19970500</v>
+      </c>
+      <c r="E66" s="3">
+        <v>18379600</v>
+      </c>
+      <c r="F66" s="3">
         <v>11482800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>12371200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>12682400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>12766900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>12765700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>12209600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>13234700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>13167700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>11583200</v>
       </c>
-      <c r="M66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N66" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O66" s="3" t="s">
         <v>5</v>
       </c>
@@ -4181,8 +4497,14 @@
       <c r="W66" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y66" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4206,8 +4528,10 @@
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
-    </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X67" s="3"/>
+      <c r="Y67" s="3"/>
+    </row>
+    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4271,8 +4595,14 @@
       <c r="W68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4336,8 +4666,14 @@
       <c r="W69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4401,8 +4737,14 @@
       <c r="W70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4466,44 +4808,50 @@
       <c r="W71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>4033400</v>
+      </c>
+      <c r="E72" s="3">
+        <v>3712100</v>
+      </c>
+      <c r="F72" s="3">
         <v>3551300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>3826100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>3086700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>3107300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>3456200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>3305700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>10183900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>10132400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>10169000</v>
       </c>
-      <c r="M72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O72" s="3" t="s">
         <v>5</v>
       </c>
@@ -4531,8 +4879,14 @@
       <c r="W72" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y72" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4596,8 +4950,14 @@
       <c r="W73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4661,8 +5021,14 @@
       <c r="W74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4726,44 +5092,50 @@
       <c r="W75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3939100</v>
+      </c>
+      <c r="E76" s="3">
+        <v>3625300</v>
+      </c>
+      <c r="F76" s="3">
         <v>3855200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>4153500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>3112100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>3132900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>3445500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>3295400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>4146100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>4125100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>4583600</v>
       </c>
-      <c r="M76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N76" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O76" s="3" t="s">
         <v>5</v>
       </c>
@@ -4791,8 +5163,14 @@
       <c r="W76" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y76" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4856,78 +5234,90 @@
       <c r="W77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -4961,38 +5351,44 @@
       <c r="M81" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N81" s="3">
+      <c r="N81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P81" s="3">
         <v>-770100</v>
       </c>
-      <c r="O81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R81" s="3">
         <v>555700</v>
       </c>
-      <c r="Q81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T81" s="3">
         <v>430400</v>
       </c>
-      <c r="S81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V81" s="3">
         <v>425800</v>
       </c>
-      <c r="U81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X81" s="3">
         <v>418800</v>
       </c>
-      <c r="W81" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="Y81" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5016,73 +5412,81 @@
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
-    </row>
-    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X82" s="3"/>
+      <c r="Y82" s="3"/>
+    </row>
+    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>149900</v>
+      </c>
+      <c r="E83" s="3">
+        <v>150900</v>
+      </c>
+      <c r="F83" s="3">
         <v>136100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>130200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>143400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>142700</v>
       </c>
-      <c r="H83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J83" s="3">
+      <c r="J83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L83" s="3">
         <v>149700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>158800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>169300</v>
       </c>
-      <c r="M83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P83" s="3">
         <v>310600</v>
       </c>
-      <c r="O83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R83" s="3">
         <v>671000</v>
       </c>
-      <c r="Q83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T83" s="3">
         <v>303500</v>
       </c>
-      <c r="S83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V83" s="3">
         <v>588200</v>
       </c>
-      <c r="U83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X83" s="3">
         <v>320100</v>
       </c>
-      <c r="W83" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="Y83" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5146,8 +5550,14 @@
       <c r="W84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5211,8 +5621,14 @@
       <c r="W85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5276,8 +5692,14 @@
       <c r="W86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5341,8 +5763,14 @@
       <c r="W87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5406,73 +5834,85 @@
       <c r="W88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F89" s="3">
+      <c r="D89" s="3">
+        <v>418000</v>
+      </c>
+      <c r="E89" s="3">
+        <v>384700</v>
+      </c>
+      <c r="F89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H89" s="3">
         <v>422500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>425300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>183800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>175800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>596100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>593100</v>
       </c>
-      <c r="L89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N89" s="3">
+      <c r="N89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P89" s="3">
         <v>1223200</v>
       </c>
-      <c r="O89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R89" s="3">
         <v>1929200</v>
       </c>
-      <c r="Q89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T89" s="3">
         <v>950500</v>
       </c>
-      <c r="S89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V89" s="3">
         <v>1465600</v>
       </c>
-      <c r="U89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X89" s="3">
         <v>749900</v>
       </c>
-      <c r="W89" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="Y89" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5496,43 +5936,45 @@
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
-    </row>
-    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X90" s="3"/>
+      <c r="Y90" s="3"/>
+    </row>
+    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F91" s="3">
-        <v>-163700</v>
-      </c>
-      <c r="G91" s="3">
-        <v>-164800</v>
+      <c r="D91" s="3">
+        <v>-198000</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-182300</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H91" s="3">
+        <v>-156700</v>
+      </c>
+      <c r="I91" s="3">
+        <v>-157700</v>
+      </c>
+      <c r="J91" s="3">
         <v>-155300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-148600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-131300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-130700</v>
       </c>
-      <c r="L91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
-      <c r="N91" s="3">
-        <v>0</v>
+      <c r="N91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="O91" s="3">
         <v>0</v>
@@ -5544,25 +5986,31 @@
         <v>0</v>
       </c>
       <c r="R91" s="3">
+        <v>0</v>
+      </c>
+      <c r="S91" s="3">
+        <v>0</v>
+      </c>
+      <c r="T91" s="3">
         <v>-235900</v>
       </c>
-      <c r="S91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V91" s="3">
         <v>-589500</v>
       </c>
-      <c r="U91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X91" s="3">
         <v>-363900</v>
       </c>
-      <c r="W91" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="Y91" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5626,8 +6074,14 @@
       <c r="W92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5691,73 +6145,85 @@
       <c r="W93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F94" s="3">
+      <c r="D94" s="3">
+        <v>-2519300</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-2318600</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H94" s="3">
         <v>8800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>8800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-326600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-312400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-170300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-169500</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N94" s="3">
+      <c r="N94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P94" s="3">
         <v>-158500</v>
       </c>
-      <c r="O94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R94" s="3">
         <v>-591700</v>
       </c>
-      <c r="Q94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T94" s="3">
         <v>-179600</v>
       </c>
-      <c r="S94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V94" s="3">
         <v>-787400</v>
       </c>
-      <c r="U94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X94" s="3">
         <v>-289100</v>
       </c>
-      <c r="W94" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="Y94" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5781,73 +6247,81 @@
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
-    </row>
-    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X95" s="3"/>
+      <c r="Y95" s="3"/>
+    </row>
+    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E96" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F96" s="3">
+      <c r="D96" s="3">
+        <v>280900</v>
+      </c>
+      <c r="E96" s="3">
+        <v>258600</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H96" s="3">
         <v>258700</v>
       </c>
-      <c r="G96" s="3">
+      <c r="I96" s="3">
         <v>260400</v>
       </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
       <c r="J96" s="3">
+        <v>0</v>
+      </c>
+      <c r="K96" s="3">
+        <v>0</v>
+      </c>
+      <c r="L96" s="3">
         <v>270800</v>
       </c>
-      <c r="K96" s="3">
+      <c r="M96" s="3">
         <v>269400</v>
       </c>
-      <c r="L96" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
-      <c r="N96" s="3">
+      <c r="N96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3">
         <v>-494700</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3">
         <v>-463700</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
-      </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
+        <v>0</v>
+      </c>
+      <c r="T96" s="3">
         <v>-453200</v>
       </c>
-      <c r="S96" s="3">
-        <v>0</v>
-      </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+      <c r="V96" s="3">
         <v>-414800</v>
       </c>
-      <c r="U96" s="3">
-        <v>0</v>
-      </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+      <c r="X96" s="3">
         <v>-453700</v>
       </c>
-      <c r="W96" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5911,8 +6385,14 @@
       <c r="W97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5976,8 +6456,14 @@
       <c r="W98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6041,199 +6527,223 @@
       <c r="W99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F100" s="3">
+      <c r="D100" s="3">
+        <v>1937000</v>
+      </c>
+      <c r="E100" s="3">
+        <v>1782700</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H100" s="3">
         <v>-624700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-628900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>123800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>118400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-22000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-21900</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N100" s="3">
+      <c r="N100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P100" s="3">
         <v>-328100</v>
       </c>
-      <c r="O100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R100" s="3">
         <v>-1301500</v>
       </c>
-      <c r="Q100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T100" s="3">
         <v>-713100</v>
       </c>
-      <c r="S100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V100" s="3">
         <v>-242700</v>
       </c>
-      <c r="U100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X100" s="3">
         <v>-73200</v>
       </c>
-      <c r="W100" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="Y100" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E101" s="3">
+        <v>1400</v>
+      </c>
+      <c r="F101" s="3">
         <v>-15900</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-15200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>-74400</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>-74000</v>
       </c>
-      <c r="H101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J101" s="3">
+      <c r="J101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L101" s="3">
         <v>27500</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>29200</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>22900</v>
       </c>
-      <c r="M101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P101" s="3">
         <v>57100</v>
       </c>
-      <c r="O101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R101" s="3">
         <v>66600</v>
       </c>
-      <c r="Q101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T101" s="3">
         <v>22600</v>
       </c>
-      <c r="S101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V101" s="3">
         <v>-58700</v>
       </c>
-      <c r="U101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X101" s="3">
         <v>-16700</v>
       </c>
-      <c r="W101" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="Y101" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>0</v>
+        <v>-205800</v>
       </c>
       <c r="E102" s="3">
-        <v>0</v>
+        <v>-189400</v>
       </c>
       <c r="F102" s="3">
+        <v>0</v>
+      </c>
+      <c r="G102" s="3">
+        <v>0</v>
+      </c>
+      <c r="H102" s="3">
         <v>-192000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-193300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-34800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-33300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>329400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>327800</v>
       </c>
-      <c r="L102" s="3">
-        <v>0</v>
-      </c>
-      <c r="M102" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N102" s="3">
+        <v>0</v>
+      </c>
+      <c r="O102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P102" s="3">
         <v>793600</v>
       </c>
-      <c r="O102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R102" s="3">
         <v>56200</v>
       </c>
-      <c r="Q102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T102" s="3">
         <v>59400</v>
       </c>
-      <c r="S102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V102" s="3">
         <v>376700</v>
       </c>
-      <c r="U102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X102" s="3">
         <v>370800</v>
       </c>
-      <c r="W102" s="3" t="s">
+      <c r="Y102" s="3" t="s">
         <v>5</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CABGY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CABGY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="699" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="745" uniqueCount="92">
   <si>
     <t>CABGY</t>
   </si>
@@ -656,114 +656,121 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Y102"/>
+  <dimension ref="A5:AA102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45930</v>
+      </c>
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>44104</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>44012</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -800,41 +807,47 @@
       <c r="N8" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O8" s="3">
+      <c r="O8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q8" s="3">
         <v>2932900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>5174200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>2173500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>4572300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>2586000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>4077200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>1620100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>3984500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>2407800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>4229100</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>1899000</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -874,38 +887,44 @@
       <c r="O9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P9" s="3">
+      <c r="P9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R9" s="3">
         <v>2780100</v>
       </c>
-      <c r="Q9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T9" s="3">
         <v>2415700</v>
       </c>
-      <c r="S9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V9" s="3">
         <v>2122300</v>
       </c>
-      <c r="U9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X9" s="3">
         <v>2061000</v>
       </c>
-      <c r="W9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z9" s="3">
         <v>2172800</v>
       </c>
-      <c r="Y9" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="AA9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -945,38 +964,44 @@
       <c r="O10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P10" s="3">
+      <c r="P10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R10" s="3">
         <v>2394100</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T10" s="3">
         <v>2156600</v>
       </c>
-      <c r="S10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V10" s="3">
         <v>1954800</v>
       </c>
-      <c r="U10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X10" s="3">
         <v>1923500</v>
       </c>
-      <c r="W10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z10" s="3">
         <v>2056300</v>
       </c>
-      <c r="Y10" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="AA10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1002,8 +1027,10 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z11" s="3"/>
+      <c r="AA11" s="3"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1073,8 +1100,14 @@
       <c r="Y12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1144,8 +1177,14 @@
       <c r="Y13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1185,38 +1224,44 @@
       <c r="O14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P14" s="3">
+      <c r="P14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R14" s="3">
         <v>124500</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T14" s="3">
         <v>-34900</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V14" s="3">
         <v>28200</v>
       </c>
-      <c r="U14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X14" s="3">
         <v>38500</v>
       </c>
-      <c r="W14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z14" s="3">
         <v>1800</v>
       </c>
-      <c r="Y14" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="AA14" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1253,11 +1298,11 @@
       <c r="N15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O15" s="3">
-        <v>0</v>
-      </c>
-      <c r="P15" s="3">
-        <v>0</v>
+      <c r="O15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P15" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q15" s="3">
         <v>0</v>
@@ -1286,8 +1331,14 @@
       <c r="Y15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1310,8 +1361,10 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
-    </row>
-    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z16" s="3"/>
+      <c r="AA16" s="3"/>
+    </row>
+    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1351,38 +1404,44 @@
       <c r="O17" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P17" s="3">
+      <c r="P17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R17" s="3">
         <v>4358400</v>
       </c>
-      <c r="Q17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T17" s="3">
         <v>3608300</v>
       </c>
-      <c r="S17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V17" s="3">
         <v>3427400</v>
       </c>
-      <c r="U17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X17" s="3">
         <v>3341200</v>
       </c>
-      <c r="W17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z17" s="3">
         <v>3553900</v>
       </c>
-      <c r="Y17" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="AA17" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1422,38 +1481,44 @@
       <c r="O18" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P18" s="3">
+      <c r="P18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R18" s="3">
         <v>815800</v>
       </c>
-      <c r="Q18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T18" s="3">
         <v>964100</v>
       </c>
-      <c r="S18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V18" s="3">
         <v>649700</v>
       </c>
-      <c r="U18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X18" s="3">
         <v>643300</v>
       </c>
-      <c r="W18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z18" s="3">
         <v>675200</v>
       </c>
-      <c r="Y18" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="AA18" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1479,8 +1544,10 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
-    </row>
-    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z19" s="3"/>
+      <c r="AA19" s="3"/>
+    </row>
+    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1520,38 +1587,44 @@
       <c r="O20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P20" s="3">
+      <c r="P20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R20" s="3">
         <v>-38800</v>
       </c>
-      <c r="Q20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T20" s="3">
         <v>-33300</v>
       </c>
-      <c r="S20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V20" s="3">
         <v>-1600</v>
       </c>
-      <c r="U20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X20" s="3">
         <v>13400</v>
       </c>
-      <c r="W20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z20" s="3">
         <v>5300</v>
       </c>
-      <c r="Y20" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="AA20" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1591,38 +1664,44 @@
       <c r="O21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P21" s="3">
+      <c r="P21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R21" s="3">
         <v>1087600</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T21" s="3">
         <v>1547400</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V21" s="3">
         <v>926400</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X21" s="3">
         <v>1244900</v>
       </c>
-      <c r="W21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z21" s="3">
         <v>1000600</v>
       </c>
-      <c r="Y21" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="AA21" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1662,8 +1741,8 @@
       <c r="O22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P22" s="3">
-        <v>37100</v>
+      <c r="P22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q22" s="3" t="s">
         <v>5</v>
@@ -1675,25 +1754,31 @@
         <v>5</v>
       </c>
       <c r="T22" s="3">
+        <v>37100</v>
+      </c>
+      <c r="U22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V22" s="3">
         <v>36000</v>
       </c>
-      <c r="U22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X22" s="3">
         <v>34900</v>
       </c>
-      <c r="W22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z22" s="3">
         <v>34500</v>
       </c>
-      <c r="Y22" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="AA22" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1733,38 +1818,44 @@
       <c r="O23" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P23" s="3">
+      <c r="P23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R23" s="3">
         <v>739900</v>
       </c>
-      <c r="Q23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T23" s="3">
         <v>893700</v>
       </c>
-      <c r="S23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V23" s="3">
         <v>612200</v>
       </c>
-      <c r="U23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X23" s="3">
         <v>621900</v>
       </c>
-      <c r="W23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z23" s="3">
         <v>646000</v>
       </c>
-      <c r="Y23" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="AA23" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1804,38 +1895,44 @@
       <c r="O24" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P24" s="3">
+      <c r="P24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R24" s="3">
         <v>162800</v>
       </c>
-      <c r="Q24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T24" s="3">
         <v>152500</v>
       </c>
-      <c r="S24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V24" s="3">
         <v>157300</v>
       </c>
-      <c r="U24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X24" s="3">
         <v>145900</v>
       </c>
-      <c r="W24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z24" s="3">
         <v>168000</v>
       </c>
-      <c r="Y24" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="AA24" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1905,8 +2002,14 @@
       <c r="Y25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1946,38 +2049,44 @@
       <c r="O26" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P26" s="3">
+      <c r="P26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R26" s="3">
         <v>577200</v>
       </c>
-      <c r="Q26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T26" s="3">
         <v>741200</v>
       </c>
-      <c r="S26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V26" s="3">
         <v>454900</v>
       </c>
-      <c r="U26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X26" s="3">
         <v>476000</v>
       </c>
-      <c r="W26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z26" s="3">
         <v>478100</v>
       </c>
-      <c r="Y26" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="AA26" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2017,38 +2126,44 @@
       <c r="O27" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P27" s="3">
+      <c r="P27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R27" s="3">
         <v>487800</v>
       </c>
-      <c r="Q27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T27" s="3">
         <v>642700</v>
       </c>
-      <c r="S27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V27" s="3">
         <v>385800</v>
       </c>
-      <c r="U27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X27" s="3">
         <v>425800</v>
       </c>
-      <c r="W27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z27" s="3">
         <v>418800</v>
       </c>
-      <c r="Y27" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="AA27" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2118,8 +2233,14 @@
       <c r="Y28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2159,38 +2280,44 @@
       <c r="O29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P29" s="3">
+      <c r="P29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R29" s="3">
         <v>-1258000</v>
       </c>
-      <c r="Q29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T29" s="3">
         <v>-87000</v>
       </c>
-      <c r="S29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V29" s="3">
         <v>44700</v>
       </c>
-      <c r="U29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W29" s="3">
-        <v>0</v>
-      </c>
-      <c r="X29" s="3">
-        <v>0</v>
+      <c r="W29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2260,8 +2387,14 @@
       <c r="Y30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2331,8 +2464,14 @@
       <c r="Y31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2372,38 +2511,44 @@
       <c r="O32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P32" s="3">
+      <c r="P32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R32" s="3">
         <v>38800</v>
       </c>
-      <c r="Q32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T32" s="3">
         <v>33300</v>
       </c>
-      <c r="S32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V32" s="3">
         <v>1600</v>
       </c>
-      <c r="U32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X32" s="3">
         <v>-13400</v>
       </c>
-      <c r="W32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z32" s="3">
         <v>-5300</v>
       </c>
-      <c r="Y32" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="AA32" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -2443,38 +2588,44 @@
       <c r="O33" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P33" s="3">
+      <c r="P33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R33" s="3">
         <v>-770100</v>
       </c>
-      <c r="Q33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T33" s="3">
         <v>555700</v>
       </c>
-      <c r="S33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V33" s="3">
         <v>430400</v>
       </c>
-      <c r="U33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X33" s="3">
         <v>425800</v>
       </c>
-      <c r="W33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z33" s="3">
         <v>418800</v>
       </c>
-      <c r="Y33" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="AA33" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2544,8 +2695,14 @@
       <c r="Y34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -2585,114 +2742,126 @@
       <c r="O35" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P35" s="3">
+      <c r="P35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R35" s="3">
         <v>-770100</v>
       </c>
-      <c r="Q35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T35" s="3">
         <v>555700</v>
       </c>
-      <c r="S35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V35" s="3">
         <v>430400</v>
       </c>
-      <c r="U35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X35" s="3">
         <v>425800</v>
       </c>
-      <c r="W35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z35" s="3">
         <v>418800</v>
       </c>
-      <c r="Y35" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="AA35" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45930</v>
+      </c>
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>44104</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>44012</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2718,8 +2887,10 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z39" s="3"/>
+      <c r="AA39" s="3"/>
+    </row>
+    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2745,50 +2916,52 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z40" s="3"/>
+      <c r="AA40" s="3"/>
+    </row>
+    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1506900</v>
+      </c>
+      <c r="E41" s="3">
+        <v>1505800</v>
+      </c>
+      <c r="F41" s="3">
         <v>1487300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>1368800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>1602300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>1726300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>1538600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>1548900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>1984500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>1898100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>1647100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>1638800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>1172800</v>
       </c>
-      <c r="O41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P41" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q41" s="3" t="s">
         <v>5</v>
       </c>
@@ -2816,55 +2989,61 @@
       <c r="Y41" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA41" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
         <v>102800</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>94600</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>8200</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>8800</v>
       </c>
-      <c r="H42" s="3">
-        <v>0</v>
-      </c>
-      <c r="I42" s="3">
-        <v>0</v>
-      </c>
       <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
         <v>331600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>317100</v>
       </c>
-      <c r="L42" s="3">
-        <v>0</v>
-      </c>
-      <c r="M42" s="3">
-        <v>0</v>
-      </c>
       <c r="N42" s="3">
         <v>0</v>
       </c>
-      <c r="O42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q42" s="3">
-        <v>0</v>
-      </c>
-      <c r="R42" s="3">
-        <v>0</v>
+      <c r="O42" s="3">
+        <v>0</v>
+      </c>
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R42" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="S42" s="3">
         <v>0</v>
@@ -2887,50 +3066,56 @@
       <c r="Y42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1742700</v>
+      </c>
+      <c r="E43" s="3">
+        <v>1741400</v>
+      </c>
+      <c r="F43" s="3">
         <v>2600900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>2393700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>1056200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>1137900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>1764900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>1776700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>1176600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>1125300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>1798100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>1789000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>1118700</v>
       </c>
-      <c r="O43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P43" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q43" s="3" t="s">
         <v>5</v>
       </c>
@@ -2958,50 +3143,56 @@
       <c r="Y43" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA43" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1117800</v>
+      </c>
+      <c r="E44" s="3">
+        <v>1117000</v>
+      </c>
+      <c r="F44" s="3">
         <v>1262400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>1161900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>826400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>890300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>936900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>943100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>861800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>824200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>982100</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>977100</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>821600</v>
       </c>
-      <c r="O44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P44" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q44" s="3" t="s">
         <v>5</v>
       </c>
@@ -3029,8 +3220,14 @@
       <c r="Y44" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA44" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3058,21 +3255,21 @@
       <c r="K45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N45" s="3">
         <v>1478200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>1470800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>1669300</v>
       </c>
-      <c r="O45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P45" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q45" s="3" t="s">
         <v>5</v>
       </c>
@@ -3100,50 +3297,56 @@
       <c r="Y45" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA45" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>4598300</v>
+      </c>
+      <c r="E46" s="3">
+        <v>4594900</v>
+      </c>
+      <c r="F46" s="3">
         <v>5453400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>5019000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>3657500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>3940500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>4240400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>4268600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>4478300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>4283200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>5905500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>5875600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>4920800</v>
       </c>
-      <c r="O46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P46" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q46" s="3" t="s">
         <v>5</v>
       </c>
@@ -3171,50 +3374,56 @@
       <c r="Y46" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA46" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F47" s="3">
-        <v>648900</v>
-      </c>
-      <c r="G47" s="3">
-        <v>699100</v>
-      </c>
-      <c r="H47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J47" s="3">
+      <c r="D47" s="3">
+        <v>679900</v>
+      </c>
+      <c r="E47" s="3">
+        <v>679400</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H47" s="3">
+        <v>631100</v>
+      </c>
+      <c r="I47" s="3">
+        <v>679900</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L47" s="3">
         <v>806300</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>771200</v>
       </c>
-      <c r="L47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N47" s="3">
+      <c r="N47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P47" s="3">
         <v>793500</v>
       </c>
-      <c r="O47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P47" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q47" s="3" t="s">
         <v>5</v>
       </c>
@@ -3242,50 +3451,56 @@
       <c r="Y47" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA47" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>5153400</v>
+      </c>
+      <c r="E48" s="3">
+        <v>5149700</v>
+      </c>
+      <c r="F48" s="3">
         <v>4874100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>4485800</v>
       </c>
-      <c r="F48" s="3">
-        <v>3755100</v>
-      </c>
-      <c r="G48" s="3">
-        <v>4045700</v>
-      </c>
       <c r="H48" s="3">
+        <v>3755600</v>
+      </c>
+      <c r="I48" s="3">
+        <v>4046100</v>
+      </c>
+      <c r="J48" s="3">
         <v>3602900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>3626900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>3619200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>3461500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>3457900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>3440400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>3402200</v>
       </c>
-      <c r="O48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q48" s="3" t="s">
         <v>5</v>
       </c>
@@ -3313,50 +3528,56 @@
       <c r="Y48" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA48" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>13084800</v>
+      </c>
+      <c r="E49" s="3">
+        <v>13075400</v>
+      </c>
+      <c r="F49" s="3">
         <v>12758300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>11741900</v>
       </c>
-      <c r="F49" s="3">
-        <v>7272500</v>
-      </c>
-      <c r="G49" s="3">
-        <v>7835200</v>
-      </c>
       <c r="H49" s="3">
+        <v>7382000</v>
+      </c>
+      <c r="I49" s="3">
+        <v>7953200</v>
+      </c>
+      <c r="J49" s="3">
         <v>7070000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>7117200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>7281400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>6964200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>7186600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>7150200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>7072300</v>
       </c>
-      <c r="O49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P49" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q49" s="3" t="s">
         <v>5</v>
       </c>
@@ -3384,8 +3605,14 @@
       <c r="Y49" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA49" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3455,8 +3682,14 @@
       <c r="Y50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3526,50 +3759,56 @@
       <c r="Y51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>205300</v>
+      </c>
+      <c r="E52" s="3">
+        <v>205200</v>
+      </c>
+      <c r="F52" s="3">
         <v>1256500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>1156400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>27300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>29500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>1217500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>1225600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>33200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>31800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>1186800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>1180800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>42000</v>
       </c>
-      <c r="O52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q52" s="3" t="s">
         <v>5</v>
       </c>
@@ -3597,8 +3836,14 @@
       <c r="Y52" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA52" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3668,50 +3913,56 @@
       <c r="Y53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>24203400</v>
+      </c>
+      <c r="E54" s="3">
+        <v>24185900</v>
+      </c>
+      <c r="F54" s="3">
         <v>24342300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>22403100</v>
       </c>
-      <c r="F54" s="3">
-        <v>15732400</v>
-      </c>
-      <c r="G54" s="3">
-        <v>16949700</v>
-      </c>
       <c r="H54" s="3">
+        <v>15824600</v>
+      </c>
+      <c r="I54" s="3">
+        <v>17049000</v>
+      </c>
+      <c r="J54" s="3">
         <v>16130800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>16238300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>16584200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>15861800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>17736800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>17647100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>16572000</v>
       </c>
-      <c r="O54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P54" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q54" s="3" t="s">
         <v>5</v>
       </c>
@@ -3739,8 +3990,14 @@
       <c r="Y54" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA54" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3766,8 +4023,10 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
-    </row>
-    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z55" s="3"/>
+      <c r="AA55" s="3"/>
+    </row>
+    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3793,50 +4052,52 @@
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
-    </row>
-    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z56" s="3"/>
+      <c r="AA56" s="3"/>
+    </row>
+    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>4225400</v>
+      </c>
+      <c r="E57" s="3">
+        <v>4222300</v>
+      </c>
+      <c r="F57" s="3">
         <v>4531800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>4170800</v>
       </c>
-      <c r="F57" s="3">
-        <v>3236900</v>
-      </c>
-      <c r="G57" s="3">
-        <v>3487400</v>
-      </c>
       <c r="H57" s="3">
+        <v>3233900</v>
+      </c>
+      <c r="I57" s="3">
+        <v>3484100</v>
+      </c>
+      <c r="J57" s="3">
         <v>3707200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>3731900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>3286100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>3143000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>3672400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>3653800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>3149000</v>
       </c>
-      <c r="O57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q57" s="3" t="s">
         <v>5</v>
       </c>
@@ -3864,50 +4125,56 @@
       <c r="Y57" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA57" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1441800</v>
+      </c>
+      <c r="E58" s="3">
+        <v>1440700</v>
+      </c>
+      <c r="F58" s="3">
         <v>1144400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>1053200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>1492100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>1607500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>902800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>908900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>1236500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>1182600</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>1996400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>1986300</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>830600</v>
       </c>
-      <c r="O58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P58" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q58" s="3" t="s">
         <v>5</v>
       </c>
@@ -3935,50 +4202,56 @@
       <c r="Y58" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA58" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1964800</v>
+      </c>
+      <c r="E59" s="3">
+        <v>1963400</v>
+      </c>
+      <c r="F59" s="3">
         <v>2143700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>1973000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>1663100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>1791800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>2535700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>2552600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>2481500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>2373400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>3231600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>3215200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>3024300</v>
       </c>
-      <c r="O59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q59" s="3" t="s">
         <v>5</v>
       </c>
@@ -4006,50 +4279,56 @@
       <c r="Y59" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA59" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>7632000</v>
+      </c>
+      <c r="E60" s="3">
+        <v>7626400</v>
+      </c>
+      <c r="F60" s="3">
         <v>7819900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>7197000</v>
       </c>
-      <c r="F60" s="3">
-        <v>6392100</v>
-      </c>
-      <c r="G60" s="3">
-        <v>6886600</v>
-      </c>
       <c r="H60" s="3">
+        <v>6389000</v>
+      </c>
+      <c r="I60" s="3">
+        <v>6883300</v>
+      </c>
+      <c r="J60" s="3">
         <v>7145800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>7193400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>7004100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>6699000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>8900400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>8855300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>7003900</v>
       </c>
-      <c r="O60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P60" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q60" s="3" t="s">
         <v>5</v>
       </c>
@@ -4077,50 +4356,56 @@
       <c r="Y60" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA60" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>9660900</v>
+      </c>
+      <c r="E61" s="3">
+        <v>9653900</v>
+      </c>
+      <c r="F61" s="3">
         <v>10518200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>9680300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>3802600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>4096800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>4424300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>4453800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>4562100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>4363300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>3103800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>3088100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>3285200</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
         <v>0</v>
       </c>
@@ -4148,50 +4433,56 @@
       <c r="Y61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>520200</v>
+      </c>
+      <c r="E62" s="3">
+        <v>519800</v>
+      </c>
+      <c r="F62" s="3">
         <v>1632400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>1502400</v>
       </c>
-      <c r="F62" s="3">
-        <v>448500</v>
-      </c>
-      <c r="G62" s="3">
-        <v>483200</v>
-      </c>
       <c r="H62" s="3">
+        <v>497000</v>
+      </c>
+      <c r="I62" s="3">
+        <v>535400</v>
+      </c>
+      <c r="J62" s="3">
         <v>1112300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>1119700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>278700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>266500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>1230500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>1224300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>374900</v>
       </c>
-      <c r="O62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P62" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q62" s="3" t="s">
         <v>5</v>
       </c>
@@ -4219,8 +4510,14 @@
       <c r="Y62" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA62" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4290,8 +4587,14 @@
       <c r="Y63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4361,8 +4664,14 @@
       <c r="Y64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4432,50 +4741,56 @@
       <c r="Y65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>19380800</v>
+      </c>
+      <c r="E66" s="3">
+        <v>19366800</v>
+      </c>
+      <c r="F66" s="3">
         <v>19970500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>18379600</v>
       </c>
-      <c r="F66" s="3">
-        <v>11482800</v>
-      </c>
-      <c r="G66" s="3">
-        <v>12371200</v>
-      </c>
       <c r="H66" s="3">
+        <v>11575000</v>
+      </c>
+      <c r="I66" s="3">
+        <v>12470600</v>
+      </c>
+      <c r="J66" s="3">
         <v>12682400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>12766900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>12765700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>12209600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>13234700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>13167700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>11583200</v>
       </c>
-      <c r="O66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P66" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q66" s="3" t="s">
         <v>5</v>
       </c>
@@ -4503,8 +4818,14 @@
       <c r="Y66" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA66" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4530,8 +4851,10 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-    </row>
-    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z67" s="3"/>
+      <c r="AA67" s="3"/>
+    </row>
+    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4601,8 +4924,14 @@
       <c r="Y68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4672,8 +5001,14 @@
       <c r="Y69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4743,8 +5078,14 @@
       <c r="Y70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4814,50 +5155,56 @@
       <c r="Y71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>4456100</v>
+      </c>
+      <c r="E72" s="3">
+        <v>4452900</v>
+      </c>
+      <c r="F72" s="3">
         <v>4033400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>3712100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>3551300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>3826100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>3086700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>3107300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>3456200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>3305700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>10183900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>10132400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>10169000</v>
       </c>
-      <c r="O72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q72" s="3" t="s">
         <v>5</v>
       </c>
@@ -4885,8 +5232,14 @@
       <c r="Y72" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA72" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4956,8 +5309,14 @@
       <c r="Y73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5027,8 +5386,14 @@
       <c r="Y74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5098,50 +5463,56 @@
       <c r="Y75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4371100</v>
+      </c>
+      <c r="E76" s="3">
+        <v>4367900</v>
+      </c>
+      <c r="F76" s="3">
         <v>3939100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>3625300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>3855200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>4153500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>3112100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>3132900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>3445500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>3295400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>4146100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>4125100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>4583600</v>
       </c>
-      <c r="O76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P76" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q76" s="3" t="s">
         <v>5</v>
       </c>
@@ -5169,8 +5540,14 @@
       <c r="Y76" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA76" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5240,84 +5617,96 @@
       <c r="Y77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45930</v>
+      </c>
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>44104</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>44012</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -5357,38 +5746,44 @@
       <c r="O81" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P81" s="3">
+      <c r="P81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R81" s="3">
         <v>-770100</v>
       </c>
-      <c r="Q81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T81" s="3">
         <v>555700</v>
       </c>
-      <c r="S81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V81" s="3">
         <v>430400</v>
       </c>
-      <c r="U81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X81" s="3">
         <v>425800</v>
       </c>
-      <c r="W81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z81" s="3">
         <v>418800</v>
       </c>
-      <c r="Y81" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="AA81" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5414,79 +5809,87 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
-    </row>
-    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z82" s="3"/>
+      <c r="AA82" s="3"/>
+    </row>
+    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
+      <c r="D83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F83" s="3">
         <v>149900</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>150900</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>136100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>130200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>143400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>142700</v>
       </c>
-      <c r="J83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L83" s="3">
+      <c r="L83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N83" s="3">
         <v>149700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>158800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>169300</v>
       </c>
-      <c r="O83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R83" s="3">
         <v>310600</v>
       </c>
-      <c r="Q83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T83" s="3">
         <v>671000</v>
       </c>
-      <c r="S83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V83" s="3">
         <v>303500</v>
       </c>
-      <c r="U83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X83" s="3">
         <v>588200</v>
       </c>
-      <c r="W83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z83" s="3">
         <v>320100</v>
       </c>
-      <c r="Y83" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="AA83" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5556,8 +5959,14 @@
       <c r="Y84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5627,8 +6036,14 @@
       <c r="Y85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5698,8 +6113,14 @@
       <c r="Y86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5769,8 +6190,14 @@
       <c r="Y87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5840,79 +6267,91 @@
       <c r="Y88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>559700</v>
+      </c>
+      <c r="E89" s="3">
+        <v>559300</v>
+      </c>
+      <c r="F89" s="3">
         <v>418000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>384700</v>
       </c>
-      <c r="F89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H89" s="3">
+      <c r="H89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J89" s="3">
         <v>422500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>425300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>183800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>175800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>596100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>593100</v>
       </c>
-      <c r="N89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P89" s="3">
+      <c r="P89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R89" s="3">
         <v>1223200</v>
       </c>
-      <c r="Q89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T89" s="3">
         <v>1929200</v>
       </c>
-      <c r="S89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V89" s="3">
         <v>950500</v>
       </c>
-      <c r="U89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X89" s="3">
         <v>1465600</v>
       </c>
-      <c r="W89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z89" s="3">
         <v>749900</v>
       </c>
-      <c r="Y89" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="AA89" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5938,49 +6377,51 @@
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
-    </row>
-    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z90" s="3"/>
+      <c r="AA90" s="3"/>
+    </row>
+    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-189300</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-189100</v>
+      </c>
+      <c r="F91" s="3">
         <v>-198000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-182300</v>
       </c>
-      <c r="F91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H91" s="3">
+      <c r="H91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J91" s="3">
         <v>-156700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-157700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-155300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-148600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-131300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-130700</v>
       </c>
-      <c r="N91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
-      <c r="P91" s="3">
-        <v>0</v>
+      <c r="P91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q91" s="3">
         <v>0</v>
@@ -5992,25 +6433,31 @@
         <v>0</v>
       </c>
       <c r="T91" s="3">
+        <v>0</v>
+      </c>
+      <c r="U91" s="3">
+        <v>0</v>
+      </c>
+      <c r="V91" s="3">
         <v>-235900</v>
       </c>
-      <c r="U91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X91" s="3">
         <v>-589500</v>
       </c>
-      <c r="W91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z91" s="3">
         <v>-363900</v>
       </c>
-      <c r="Y91" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="AA91" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6080,8 +6527,14 @@
       <c r="Y92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6151,79 +6604,91 @@
       <c r="Y93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-164500</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-164400</v>
+      </c>
+      <c r="F94" s="3">
         <v>-2519300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-2318600</v>
       </c>
-      <c r="F94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H94" s="3">
+      <c r="H94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J94" s="3">
         <v>8800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>8800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-326600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-312400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-170300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-169500</v>
       </c>
-      <c r="N94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P94" s="3">
+      <c r="P94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R94" s="3">
         <v>-158500</v>
       </c>
-      <c r="Q94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T94" s="3">
         <v>-591700</v>
       </c>
-      <c r="S94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V94" s="3">
         <v>-179600</v>
       </c>
-      <c r="U94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X94" s="3">
         <v>-787400</v>
       </c>
-      <c r="W94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z94" s="3">
         <v>-289100</v>
       </c>
-      <c r="Y94" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="AA94" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6249,79 +6714,87 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
-    </row>
-    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z95" s="3"/>
+      <c r="AA95" s="3"/>
+    </row>
+    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>0</v>
+      </c>
+      <c r="E96" s="3">
+        <v>0</v>
+      </c>
+      <c r="F96" s="3">
         <v>280900</v>
       </c>
-      <c r="E96" s="3">
+      <c r="G96" s="3">
         <v>258600</v>
       </c>
-      <c r="F96" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G96" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H96" s="3">
+      <c r="H96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J96" s="3">
         <v>258700</v>
       </c>
-      <c r="I96" s="3">
+      <c r="K96" s="3">
         <v>260400</v>
       </c>
-      <c r="J96" s="3">
-        <v>0</v>
-      </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
       <c r="L96" s="3">
+        <v>0</v>
+      </c>
+      <c r="M96" s="3">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3">
         <v>270800</v>
       </c>
-      <c r="M96" s="3">
+      <c r="O96" s="3">
         <v>269400</v>
       </c>
-      <c r="N96" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
-      <c r="P96" s="3">
+      <c r="P96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3">
         <v>-494700</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
-      </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
+        <v>0</v>
+      </c>
+      <c r="T96" s="3">
         <v>-463700</v>
       </c>
-      <c r="S96" s="3">
-        <v>0</v>
-      </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+      <c r="V96" s="3">
         <v>-453200</v>
       </c>
-      <c r="U96" s="3">
-        <v>0</v>
-      </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+      <c r="X96" s="3">
         <v>-414800</v>
       </c>
-      <c r="W96" s="3">
-        <v>0</v>
-      </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z96" s="3">
         <v>-453700</v>
       </c>
-      <c r="Y96" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6391,8 +6864,14 @@
       <c r="Y97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6462,8 +6941,14 @@
       <c r="Y98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6533,217 +7018,241 @@
       <c r="Y99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-337800</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-337600</v>
+      </c>
+      <c r="F100" s="3">
         <v>1937000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>1782700</v>
       </c>
-      <c r="F100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H100" s="3">
+      <c r="H100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J100" s="3">
         <v>-624700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-628900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>123800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>118400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-22000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-21900</v>
       </c>
-      <c r="N100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P100" s="3">
+      <c r="P100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R100" s="3">
         <v>-328100</v>
       </c>
-      <c r="Q100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T100" s="3">
         <v>-1301500</v>
       </c>
-      <c r="S100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V100" s="3">
         <v>-713100</v>
       </c>
-      <c r="U100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X100" s="3">
         <v>-242700</v>
       </c>
-      <c r="W100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z100" s="3">
         <v>-73200</v>
       </c>
-      <c r="Y100" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="AA100" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
+      <c r="D101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F101" s="3">
         <v>1400</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>1400</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>-15900</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>-15200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>-74400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>-74000</v>
       </c>
-      <c r="J101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L101" s="3">
+      <c r="L101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N101" s="3">
         <v>27500</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>29200</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>22900</v>
       </c>
-      <c r="O101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R101" s="3">
         <v>57100</v>
       </c>
-      <c r="Q101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T101" s="3">
         <v>66600</v>
       </c>
-      <c r="S101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V101" s="3">
         <v>22600</v>
       </c>
-      <c r="U101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X101" s="3">
         <v>-58700</v>
       </c>
-      <c r="W101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z101" s="3">
         <v>-16700</v>
       </c>
-      <c r="Y101" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="AA101" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>51500</v>
+      </c>
+      <c r="E102" s="3">
+        <v>51400</v>
+      </c>
+      <c r="F102" s="3">
         <v>-205800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-189400</v>
       </c>
-      <c r="F102" s="3">
-        <v>0</v>
-      </c>
-      <c r="G102" s="3">
-        <v>0</v>
-      </c>
       <c r="H102" s="3">
+        <v>0</v>
+      </c>
+      <c r="I102" s="3">
+        <v>0</v>
+      </c>
+      <c r="J102" s="3">
         <v>-192000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-193300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-34800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-33300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>329400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>327800</v>
       </c>
-      <c r="N102" s="3">
-        <v>0</v>
-      </c>
-      <c r="O102" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R102" s="3">
         <v>793600</v>
       </c>
-      <c r="Q102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T102" s="3">
         <v>56200</v>
       </c>
-      <c r="S102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V102" s="3">
         <v>59400</v>
       </c>
-      <c r="U102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X102" s="3">
         <v>376700</v>
       </c>
-      <c r="W102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z102" s="3">
         <v>370800</v>
       </c>
-      <c r="Y102" s="3" t="s">
+      <c r="AA102" s="3" t="s">
         <v>5</v>
       </c>
     </row>
